--- a/google_data/Opravný Report.xlsx
+++ b/google_data/Opravný Report.xlsx
@@ -2759,8 +2759,8 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),0.4550848808059312)</f>
-        <v>0.4550848808</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),0.4622972088058687)</f>
+        <v>0.4622972088</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="16">
@@ -25801,8 +25801,8 @@
       <c r="T1" s="198"/>
       <c r="U1" s="198"/>
       <c r="V1" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),31.0)</f>
-        <v>31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),30.0)</f>
+        <v>30</v>
       </c>
       <c r="W1" s="201" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"dní")</f>
@@ -26007,8 +26007,8 @@
         <v>432.3078</v>
       </c>
       <c r="W5" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X5" s="198"/>
       <c r="Y5" s="198"/>
@@ -26073,8 +26073,8 @@
         <v>432.3078</v>
       </c>
       <c r="W6" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X6" s="198"/>
       <c r="Y6" s="198"/>
@@ -26133,8 +26133,8 @@
         <v>341.19</v>
       </c>
       <c r="W7" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X7" s="198"/>
       <c r="Y7" s="198"/>
@@ -26202,8 +26202,8 @@
         <v>432.3078</v>
       </c>
       <c r="W8" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X8" s="198"/>
       <c r="Y8" s="198"/>
@@ -26265,8 +26265,8 @@
         <v>341.19</v>
       </c>
       <c r="W9" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X9" s="198"/>
       <c r="Y9" s="198"/>
@@ -26334,8 +26334,8 @@
         <v>432.3078</v>
       </c>
       <c r="W10" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X10" s="198"/>
       <c r="Y10" s="198"/>
@@ -26514,8 +26514,8 @@
         <v>341.19</v>
       </c>
       <c r="W13" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X13" s="198"/>
       <c r="Y13" s="198"/>
@@ -26643,8 +26643,8 @@
         <v>341.19</v>
       </c>
       <c r="W15" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X15" s="198"/>
       <c r="Y15" s="198"/>
@@ -26706,8 +26706,8 @@
         <v>341.19</v>
       </c>
       <c r="W16" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
-        <v>2201.225806</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
+        <v>2274.6</v>
       </c>
       <c r="X16" s="198"/>
       <c r="Y16" s="198"/>
@@ -27015,8 +27015,8 @@
         <v>432.3078</v>
       </c>
       <c r="W21" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X21" s="198"/>
       <c r="Y21" s="198"/>
@@ -27075,8 +27075,8 @@
         <v>432.3078</v>
       </c>
       <c r="W22" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
-        <v>2789.082581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
+        <v>2882.052</v>
       </c>
       <c r="X22" s="198"/>
       <c r="Y22" s="198"/>
@@ -31101,8 +31101,8 @@
         <v>386.682</v>
       </c>
       <c r="W96" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2494.722580645161)</f>
-        <v>2494.722581</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2577.8799999999997)</f>
+        <v>2577.88</v>
       </c>
       <c r="X96" s="198"/>
       <c r="Y96" s="198"/>
@@ -32574,8 +32574,8 @@
         <v>49506</v>
       </c>
       <c r="W122" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1596.967741935484)</f>
-        <v>1596.967742</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1650.2)</f>
+        <v>1650.2</v>
       </c>
       <c r="X122" s="198"/>
       <c r="Y122" s="198"/>
@@ -32957,8 +32957,8 @@
       <c r="T129" s="198"/>
       <c r="U129" s="198"/>
       <c r="V129" s="201">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
-        <v>170</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),200.0)</f>
+        <v>200</v>
       </c>
       <c r="W129" s="201">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>

--- a/google_data/Opravný Report.xlsx
+++ b/google_data/Opravný Report.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="492">
   <si>
-    <t>Bolevec</t>
+    <t>Libuš</t>
   </si>
   <si>
     <t>Datum</t>
@@ -86,19 +86,31 @@
     <t>Počet hodin</t>
   </si>
   <si>
-    <t>Roth Stanislav ml.</t>
+    <t>Hegedüs Erik</t>
   </si>
   <si>
     <t>10:00</t>
   </si>
   <si>
-    <t>01:00</t>
+    <t>17:00</t>
   </si>
   <si>
     <t>Výdaje</t>
   </si>
   <si>
+    <t>Bubník Martin</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
     <t>Benzín</t>
+  </si>
+  <si>
+    <t>Eszenyiová Patrícia</t>
+  </si>
+  <si>
+    <t>22:45</t>
   </si>
   <si>
     <t>Auta</t>
@@ -152,13 +164,7 @@
     <t>Počet pozdě přiřazeným WoltDrive 5+</t>
   </si>
   <si>
-    <t>Vopatová Anna</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>Světlík František</t>
+    <t>Dušek Sam</t>
   </si>
   <si>
     <t>11:00</t>
@@ -260,22 +266,25 @@
     <t>damejidlo</t>
   </si>
   <si>
-    <t>canceled</t>
+    <t>ready_pickup</t>
   </si>
   <si>
-    <t>delivery</t>
+    <t>external-delivery</t>
   </si>
   <si>
-    <t>cash</t>
+    <t>online</t>
   </si>
   <si>
-    <t>2026-06-02T00:32:05.882+02:00</t>
+    <t>2026-06-07T23:07:28.092+02:00</t>
   </si>
   <si>
-    <t>F - Pizza Comeback Bolevec - rozvoz</t>
+    <t>2026-06-07T23:14:11.931+02:00</t>
   </si>
   <si>
-    <t>[{"id":"65874323","note":"","size":"Hot &amp; Spicy 40cm 🌶️🌶️","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":32900,"isExtra":false},{"id":"65874385","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"65874504","note":"","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"65874359","note":"","size":"Dip Jalapeňos","count":1,"label":"Dip Jalapeňos","posId":"P107","price":2500,"isExtra":false}]</t>
+    <t>Pizza Comeback Libuš</t>
+  </si>
+  <si>
+    <t>[{"id":"55199471","note":"","size":"Quattro Formaggi 40cm","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199662","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
   </si>
   <si>
     <t>generic</t>
@@ -284,451 +293,1087 @@
     <t>delivered</t>
   </si>
   <si>
-    <t>pickup</t>
+    <t>delivery</t>
   </si>
   <si>
-    <t>2026-06-01T23:57:05.673+02:00</t>
+    <t>2026-06-07T23:05:07.221+02:00</t>
   </si>
   <si>
-    <t>2026-06-02T00:08:38.117+02:00</t>
+    <t>2026-06-07T23:07:32.219+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T23:25:26.572+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T23:05:07.346+02:00</t>
   </si>
   <si>
     <t>Adaptee</t>
   </si>
   <si>
-    <t>[{"id":"0b867b16-3995-4b4a-9deb-1c0d8cecf8d6","note":"","count":1,"label":"Pepperoni 32 cm","posId":"120","price":25900,"isExtra":false},{"id":"fcbcf6b6-34c6-4d5f-ac5b-f6ece72e0953","note":"","count":1,"label":"BBQ Meteor 32 cm","posId":"118","price":25900,"isExtra":false}]</t>
+    <t>[{"id":"e8f571e6-dd36-42d7-8826-52c90315986b","note":"","count":1,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false},{"id":"e1ef9526-7c68-483b-a8a1-92bb58ce9f1e","note":"","count":1,"label":"Jalapenos Rolls","posId":"jpr200","price":8900,"isExtra":false},{"id":"739ceea4-4275-4f09-8cf5-ae08fe640a77","note":"","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:54:06.980+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T23:05:03.921+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199479","note":"","size":"Hawai 40cm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199592","note":"","count":1,"label":"Bez ananasu","posId":"X100","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>pickup</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:52:57.376+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T23:02:45.051+02:00</t>
+  </si>
+  <si>
+    <t>Ručně zadané obj.</t>
+  </si>
+  <si>
+    <t>[{"id":"R1tT2XKKK09mV9E4oM_A2","count":1,"label":"BBQ Texas 32cm","posId":"119","price":24900,"isExtra":false,"creatorId":"fdYt-_KNAQXKtF2EU98lm","isPackging":0,"actualLabel":"BBQ Texas 32cm"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:49:27.806+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:57:52.111+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199472","note":"","size":"Hot &amp; Spicy 40cm 🌶️🌶️","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199611","note":"","count":1,"label":"okraj hotdog, hořčice","posId":"A118","price":6500,"isExtra":true},{"id":"59589456","note":"","size":"Quattro Formaggi 32cm","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199511","note":"","size":"Spicy Wings 🌶️","count":2,"label":"spicy wings 🌶️","posId":"P101","price":11900,"isExtra":false},{"id":"55199562","note":"","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:45:11.706+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:54:05.725+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"slIXfu3mjSW-0V2k39Ukz","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false,"creatorId":"TSfzk79JeAkTputyaLsi1","isPackging":0,"actualLabel":"Hawai 32cm"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:39:46.425+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:52:11.837+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589458","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>bolt</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:32:32.479+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:41:31.079+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"102","note":"","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"111","note":"","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:24:25.034+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:37:14.017+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589457","note":"","size":"Hot &amp; Spicy 32cm 🌶️🌶️","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59589455","note":"","size":"Margherita 32cm","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199516","note":"","size":"Česnekový dip","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
   </si>
   <si>
     <t>wolt</t>
   </si>
   <si>
-    <t>external-delivery</t>
+    <t>2026-06-07T22:18:38.259+02:00</t>
   </si>
   <si>
-    <t>online</t>
+    <t>2026-06-07T22:26:14.734+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T23:35:26.525+02:00</t>
+    <t>[{"id":"8a4618993c6f7ee5917bb6ac","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59839d6b839f5e8fe6d29556","count":1,"label":"BBQ základ","posId":"ZRB32","price":0,"isExtra":true},{"id":"9db33b6e2b744d67b8488546","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A123","price":5700,"isExtra":true},{"id":"4f453a9a502066523bdfdc6b","count":1,"label":"Cibule","posId":"B103","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"730ed795f7d83f1d26b843e5","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
   </si>
   <si>
-    <t>2026-06-01T23:46:35.153+02:00</t>
+    <t>2026-06-07T22:12:06.596+02:00</t>
   </si>
   <si>
-    <t>W - Pizza Comeback Bolevec</t>
+    <t>2026-06-07T22:23:43.851+02:00</t>
   </si>
   <si>
-    <t>[{"id":"6893484371e1a7827faa282a","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":29900,"isExtra":false},{"id":"8492ff01857ad344daba3d10","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+    <t>[{"id":"59589458","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199586","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
   </si>
   <si>
-    <t>bolt</t>
+    <t>2026-06-07T22:05:18.254+02:00</t>
   </si>
   <si>
-    <t>Yevhenii</t>
+    <t>2026-06-07T22:13:41.102+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T23:33:46.379+02:00</t>
+    <t>[{"id":"55199479","note":"","size":"Hawai 40cm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199475","note":"","size":"BBQ Texas 40cm","count":1,"label":"BBQ Texas 40cm","posId":"107","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199617","note":"","count":1,"label":"Bez papriky","posId":"X111","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"57405742","note":"","size":"Pepsi 1l","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-06-01T23:45:02.283+02:00</t>
+    <t>2026-06-07T22:01:23.865+02:00</t>
   </si>
   <si>
-    <t>B - Pizza Comeback Bolevec</t>
+    <t>2026-06-07T22:10:08.407+02:00</t>
   </si>
   <si>
-    <t>[{"id":"N125","note":"","count":1,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false},{"id":"110","note":"","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":29900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZRS40","note":"","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"A122","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6900,"isExtra":true},{"id":"C100","note":"","count":1,"label":"Ananas","posId":"C100","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"P106","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>[{"id":"c4cf500880b17d3ffa827758","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"c8f41becd43979fe4250d2db","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"730ed795f7d83f1d26b843e5","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
   </si>
   <si>
-    <t>Roman</t>
+    <t>2026-06-07T21:56:04.078+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T23:18:10.347+02:00</t>
+    <t>2026-06-07T22:46:24.912+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T23:26:16.144+02:00</t>
+    <t>[{"id":"b3008ec8-24a5-4d30-bf46-9133028be7e4","note":"","count":1,"label":"Margherita 32 cm","posId":"136","price":20900,"isExtra":false},{"id":"a4efa812-1470-4ea2-a19d-39843abed3be","note":"","count":1,"label":"Comeback 32 cm","posId":"145","price":24900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>[{"id":"106","note":"","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":29900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZBR40","note":"","count":1,"label":"Rajčatový základ","posId":"ZBR40","price":0,"isExtra":true}]</t>
+    <t>2026-06-07T21:50:20.103+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T23:07:12.697+02:00</t>
+    <t>2026-06-07T21:58:37.807+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T23:17:28.308+02:00</t>
+    <t>[{"id":"55199510","note":"","size":"Veggie menu Comeback","count":1,"label":"Veggie menu Comeback","posId":"M200","price":34900,"isExtra":false},{"id":"55199670","note":"","count":1,"label":"Veggieballs","posId":"Y117","price":0,"isExtra":true},{"id":"55199547","note":"","count":1,"label":"Balné","posId":"K0000","price":3000,"isExtra":true},{"id":"55199586","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"55199543","note":"","count":1,"label":"pečené brambory","posId":"P103","price":0,"isExtra":true},{"id":"61748710","note":"","count":1,"label":"Guarana kiwi a jablko","posId":"N144","price":0,"isExtra":true},{"id":"55199516","note":"","size":"Česnekový dip","count":2,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"55199562","note":"","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199519","note":"","size":"Choco Rolls","count":1,"label":"Choco Rolls","posId":"chr100","price":8900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
   </si>
   <si>
-    <t>[{"id":"50407dc440b990acd4054e0f","count":2,"label":"Pilsner Urquell 12","posId":"N20","price":6500,"isExtra":false},{"id":"6893484371e1a7827faa2844","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":22900,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"cc6a9570333d25cab14bc37d","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"380ab62bcb0705673955fc74","count":1,"label":"Šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"8cfd349c9dc7f129d0cfd899","count":2,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"6893484371e1a7827faa285e","count":1,"label":"Masové kuličky","posId":"P102","price":8900,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>2026-06-07T21:40:35.061+02:00</t>
   </si>
   <si>
-    <t>Patrik</t>
+    <t>2026-06-07T21:46:34.705+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T22:08:34.021+02:00</t>
+    <t>[{"id":"8a4618993c6f7ee5917bb6ac","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"84e4b48cb1bf1b04bc7feb09","count":1,"label":"Smetanový základ","posId":"ZRS32","price":0,"isExtra":true},{"id":"ca100378d5704fe4b05cd7db","count":1,"label":"Aquilla zelený čaj/citron","posId":"N121","price":4900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-06-01T22:17:00.974+02:00</t>
+    <t>2026-06-07T21:37:25.753+02:00</t>
   </si>
   <si>
-    <t>[{"id":"109","note":"","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":29900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+    <t>2026-06-07T21:39:20.317+02:00</t>
   </si>
   <si>
-    <t>Anicka Vopatova</t>
+    <t>[{"id":"SblDElWgYWbkoUl-URfQe","count":1,"label":"Poděbradská malinovka 0,5l","posId":"N129","price":4900,"isExtra":false,"creatorId":"vpZbsDxHBv2udhj-HMaCJ","isPackging":0,"actualLabel":"Poděbradská malinovka 0,5l"}]</t>
   </si>
   <si>
-    <t>2026-06-01T22:08:15.771+02:00</t>
+    <t>Amandeep</t>
   </si>
   <si>
-    <t>2026-06-01T22:19:24.729+02:00</t>
+    <t>2026-06-07T21:32:24.164+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T22:36:12.675+02:00</t>
+    <t>2026-06-07T21:41:35.965+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T22:08:59.271+02:00</t>
+    <t>[{"id":"121","note":"","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"A117","note":"","count":1,"label":"okraj hotdog, hořčice","posId":"A117","price":5700,"isExtra":true},{"id":"B102","note":"","count":1,"label":"Jalapeňos","posId":"B102","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"B130","note":"","count":1,"label":"Grana padano, pecorino, parmazán","posId":"B130","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
   </si>
   <si>
-    <t>[{"id":"65874334","note":"","size":"Margherita 32cm","count":1,"label":"Margherita 32cm","posId":"112","price":21900,"isExtra":false},{"id":"65874393","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"65874480","note":"","count":1,"label":"Kuře","posId":"B114","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+    <t>2026-06-07T21:30:03.426+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:39:24.489+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T22:11:01.696+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:34:01.240+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"bf8dc38b-6c8e-42b6-9da3-3170253a57d4","note":"","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:29:49.762+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:35:36.664+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"x0GVZnJx1AargkKfPiwGh","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false,"creatorId":"eZILysVx3JPug4eU_dY8l","isPackging":0,"actualLabel":"BBQ Meteor 40cm"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:26:46.309+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:29:11.619+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"QvTM0biDDphkG686YLgHj","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false,"creatorId":"pe5JPGMIF7ceUAtoeO-mc","isPackging":0,"actualLabel":"Česnekový dip"},{"id":"QvTM0biDDphkG686YLgHj","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false,"creatorId":"G2keeQjlKOaWL3T98FWDB","isPackging":0,"actualLabel":"Česnekový dip"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:19:05.486+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:29:13.743+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:41:44.732+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:19:05.568+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"d63e9120-8ffe-444c-ba51-6c942a13f4fc","note":"","count":1,"label":"Margherita 40cm","posId":"100","price":26900,"isExtra":false},{"id":"86843148-4e32-4979-bfd6-d7151207f70f","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:18:03.470+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:33:04.099+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"e12521cc-9391-4513-be27-f090014536cf","note":"","count":1,"label":"BBQ Texas 32 cm","posId":"143","price":24900,"isExtra":false},{"id":"68d93a2c-5ce2-44a5-857b-6d579cd1f445","note":"","count":1,"label":"Žampiony","posId":"B105","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"a4efa812-1470-4ea2-a19d-39843abed3be","note":"","count":1,"label":"Comeback 32 cm","posId":"145","price":24900,"isExtra":false},{"id":"68d93a2c-5ce2-44a5-857b-6d579cd1f445","note":"","count":1,"label":"Žampiony","posId":"B105","price":2500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:17:52.422+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:25:58.612+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"8a4618993c6f7ee5917bb6ac","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"9ee1d6724717b6cc0fc41c1b","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:08:29.502+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:12:39.950+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"GtkxIY8m7ME9N7fLIL1mf","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false,"creatorId":"X1QOAUzWeFCCYU9ww6x7J","isPackging":0,"actualLabel":"Pepperoni 40cm 🌶️🌶️"},{"id":"mlKAkZexF06HA66I5Wi46","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false,"creatorId":"jW7uljm6QSPqpZX1pN5jz","isPackging":0,"actualLabel":"Pepperoni 32cm 🌶️🌶️"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:00:15.539+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:05:46.788+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"9259131a4eb3cd567a85680a","count":1,"label":"Buchtičky se šodó","posId":"D12","price":7900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"9658a9f3ed07a1961ed48d65","count":1,"label":"Margherita 18cm","posId":"124","price":11900,"isExtra":false},{"id":"2e7ea11ae7ec33bacee46408","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>Masoud</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:55:29.986+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:04:03.598+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"110","note":"","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"C114","note":"","count":1,"label":"Kuře","posId":"C114","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:54:54.584+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:00:51.436+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199505","note":"","size":"Hawai 18cm","count":1,"label":"Hawai 18cm","posId":"126","price":11900,"isExtra":false},{"id":"55199538","note":"","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true},{"id":"59555722","note":"","count":1,"label":"BBQ základ","posId":"ZRB18","price":0,"isExtra":true},{"id":"57405742","note":"","size":"Pepsi 1l","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>Andrey</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:33:29.906+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:41:41.827+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"M200","note":"","count":1,"label":"Veggie menu Comeback","posId":"M200","price":34900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":3000,"isExtra":true},{"id":"Y122","note":"","count":1,"label":"Hot &amp; Spicy","posId":"Y122","price":0,"isExtra":true},{"id":"P103","note":"","count":1,"label":"pečené brambory","posId":"P103","price":0,"isExtra":true},{"id":"N120","note":"","count":1,"label":"Aquilla černý čaj a broskev","posId":"N120","price":0,"isExtra":true},{"id":"P106","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:13:23.371+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:19:44.209+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"71474d2ff08764e8563178d6","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"c71f71bd04444e93fe083c01","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:02:04.710+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:13:47.590+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:19:42.571+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:02:04.859+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"194f980e-141e-4220-9f1e-0e1e9edc412e","note":"","count":1,"label":"Quattro Formaggi 18cm","posId":"135","price":11900,"isExtra":false},{"id":"1fae666b-4102-4ed0-b317-2a07b21ae279","note":"","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:54:05.921+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:04:31.406+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589464","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59589458","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:54:03.316+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:10:50.162+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:31:56.534+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:54:03.529+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"9579f3b5-1ac6-43ac-b132-28666e0777ec","note":"","count":1,"label":"Sweet Passion 18 cm","posId":"30","price":11900,"isExtra":false},{"id":"10a95fda-50ac-4e8b-a092-eba50264ce8d","note":"","count":1,"label":"Comeback 18cm 🌶️","posId":"133","price":11900,"isExtra":false},{"id":"a214d9a6-262f-4d59-9d6c-8c1bdecc573c","note":"","count":1,"label":"Gorgonzola","posId":"A101","price":2000,"isExtra":true},{"id":"a851d29a-5134-4946-b96f-7df04ca56ce8","note":"","count":2,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false},{"id":"35e045f9-bc36-46e9-8142-6579de78a05b","note":"","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"a3d62a5d-2e1d-48db-874e-d64becff7059","note":"","count":1,"label":"změna na BBQ základ","posId":"a3d62a5d-2e1d-48db-874e-d64becff7059","price":0,"isExtra":true},{"id":"f2ca88ba-7288-4f05-a925-149da2e2137e","note":"","count":1,"label":"okraj hotdog, bbq omáčka","posId":"A119","price":5700,"isExtra":true},{"id":"dba0d6ed-9e38-4f33-8ec2-cc6e2ff8f1a9","note":"","count":1,"label":"Gorgonzola","posId":"B101","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:50:03.736+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:57:41.718+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T20:03:21.621+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:50:03.857+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"8c704055-e242-493d-b754-bb711e5a6c0b","note":"","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:47:51.011+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:47:56.361+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"hq1R5HxeYrJr4Ew-dOjt-","count":1,"label":"Guarana classic","posId":"N142","price":5500,"isExtra":false,"creatorId":"ylryrAFnjeygokdT3PLKR","isPackging":0,"actualLabel":"Guarana classic"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:40:00.291+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:46:58.511+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589463","note":"","size":"Hawai 32cm","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59589456","note":"","size":"Quattro Formaggi 32cm","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:29:03.706+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:40:19.111+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:54:47.133+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:29:03.824+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"d63e9120-8ffe-444c-ba51-6c942a13f4fc","note":"","count":1,"label":"Margherita 40cm","posId":"100","price":26900,"isExtra":false},{"id":"e7501e4e-7b75-458f-8655-4ba5ba9c5990","note":"","count":1,"label":"Jalapeňos dip","posId":"P107","price":2000,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:24:58.826+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:38:28.872+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199516","note":"","size":"Česnekový dip","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199515","note":"","size":"Pepperoni Rolls 🌶️","count":1,"label":"Pepperoni Rolls 🌶️","posId":"P100","price":8900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59589459","note":"","size":"Pepperoni 32cm 🌶️🌶️","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199622","note":"","count":1,"label":"okraj hotdog, bbq omáčka","posId":"A119","price":5700,"isExtra":true},{"id":"55199659","note":"","count":1,"label":"Mozzarella","posId":"B113","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:24:03.709+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:34:28.090+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:47:19.180+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:24:03.873+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"aef5aaf8-2acf-4f20-91be-c8829f11cd0c","note":"","count":1,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false},{"id":"0f32557d-3b00-4445-b026-75e05c963906","note":"","count":1,"label":"Jalapeňos","posId":"C102","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"b3008ec8-24a5-4d30-bf46-9133028be7e4","note":"","count":1,"label":"Margherita 32 cm","posId":"136","price":20900,"isExtra":false},{"id":"38de8e38-e51e-422d-9a89-960ebc505f1b","note":"","count":1,"label":"Šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:21:26.274+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:31:43.936+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"d5f548ecefcfc95cc5941e55","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"c71f71bd04444e93fe083c01","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:13:49.017+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T19:23:39.420+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"284143256f41c905feeed114","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"2967f1730e0f7e46102406af","count":1,"label":"Pepperoni salám","posId":"B109","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"39b4dba259045cb10a80740d","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"987bfd69b1586254c4704730","count":1,"label":"Žampiony","posId":"B105","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"63345f6ebe03a711ce9d952e","count":1,"label":"Slanina","posId":"B108","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"3066e1327dc15df83048b59b","count":1,"label":"Mirinda 1l","posId":"N126","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:47:16.350+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:53:08.829+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199477","note":"","size":"Baby špenát &amp; kuře 40cm","count":1,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"59555725","note":"","count":1,"label":"BBQ základ","posId":"ZSB49","price":0,"isExtra":true},{"id":"55199602","note":"","count":1,"label":"Bez špenátu s česnekem","posId":"X107","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"55199598","note":"","count":1,"label":"Žampiony","posId":"C105","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"55199646","note":"","count":1,"label":"Cibule","posId":"C103","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"55199650","note":"","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:36:14.866+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:46:00.448+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199471","note":"","size":"Quattro Formaggi 40cm","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199581","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"57405744","note":"","size":"Mirinda 1l","count":1,"label":"Mirinda 1l","posId":"N126","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:28:16.759+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:28:26.519+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"hq1R5HxeYrJr4Ew-dOjt-","count":1,"label":"Guarana classic","posId":"N142","price":5500,"isExtra":false,"creatorId":"IZwDArI_q8X7OkdPAFBLy","isPackging":0,"actualLabel":"Guarana classic"},{"id":"hq1R5HxeYrJr4Ew-dOjt-","count":1,"label":"Guarana classic","posId":"N142","price":5500,"isExtra":false,"creatorId":"hH8QxXr_xf9bfX0qrxLSj","isPackging":0,"actualLabel":"Guarana classic"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:21:03.162+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:28:40.444+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:49:19.047+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:21:03.339+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"f59b90ea-5e33-470c-9864-9b5a80873c77","note":"","count":1,"label":"Zeleninová 32 cm","posId":"139","price":24900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>roman</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:15:15.022+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:22:58.639+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"121","note":"","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"A121","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"112","note":"","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"A121","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:10:00.695+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:21:26.820+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589464","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59589460","note":"","size":"BBQ Texas 32cm","count":1,"label":"BBQ Texas 32cm","posId":"119","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57405742","note":"","size":"Pepsi 1l","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false},{"id":"55199516","note":"","size":"Česnekový dip","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199511","note":"","size":"Spicy Wings 🌶️","count":1,"label":"spicy wings 🌶️","posId":"P101","price":11900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:07:04.540+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:20:27.826+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"99710cd8-fa1f-4712-84a8-85da37e18dd0","note":"","count":1,"label":"česnekový chléb","posId":"P104","price":7900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:07:04.529+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:14:18.430+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:26:55.715+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:07:04.653+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"e8f571e6-dd36-42d7-8826-52c90315986b","note":"","count":1,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:59:05.410+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:08:46.106+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"03ade9ce-5d0f-4499-a6a3-340b58ae4468","note":"","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"8c704055-e242-493d-b754-bb711e5a6c0b","note":"","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"211d85d0-839e-41d0-89e3-ea177ad7489e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:55:28.292+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:06:38.685+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"8a4618993c6f7ee5917bb6ac","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"730ed795f7d83f1d26b843e5","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"216519e2411a0b808e5e66a5","count":1,"label":"Šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"26d130ce3ef2dd539f98fc3d","count":1,"label":"BBQ Meteor 32cm","posId":"118","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"2c0f597d3afb8c80df48f8ff","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:53:55.157+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:12:06.662+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199473","note":"bez sýru","size":"Comeback 40cm 🌶️","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"59555723","note":"","count":1,"label":"BBQ základ","posId":"ZRB40","price":0,"isExtra":true},{"id":"55199641","note":"","count":1,"label":"okraj hotdog, bez omáčky","posId":"A126","price":6500,"isExtra":true},{"id":"55199561","note":"","count":1,"label":"Bez mozzarelly","posId":"X113","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:52:04.697+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:00:19.538+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T18:04:37.319+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:52:04.821+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"35e045f9-bc36-46e9-8142-6579de78a05b","note":"","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:32:20.464+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:33:45.234+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"Ikpant5VvldJA1UskSxb0","count":1,"label":"Aquilla neperlivá","posId":"N140","price":3900,"isExtra":false,"creatorId":"5D6o731w5PSk_PfFb6z6h","isPackging":0,"actualLabel":"Aquilla neperlivá"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:31:16.273+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:44:32.621+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199476","note":"","size":"BBQ Meteor 40cm","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199624","note":"","count":1,"label":"okraj hotdog, bbq omáčka","posId":"A120","price":6500,"isExtra":true},{"id":"55199476","note":"","size":"BBQ Meteor 40cm","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199581","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:28:56.100+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:39:41.378+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589458","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199618","note":"","count":1,"label":"okraj hotdog, hořčice","posId":"A117","price":5700,"isExtra":true},{"id":"55199568","note":"","count":1,"label":"Jalapeňos","posId":"B102","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"59589464","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:16:42.678+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:23:16.625+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:12:19.473+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:20:59.234+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"QDGxk82t0Xcdbfj8t1zuF","count":1,"label":"Hawai 18cm","posId":"126","price":11900,"isExtra":false,"creatorId":"EwaSuMYYhDW9iK27VTLMf","isPackging":0,"actualLabel":"Hawai 18cm"},{"id":"GgFxWsVrDTHtwOEvP84Ga","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false,"creatorId":"VxONQbtpfTIFMX56I8gqZ","isPackging":0,"actualLabel":"Comeback 32cm 🌶️"}]</t>
+  </si>
+  <si>
+    <t>Berat</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:47:58.449+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:56:56.995+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"110","note":"","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:11:04.365+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:21:40.196+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589459","note":"","size":"Pepperoni 32cm 🌶️🌶️","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199648","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"59589464","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"66679176","note":"","size":"Buchtičky se šodó","count":1,"label":"Buchtičky se šodó","posId":"D12","price":7900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:00:04.384+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:15:29.749+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:23:58.943+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:00:04.497+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"1da47ebe-2592-435a-b854-8cbe80b56263","note":"","count":1,"label":"Hawai 32 cm","posId":"138","price":24900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:59:43.708+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:13:30.170+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199474","note":"","size":"Pepperoni 40cm 🌶️🌶️","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199588","note":"","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A124","price":6500,"isExtra":true},{"id":"55199630","note":"","count":1,"label":"Ananas","posId":"C100","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"55199479","note":"","size":"Hawai 40cm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199598","note":"","count":1,"label":"Žampiony","posId":"C105","price":3500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:55:04.031+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:18:08.189+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:32:08.089+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:55:04.176+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"f1315fc0-dfbb-459c-9f31-49d8e60875f4","note":"","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"85242cc7-02be-4e3a-9c6b-27dfd40e286b","note":"","count":1,"label":"Mirinda 1l","posId":"N126","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:40:30.150+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:51:08.274+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"c061cc0f701dc2e4cbeba65a","count":1,"label":"Zeleninová 40cm","posId":"103","price":30900,"isExtra":false},{"id":"c71f71bd04444e93fe083c01","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"49afbc27314671d4560cc7a0","count":1,"label":"Bez žampionů","posId":"X105","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:34:56.213+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:48:43.024+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589458","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199586","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"59589460","note":"","size":"BBQ Texas 32cm","count":1,"label":"BBQ Texas 32cm","posId":"119","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199597","note":"","count":1,"label":"Žampiony","posId":"B105","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"59589456","note":"","size":"Quattro Formaggi 32cm","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59555726","note":"","count":1,"label":"Rajčatový základ","posId":"ZSR32","price":0,"isExtra":true},{"id":"55199595","note":"","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A123","price":5700,"isExtra":true},{"id":"55199644","note":"","count":1,"label":"Cibule","posId":"B103","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"55199648","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"55199679","note":"","count":1,"label":"Pepperoni salám","posId":"B109","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57405744","note":"","size":"Mirinda 1l","count":1,"label":"Mirinda 1l","posId":"N126","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:34:25.816+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:16:40.084+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T16:16:40.133+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:34:25.956+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"Z9IeDGcKqFO_itODmBH5E","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false,"creatorId":"2gN1TxBOwUoVVnocs-FTz","isPackging":0,"actualLabel":"Quattro Formaggi 32cm"},{"id":"Z9IeDGcKqFO_itODmBH5E","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false,"creatorId":"KG5ujNCPgczfzOKJQY-HE","isPackging":0,"actualLabel":"Quattro Formaggi 32cm"},{"id":"tyGJixfGC6L3xZ3KUEHRE","count":1,"label":"Baby Špenát &amp; kuře 32cm","posId":"116","price":24900,"isExtra":false,"creatorId":"mBROhZ_oun9lflJfhqxze","isPackging":0,"actualLabel":"Baby Špenát &amp; kuře 32cm"},{"id":"tyGJixfGC6L3xZ3KUEHRE","count":1,"label":"Baby Špenát &amp; kuře 32cm","posId":"116","price":24900,"isExtra":false,"creatorId":"sd7VggSOESZTTg9HR-Co_","isPackging":0,"actualLabel":"Baby Špenát &amp; kuře 32cm"},{"id":"HzzLcrRniLZHhRMYsKcZq","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false,"creatorId":"CoCcPYsVGZlyMh9XXQ3FO","isPackging":0,"actualLabel":"Margherita 32cm"},{"id":"S2KCJaQ9FrnGd4277ymVD","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false,"creatorId":"CqBlu66Q335RNySJHxA8E","isPackging":0,"actualLabel":"Capricciosa 32cm"}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:28:04.270+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:18:03.574+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T17:21:34.489+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:50:00.067+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:16:42.734+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:29:54.977+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"d4505ea926b82b0e6ddfcf86","count":1,"label":"Comeback 18cm 🌶️","posId":"133","price":11900,"isExtra":false},{"id":"2e7ea11ae7ec33bacee46408","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true},{"id":"2b1b2b796dd56ca27ebdb9dc","count":1,"label":"Smetanový základ","posId":"ZRS18","price":0,"isExtra":true},{"id":"71a763e559139e5b5e188a91","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"c71f71bd04444e93fe083c01","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"6d30c23536beeaabedce6a33","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"702a37cee92bef60b73e18f1","count":1,"label":"BBQ dip","posId":"P105","price":2000,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:11:35.712+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:24:44.943+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"a0605005773056fb46785f92","count":1,"label":"BBQ Texas 40cm","posId":"107","price":30900,"isExtra":false},{"id":"c71f71bd04444e93fe083c01","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"b0909d075aa821e62b5225d6","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:10:33.809+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:22:52.059+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"d5f548ecefcfc95cc5941e55","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"c71f71bd04444e93fe083c01","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"93e138c9d50686bfde197ff4","count":1,"label":"Jalapeňos","posId":"C102","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"836af884a629f619414811e5","count":1,"label":"Paprika","posId":"C111","price":3500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:10:03.372+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:32:34.076+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:53:48.550+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:10:04.430+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"aef5aaf8-2acf-4f20-91be-c8829f11cd0c","note":"","count":1,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:53:15.099+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:06:08.945+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"c4cf500880b17d3ffa827758","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:48:10.529+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:56:27.856+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"1d215296a99939a8f5b4c23d","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"4f453a9a502066523bdfdc6b","count":1,"label":"Cibule","posId":"B103","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"2967f1730e0f7e46102406af","count":1,"label":"Pepperoni salám","posId":"B109","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"0d95a3384b070d9133ab82f7","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:45:03.244+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:04:15.916+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:14:17.154+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:45:03.353+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"f1315fc0-dfbb-459c-9f31-49d8e60875f4","note":"","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"a3d62a5d-2e1d-48db-874e-d64becff7059","note":"","count":1,"label":"změna na BBQ základ","posId":"a3d62a5d-2e1d-48db-874e-d64becff7059","price":0,"isExtra":true},{"id":"7bf5fb6e-17f1-4e62-b7d1-e31d7c483eb9","note":"","count":1,"label":"Cibule","posId":"B103","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:44:02.824+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:01:34.761+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T15:26:10.410+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:44:02.960+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:30:04.361+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:40:03.698+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"71a763e559139e5b5e188a91","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"c71f71bd04444e93fe083c01","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:02:31.043+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:18:05.542+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589457","note":"","size":"Hot &amp; Spicy 32cm 🌶️🌶️","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199568","note":"","count":1,"label":"Jalapeňos","posId":"B102","price":2500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:56:56.253+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:15:26.571+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199479","note":"","size":"Hawai 40cm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199588","note":"","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A124","price":6500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:56:39.058+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:12:06.178+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199473","note":"","size":"Comeback 40cm 🌶️","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"59555716","note":"","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"55199598","note":"","count":1,"label":"Žampiony","posId":"C105","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57405743","note":"","size":"Pepsi zero sugar 1l","count":1,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:33:04.063+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:55:44.454+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:09:49.180+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:34:07.199+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"03dae282-4cd4-4fa2-9169-2178ea3ed325","note":"","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:29:29.867+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:39:07.423+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"60d80526b1f980b09936a566","count":1,"label":"masové kuličky","posId":"P102","price":9900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"d4505ea926b82b0e6ddfcf86","count":1,"label":"Comeback 18cm 🌶️","posId":"133","price":11900,"isExtra":false},{"id":"2e7ea11ae7ec33bacee46408","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>Arvind</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:22:39.375+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:29:22.485+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"122","note":"","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:17:02.770+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:20:06.467+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:29:41.196+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:17:02.889+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"85dc195f-7d7b-4fb5-b41d-eb1c9c76b3a3","note":"","count":1,"label":"Hot &amp; Spicy 32 cm","posId":"146","price":24900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:12:03.561+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:18:01.181+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:00:39.608+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:12:03.679+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"0b867b16-3995-4b4a-9deb-1c0d8cecf8d6","note":"","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"d1e9623b-89c9-4caa-a2ba-cbaafad1a883","note":"","count":1,"label":"Slanina","posId":"B108","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>Aider</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:09:25.143+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:23:56.605+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"106","note":"","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZBR40","note":"","count":1,"label":"Rajčatový základ","posId":"ZBR40","price":0,"isExtra":true},{"id":"111","note":"","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZSR40","note":"","count":1,"label":"Rajčatový základ","posId":"ZSR40","price":0,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:08:14.070+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:15:30.910+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199473","note":"","size":"Comeback 40cm 🌶️","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57405744","note":"","size":"Mirinda 1l","count":1,"label":"Mirinda 1l","posId":"N126","price":5900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:01:36.790+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:13:34.883+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"10aff56d4ce1949bc6696131","count":1,"label":"BBQ Texas 18cm","posId":"131","price":11900,"isExtra":false},{"id":"2e7ea11ae7ec33bacee46408","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true},{"id":"55089be55592a3a2fa77668d","count":1,"label":"Jalapenos Rolls","posId":"jpr200","price":8900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:01:02.616+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:10:48.023+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:34:49.595+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:01:02.726+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"f1315fc0-dfbb-459c-9f31-49d8e60875f4","note":"","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"a3d62a5d-2e1d-48db-874e-d64becff7059","note":"","count":1,"label":"změna na BBQ základ","posId":"a3d62a5d-2e1d-48db-874e-d64becff7059","price":0,"isExtra":true},{"id":"211d85d0-839e-41d0-89e3-ea177ad7489e","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"36ea3088-07fd-428f-b871-c4a5ee9cef7b","note":"","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:59:03.528+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:05:16.031+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:50:41.597+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:59:03.648+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"03ade9ce-5d0f-4499-a6a3-340b58ae4468","note":"","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"6e9ef16b-b5cb-40a1-ad72-f28a9276a0f7","note":"","count":1,"label":"Kuře","posId":"B114","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"bd8e2f82-3d11-4ada-88ad-67191c012d18","note":"","count":1,"label":"Bez oliv","posId":"X112","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":2,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:42:18.997+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:00:45.221+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199470","note":"","size":"Margherita 40cm","count":1,"label":"Margherita 40cm","posId":"100","price":26900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199474","note":"","size":"Pepperoni 40cm 🌶️🌶️","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:37:03.356+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:56:26.865+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:02:29.204+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:37:03.661+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"1fae666b-4102-4ed0-b317-2a07b21ae279","note":"","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"35e045f9-bc36-46e9-8142-6579de78a05b","note":"","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"cf590a42-3894-4cb1-9be7-6da354b8453d","note":"","count":1,"label":"Olivy","posId":"B112","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"03ade9ce-5d0f-4499-a6a3-340b58ae4468","note":"","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"03ade9ce-5d0f-4499-a6a3-340b58ae4468","note":"","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:25:45.115+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:47:04.563+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"9259131a4eb3cd567a85680a","count":1,"label":"Buchtičky se šodó","posId":"D12","price":7900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"b81e501c3bc4e8173dde4771","count":1,"label":"Quattro Formaggi 18cm","posId":"135","price":11900,"isExtra":false},{"id":"2e7ea11ae7ec33bacee46408","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true},{"id":"d4505ea926b82b0e6ddfcf86","count":1,"label":"Comeback 18cm 🌶️","posId":"133","price":11900,"isExtra":false},{"id":"2e7ea11ae7ec33bacee46408","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true},{"id":"2b1b2b796dd56ca27ebdb9dc","count":1,"label":"Smetanový základ","posId":"ZRS18","price":0,"isExtra":true},{"id":"15d48fba0016db7394ccdeab","count":1,"label":"Bez cibule","posId":"X103","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:21:39.694+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:43:09.218+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"59589461","note":"","size":"BBQ Meteor 32cm","count":1,"label":"BBQ Meteor 32cm","posId":"118","price":24900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199614","note":"","count":1,"label":"Bez masových kuliček","posId":"X116","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"55199497","note":"","size":"Quattro Formaggi 18cm","count":1,"label":"Quattro Formaggi 18cm","posId":"135","price":11900,"isExtra":false},{"id":"55199538","note":"","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true},{"id":"55199512","note":"","size":"Masové kuličky","count":1,"label":"masové kuličky","posId":"P102","price":9900,"isExtra":false},{"id":"55199562","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57405746","note":"","size":"Poděbradská malinovka 0,5l","count":2,"label":"Poděbradská malinovka 0,5l","posId":"N129","price":4900,"isExtra":false}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:21:13.599+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:38:44.023+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"d0043b053c4bd7c6fd8359d7","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59839d6b839f5e8fe6d29556","count":1,"label":"BBQ základ","posId":"ZRB32","price":0,"isExtra":true},{"id":"0d95a3384b070d9133ab82f7","count":2,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"8a4618993c6f7ee5917bb6ac","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:00:43.944+02:00</t>
+  </si>
+  <si>
+    <t>2026-06-07T12:31:12.128+02:00</t>
+  </si>
+  <si>
+    <t>[{"id":"55199473","note":"","size":"Comeback 40cm 🌶️","count":3,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"55199557","note":"","count":3,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199475","note":"","size":"BBQ Texas 40cm","count":3,"label":"BBQ Texas 40cm","posId":"107","price":30900,"isExtra":false},{"id":"55199557","note":"","count":3,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199471","note":"","size":"Quattro Formaggi 40cm","count":2,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"55199557","note":"","count":2,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199477","note":"","size":"Baby špenát &amp; kuře 40cm","count":2,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false},{"id":"55199557","note":"","count":2,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199476","note":"","size":"BBQ Meteor 40cm","count":3,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"55199557","note":"","count":3,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199480","note":"","size":"Capricciosa 40cm","count":2,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false},{"id":"55199557","note":"","count":2,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199511","note":"","size":"Spicy Wings 🌶️","count":3,"label":"spicy wings 🌶️","posId":"P101","price":11900,"isExtra":false},{"id":"55199562","note":"","count":3,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"55199512","note":"","size":"Masové kuličky","count":3,"label":"masové kuličky","posId":"P102","price":9900,"isExtra":false},{"id":"55199562","note":"","count":3,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
   </si>
   <si>
     <t>card</t>
   </si>
   <si>
-    <t>2026-06-01T21:49:04.180+02:00</t>
+    <t>2026-06-07T11:52:04.090+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T21:57:17.527+02:00</t>
+    <t>2026-06-07T11:59:02.834+02:00</t>
   </si>
   <si>
-    <t>[{"id":"ff8bc446-e047-44f1-bae5-423b565e0123","note":"","count":1,"label":"Capricciosa 32 cm","posId":"137","price":25900,"isExtra":false}]</t>
+    <t>[{"id":"1fae666b-4102-4ed0-b317-2a07b21ae279","note":"","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-06-01T21:23:42.262+02:00</t>
+    <t>2026-06-07T11:43:10.826+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T21:31:59.591+02:00</t>
+    <t>2026-06-07T11:55:40.604+02:00</t>
   </si>
   <si>
-    <t>[{"id":"6893484371e1a7827faa284a","count":1,"label":"BBQ Texas 32cm","posId":"119","price":22900,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>[{"id":"55199470","note":"","size":"Margherita 40cm","count":1,"label":"Margherita 40cm","posId":"100","price":26900,"isExtra":false},{"id":"55199557","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"55199641","note":"","count":1,"label":"okraj hotdog, bez omáčky","posId":"A126","price":6500,"isExtra":true},{"id":"55199662","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"55199505","note":"","size":"Hawai 18cm","count":1,"label":"Hawai 18cm","posId":"126","price":11900,"isExtra":false},{"id":"55199538","note":"","count":1,"label":"Balné","posId":"K0000","price":1000,"isExtra":true}]</t>
   </si>
   <si>
-    <t>2026-06-01T21:09:06.490+02:00</t>
+    <t>2026-06-07T11:33:48.545+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T21:20:38.695+02:00</t>
+    <t>2026-06-07T11:49:33.829+02:00</t>
   </si>
   <si>
-    <t>[{"id":"6893484371e1a7827faa2842","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":22900,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"aa7adefdbb9acf83a80d5243","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5900,"isExtra":true},{"id":"a756491743f5851faee7839c","count":1,"label":"Slanina","posId":"B108","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"8cfd349c9dc7f129d0cfd899","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>[{"id":"c8f41becd43979fe4250d2db","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59839d6b839f5e8fe6d29556","count":1,"label":"BBQ základ","posId":"ZRB32","price":0,"isExtra":true},{"id":"f6175eba1d6d031652a811c1","count":1,"label":"Bez cibule","posId":"X103","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"987bfd69b1586254c4704730","count":1,"label":"Žampiony","posId":"B105","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"730ed795f7d83f1d26b843e5","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"987b55ede997ad09176f3fbf","count":1,"label":"Mozzarella","posId":"B113","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"1d215296a99939a8f5b4c23d","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"84e4b48cb1bf1b04bc7feb09","count":1,"label":"Smetanový základ","posId":"ZRS32","price":0,"isExtra":true},{"id":"b0909d075aa821e62b5225d6","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false},{"id":"0d95a3384b070d9133ab82f7","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"ed2821f5147c44e417ef0b42","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
   </si>
   <si>
-    <t>2026-06-01T20:26:42.111+02:00</t>
+    <t>2026-06-07T11:32:40.048+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T20:35:21.408+02:00</t>
+    <t>2026-06-07T11:45:34.692+02:00</t>
   </si>
   <si>
-    <t>F - Pizza Comeback Bolevec</t>
+    <t>2026-06-07T11:53:12.210+02:00</t>
   </si>
   <si>
-    <t>[{"id":"62240188","note":"","size":"Quattro Formaggi 40cm","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":29900,"isExtra":false},{"id":"62240274","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"62240362","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+    <t>2026-06-07T11:32:40.200+02:00</t>
   </si>
   <si>
-    <t>2026-06-01T20:16:59.261+02:00</t>
+    <t>[{"id":"MWBjWTigaawF2pc4_uJCm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false,"creatorId":"11U23mx8vDIR7K2HCvqX7","isPackging":0,"actualLabel":"Hawai 40cm"},{"id":"MWBjWTigaawF2pc4_uJCm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false,"creatorId":"LEJYK8KCzMFWuIj81u5It","isPackging":0,"actualLabel":"Hawai 40cm"}]</t>
   </si>
   <si>
-    <t>2026-06-01T20:25:46.414+02:00</t>
+    <t>2026-06-07T11:12:03.364+02:00</t>
   </si>
   <si>
-    <t>[{"id":"6893484371e1a7827faa2830","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":29900,"isExtra":false},{"id":"8492ff01857ad344daba3d10","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"0866c7a48369c02d8b79a2fc","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6900,"isExtra":true}]</t>
+    <t>2026-06-07T11:41:35.559+02:00</t>
   </si>
   <si>
-    <t>manual</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:48:07.395+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:59:04.430+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T20:10:44.600+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:56:51.398+02:00</t>
-  </si>
-  <si>
-    <t>Ručně zadané obj.</t>
-  </si>
-  <si>
-    <t>[{"id":"de6753a1-e94f-40c8-bbad-ed722dabae53","count":1,"label":"Pizza Quattro Formaggi 40 0,5","posId":"H111","price":16450,"isExtra":false,"creatorId":"WfcD7uV1_l6Mr3CZAo8GO","actualLabel":"Pizza Quattro Formaggi 40 0,5"},{"id":"2lwz8DLnxAE2XXPjpySDo","count":1,"label":"Bez plněných okrajů","posId":"X1000","price":0,"isExtra":true,"mainItemId":"de6753a1-e94f-40c8-bbad-ed722dabae53"},{"id":"2eddb0dc-c598-4c27-9c40-e1df24127c19","count":1,"label":"Pizza Comeback 40 0,5","posId":"H109","price":16450,"isExtra":false,"creatorId":"HustfT3X5aF3oZ8S1Fmy4","actualLabel":"Pizza Comeback 40 0,5"},{"id":"2lwz8DLnxAE2XXPjpySDo","count":1,"label":"Bez plněných okrajů","posId":"X1000","price":0,"isExtra":true,"mainItemId":"2eddb0dc-c598-4c27-9c40-e1df24127c19"}]</t>
-  </si>
-  <si>
-    <t>ready_pickup</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:34:35.683+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:50:25.369+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240194","note":"","size":"Baby špenát &amp; kuře 40cm","count":1,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":29900,"isExtra":false},{"id":"62240274","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"62240411","note":"","count":1,"label":"Rajčatový základ","posId":"ZSR40","price":0,"isExtra":true},{"id":"62240197","note":"","size":"Capricciosa 40cm","count":1,"label":"Capricciosa 40cm","posId":"101","price":29900,"isExtra":false},{"id":"62240274","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"62240408","note":"","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:32:15.355+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:41:07.221+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240202","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:30:11.547+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T22:05:09.718+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T22:05:09.717+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"e81d1eac-78b4-4c74-9c7f-c9c1a65dccf2","count":1,"label":"Pizza Capricciosa 32","posId":"113","price":25900,"isExtra":false,"creatorId":"knWdmwagu7k83fcDb-O4H","isPackging":0,"actualLabel":"Pizza Capricciosa 32"},{"id":"2cffc280-164c-4c9f-aaee-66502dfa73f2","count":1,"label":"Pizza Špenát kuře 32 cm","posId":"116","price":25900,"isExtra":false,"creatorId":"W_IvJ--zi70_Dy4nA16qP","isPackging":0,"actualLabel":"Pizza Špenát kuře 32 cm"},{"id":"0b0f19cf-0e7b-4ef5-abad-53a9439da195","count":1,"label":"Pizza Hot &amp; Spicy 32","posId":"122","price":25900,"isExtra":false,"creatorId":"IRnPT9S-2gXVyUsl_OX_c","isPackging":0,"actualLabel":"Pizza Hot &amp; Spicy 32"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:56:41.654+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T19:06:10.405+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"6893484371e1a7827faa283a","count":1,"label":"Capricciosa 40cm","posId":"101","price":29900,"isExtra":false},{"id":"8492ff01857ad344daba3d10","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:49:03.691+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:57:23.809+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32 cm","posId":"112","price":21900,"isExtra":false},{"id":"38de8e38-e51e-422d-9a89-960ebc505f1b","note":"","count":1,"label":"šunka","posId":"38de8e38-e51e-422d-9a89-960ebc505f1b","price":3000,"isExtra":true},{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32 cm","posId":"112","price":21900,"isExtra":false},{"id":"38de8e38-e51e-422d-9a89-960ebc505f1b","note":"","count":1,"label":"šunka","posId":"38de8e38-e51e-422d-9a89-960ebc505f1b","price":3000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:46:19.781+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:53:41.209+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:30:03.660+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:46:44.851+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:59:48.809+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:31:19.920+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"0ea52415-fdb3-497f-b216-7fd5802f2e0f","note":"","count":1,"label":"Quattro Formaggi 32 cm","posId":"123","price":25900,"isExtra":false},{"id":"4cd25cb7-e092-43a0-ab38-89c50a7e6a77","note":"","count":1,"label":"Pepperoni 18 cm","posId":"132","price":13900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:19:44.645+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:54:00.037+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"e81d1eac-78b4-4c74-9c7f-c9c1a65dccf2","count":1,"label":"Pizza Capricciosa 32","posId":"113","price":25900,"isExtra":false,"creatorId":"lvFAj9lLODHOEuoViAw_c","isPackging":0,"actualLabel":"Pizza Capricciosa 32"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:18:43.215+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:31:14.986+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240200","note":"","size":"Quattro Formaggi 32cm","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"62240202","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"62240208","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:06:41.717+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:19:01.527+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240208","note":"","size":"Capricciosa 32cm","count":2,"label":"Capricciosa 32cm","posId":"113","price":22900,"isExtra":false},{"id":"62240278","note":"","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"62240202","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"62240203","note":"","size":"Pepperoni 32cm 🌶️🌶️","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T17:54:02.834+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T18:01:59.851+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"6893484371e1a7827faa283a","count":1,"label":"Capricciosa 40cm","posId":"101","price":29900,"isExtra":false},{"id":"8492ff01857ad344daba3d10","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"74f85d724d56daef88fe96a8","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"31520cbf5ed975b91e6c5722","count":1,"label":"Bez oliv","posId":"X112","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T17:45:15.149+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T17:52:05.953+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"428e1c0b-4234-4b06-b060-02a3a194dbbd","count":1,"label":"Pizza Quattro Formaggi 18","posId":"135","price":13900,"isExtra":false,"creatorId":"c8ps7koshNw6a8_djy29A","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 18"},{"id":"KHkqvH4nrpVi3rmWB6xsU","count":1,"label":"Bez gorgonzoly","posId":"X101","price":0,"KDSTags":["redhighlight"],"isExtra":true,"mainItemId":"428e1c0b-4234-4b06-b060-02a3a194dbbd"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T17:44:28.271+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T17:59:55.973+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T16:08:04.402+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T17:08:21.288+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"aef5aaf8-2acf-4f20-91be-c8829f11cd0c","note":"","count":2,"label":"Capricciosa 40 cm","posId":"101","price":32900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T15:49:55.173+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T15:53:11.346+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"88ea58e5-5aed-4c56-80f0-bcc6b35440d3","count":1,"label":"Espresso Lungo","posId":"N156","price":5500,"isExtra":false,"creatorId":"6Sx98IcfVaumQAEBat12w","isPackging":0,"actualLabel":"Espresso Lungo"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T15:27:40.885+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T15:36:34.241+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240189","note":"","size":"Hot &amp; Spicy 40cm 🌶️🌶️","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":29900,"isExtra":false},{"id":"62240274","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>Dmytro</t>
-  </si>
-  <si>
-    <t>2026-06-01T14:54:26.328+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T15:10:27.646+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"103","note":"","count":1,"label":"Zeleninová 40cm","posId":"103","price":29900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"A118","note":"","count":1,"label":"okraj hotdog, hořčice","posId":"A118","price":6900,"isExtra":true},{"id":"C106","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"C108","note":"","count":1,"label":"Slanina","posId":"C108","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"P106","note":"","count":2,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"K0000","note":"","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"106","note":"","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":29900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"chr100","note":"","count":1,"label":"Choco Rolls","posId":"chr100","price":7900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"18","note":"","count":1,"label":"Jablečno-skořicové rolls","posId":"18","price":7900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T14:41:15.685+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T14:51:50.195+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"6893484371e1a7827faa2848","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":22900,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T14:02:21.728+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T15:22:50.159+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"8bba451a-3c5e-4c20-9575-e5341c254b5e","count":1,"label":"Pizza Quattro Formaggi 32 0,5","posId":"H123","price":12950,"isExtra":false,"creatorId":"2zEdIn-c5Q58yAXty6c9j","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 32 0,5"},{"id":"ZMn0kE3IRVJjsfXstBxZb","count":1,"label":"Bez plněných okrajů","posId":"X1000","price":0,"isExtra":true,"mainItemId":"8bba451a-3c5e-4c20-9575-e5341c254b5e"},{"id":"aRPAiqbCW3Z9trz5KoEBF","count":1,"label":"Těsto italské","posId":"H32","price":0,"isExtra":true,"mainItemId":"8bba451a-3c5e-4c20-9575-e5341c254b5e"},{"id":"dd64d382-320f-41bf-9f06-cbddc81362f7","count":1,"label":"Pizza Hawai 32 cm 0,5","posId":"H114","price":12950,"isExtra":false,"creatorId":"DWb84lZlCEHR3iSnulBFi","isPackging":0,"actualLabel":"Pizza Hawai 32 cm 0,5"},{"id":"RjnzJvFGQ7bViwxWS8fAW","count":1,"label":"Bez ananasu","posId":"X100","price":0,"KDSTags":["redhighlight"],"isExtra":true,"mainItemId":"dd64d382-320f-41bf-9f06-cbddc81362f7"},{"id":"ZMn0kE3IRVJjsfXstBxZb","count":1,"label":"Bez plněných okrajů","posId":"X1000","price":0,"isExtra":true,"mainItemId":"dd64d382-320f-41bf-9f06-cbddc81362f7"},{"id":"aRPAiqbCW3Z9trz5KoEBF","count":1,"label":"Těsto italské","posId":"H32","price":0,"isExtra":true,"mainItemId":"dd64d382-320f-41bf-9f06-cbddc81362f7"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T14:00:41.752+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T15:22:51.238+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"1e8d27fe-5059-4d3c-a717-e6037379688e","count":1,"label":"Pizza Quattro Formaggi 40","posId":"111","price":32900,"isExtra":false,"creatorId":"va9T7O6Ujw6UYVUM66kTe","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 40"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T13:58:31.144+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T14:18:20.347+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"700d2e35b664c3f71c5dfa78","count":2,"label":"Buchtičky se šodó","posId":"D12","price":8900,"isExtra":false},{"id":"0cf732abf15d68df108984b2","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T13:20:50.305+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T13:29:39.389+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"38fbf306-1585-4d67-9b87-6d5b39f05c8f","count":1,"label":"Pizza BBQ Texas 32","posId":"119","price":25900,"isExtra":false,"creatorId":"U4gJdD4BRgDmSlg40dQV5","isPackging":0,"actualLabel":"Pizza BBQ Texas 32"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T13:18:24.991+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T13:24:38.442+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240200","note":"","size":"Quattro Formaggi 32cm","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"62240418","note":"","count":1,"label":"Rajčatový základ","posId":"ZSR32","price":0,"isExtra":true},{"id":"62240230","note":"","size":"Česnekový dip","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:55:21.908+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:56:11.089+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"6893484371e1a7827faa28a6","count":2,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:38:28.087+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:46:40.791+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240187","note":"Bez dipu prosím 🙏","size":"Margherita 40cm","count":1,"label":"Margherita 40cm","posId":"100","price":24900,"isExtra":false},{"id":"62240274","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:11:03.717+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:18:36.475+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"f1315fc0-dfbb-459c-9f31-49d8e60875f4","note":"","count":1,"label":"Pepperoni 40 cm","posId":"108","price":32900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"Okraj mozzarella, bylinky","posId":"eb426525-9181-4714-9963-380f5c0ae0e5","price":6900,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:09:39.027+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T12:09:49.799+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"8e14a535-5628-4959-9da1-d7350a200486","count":1,"label":"Pizza Margherita 32","posId":"112","price":21900,"isExtra":false,"discount":{"type":"percentage","value":20},"creatorId":"MVCfbLVatps7GR9K9ODQy","isPackging":0,"actualLabel":"Pizza Margherita 32"}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T11:49:27.615+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T11:58:20.777+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"62240203","note":"","size":"Pepperoni 32cm 🌶️🌶️","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":22900,"isExtra":false},{"id":"62240278","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-06-01T10:58:53.808+02:00</t>
-  </si>
-  <si>
-    <t>2026-06-01T11:30:37.251+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"f2e47a9a-9a83-4636-a9a7-f3b2d38f2cc5","count":1,"label":"Pečené brambory","posId":"P103","price":6900,"isExtra":false,"creatorId":"aIR7IaHXKgZ-trqUJSEN5","isPackging":0,"actualLabel":"Pečené brambory"},{"id":"57d9f91b-11d2-479b-bfd0-7e570ba5d2e6","count":1,"label":"Spicy Wings","posId":"P101","price":12900,"isExtra":false,"creatorId":"UMrhedhkV8rz67nELEOdq","isPackging":0,"actualLabel":"Spicy Wings"}]</t>
+    <t>[{"id":"bf8dc38b-6c8e-42b6-9da3-3170253a57d4","note":"","count":1,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"117c830b-d7db-490d-a3b9-365f8c4fa2d3","note":"","count":1,"label":"Zeleninová 32cm","posId":"115","price":24900,"isExtra":false},{"id":"ee394832-8137-440a-84b7-b9e0df42a9ab","note":"","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false}]</t>
   </si>
   <si>
     <t>Název</t>
@@ -812,6 +1457,9 @@
     <t>Ahurieva Viktoriia</t>
   </si>
   <si>
+    <t>01:00</t>
+  </si>
+  <si>
     <t>12:00</t>
   </si>
   <si>
@@ -827,16 +1475,10 @@
     <t>Zbyněk Hyský</t>
   </si>
   <si>
-    <t>00:00</t>
-  </si>
-  <si>
     <t>06:00</t>
   </si>
   <si>
     <t>Pešová Hana</t>
-  </si>
-  <si>
-    <t>17:00</t>
   </si>
   <si>
     <t>08:00</t>
@@ -2734,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46174.0</v>
+        <v>46180.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -2759,13 +3401,13 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),0.4622972088058687)</f>
-        <v>0.4622972088</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),0.2480610557250065)</f>
+        <v>0.2480610557</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="16">
         <f>SUM(RestiaCSV!C:C) - SUMIFS(RestiaCSV!C:C, RestiaCSV!B:B, "canceled")</f>
-        <v>14437.19</v>
+        <v>47952.26</v>
       </c>
       <c r="K2" s="15"/>
       <c r="L2" s="17" t="s">
@@ -2773,14 +3415,14 @@
       </c>
       <c r="M2" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, Report!L2, RestiaCSV!B:B, "&lt;&gt;canceled")</f>
-        <v>3449</v>
+        <v>8223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" s="19" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pondělí</v>
+        <v>Neděle</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2792,7 +3434,7 @@
       </c>
       <c r="M3" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, Report!L3, RestiaCSV!B:B, "&lt;&gt;canceled")</f>
-        <v>2200</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="4">
@@ -2812,7 +3454,7 @@
       </c>
       <c r="M4" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, "damejidlo", RestiaCSV!G:G, "online", RestiaCSV!B:B, "&lt;&gt;canceled")</f>
-        <v>3302.59</v>
+        <v>17242.36</v>
       </c>
     </row>
     <row r="5">
@@ -2834,7 +3476,7 @@
       </c>
       <c r="M5" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, "generic", RestiaCSV!G:G, "online", RestiaCSV!B:B, "&lt;&gt;canceled") </f>
-        <v>1372</v>
+        <v>8916</v>
       </c>
     </row>
     <row r="6">
@@ -2854,7 +3496,7 @@
       </c>
       <c r="M6" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!E:E, "wolt kurýr", RestiaCSV!A:A, "&lt;&gt;wolt", RestiaCSV!G:G, "cash", RestiaCSV!B:B, "&lt;&gt;canceled")</f>
-        <v>0</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7">
@@ -2871,7 +3513,7 @@
       </c>
       <c r="M7" s="28">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, "damejidlo", RestiaCSV!G:G, "cash", RestiaCSV!B:B, "&lt;&gt;canceled") </f>
-        <v>513</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="8">
@@ -2901,7 +3543,7 @@
         <v>13</v>
       </c>
       <c r="M9" s="31">
-        <v>1157.0</v>
+        <v>2397.0</v>
       </c>
     </row>
     <row r="10">
@@ -2941,18 +3583,20 @@
       <c r="F11" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="39"/>
+      <c r="G11" s="39" t="s">
+        <v>23</v>
+      </c>
       <c r="I11" s="15"/>
       <c r="J11" s="40">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="41" t="s">
         <v>12</v>
       </c>
       <c r="M11" s="31">
-        <v>702.0</v>
+        <v>6163.0</v>
       </c>
     </row>
     <row r="12">
@@ -2973,7 +3617,7 @@
       <c r="F12" s="46" t="str">
         <f t="shared" ref="F12:F21" si="1">IF(OR(ISBLANK(B12), ISBLANK(D12), D12=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))+1, TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))) - TIMEVALUE(IF(ISBLANK(C12), "00:00", C12)) - TIMEVALUE(IF(ISBLANK(E12), "00:00", E12))), "hh:mm"))
 </f>
-        <v>15:00</v>
+        <v>07:00</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="29"/>
@@ -2986,15 +3630,21 @@
     <row r="13">
       <c r="A13" s="42">
         <f t="array" ref="A13">IF(ISBLANK(B13), 0, IF(ISNUMBER(MATCH(B13, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B13, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B13, HR!B:B, 0)) * (F13 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
+        <v>1873.2</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>28</v>
+      </c>
       <c r="E13" s="49"/>
       <c r="F13" s="46" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>07:00</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
@@ -3002,29 +3652,35 @@
       <c r="J13" s="29"/>
       <c r="K13" s="15"/>
       <c r="L13" s="17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M13" s="50"/>
     </row>
     <row r="14">
       <c r="A14" s="42">
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+        <v>1438.6845</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>31</v>
+      </c>
       <c r="E14" s="45"/>
       <c r="F14" s="51" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>05:45</v>
       </c>
       <c r="G14" s="52"/>
       <c r="I14" s="15"/>
       <c r="J14" s="29"/>
       <c r="K14" s="15"/>
       <c r="L14" s="53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M14" s="50"/>
     </row>
@@ -3045,7 +3701,7 @@
       <c r="J15" s="29"/>
       <c r="K15" s="15"/>
       <c r="L15" s="53" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M15" s="50"/>
     </row>
@@ -3066,10 +3722,10 @@
       <c r="J16" s="29"/>
       <c r="K16" s="15"/>
       <c r="L16" s="53" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M16" s="50">
-        <v>2175.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="17">
@@ -3091,11 +3747,11 @@
       <c r="J17" s="12"/>
       <c r="K17" s="13"/>
       <c r="L17" s="57" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M17" s="58">
         <f>SUM(I25:I31)</f>
-        <v>80</v>
+        <v>920</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1">
@@ -3112,7 +3768,7 @@
         <v>0:00</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="13"/>
@@ -3132,7 +3788,9 @@
         <f t="shared" si="1"/>
         <v>0:00</v>
       </c>
-      <c r="G19" s="39"/>
+      <c r="G19" s="39" t="s">
+        <v>27</v>
+      </c>
       <c r="I19" s="15"/>
       <c r="M19" s="62"/>
     </row>
@@ -3181,40 +3839,40 @@
       <c r="H22" s="21"/>
       <c r="I22" s="13"/>
       <c r="J22" s="71" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K22" s="71" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L22" s="72" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M22" s="72" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="69"/>
       <c r="B23" s="32" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="73">
         <f>COUNTIF(RestiaCSV!B:B, "canceled")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="74">
         <f>SUMIF(RestiaCSV!B:B, "canceled", RestiaCSV!C:C)</f>
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="L23" s="75">
         <f>COUNTIFS(RestiaCSV!L:L, "&gt;5", RestiaCSV!F:F, "delivery")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23" s="73" t="str">
         <f>INT(AVERAGE(RestiaCSV!N2:N32)) &amp; " min " &amp; TEXT(MOD(AVERAGE(RestiaCSV!N2:N32) * 60, 60), "00") &amp; " s"
 </f>
-        <v>18 min 53 s</v>
+        <v>12 min 45 s</v>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
@@ -3235,57 +3893,57 @@
         <v>22</v>
       </c>
       <c r="G24" s="76" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H24" s="76" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I24" s="77" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J24" s="78" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K24" s="79" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L24" s="78" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M24" s="79" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="42">
         <f t="array" ref="A25">IF(ISBLANK(B25), 0, IF(ISNUMBER(MATCH(B25, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B25, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B25, HR!B:B, 0)) * (F25 * 24), 0)))</f>
-        <v>2140.8</v>
+        <v>3252.678</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E25" s="80"/>
       <c r="F25" s="46" t="str">
         <f t="shared" ref="F25:F31" si="2">IF(OR(ISBLANK(B25), ISBLANK(D25), D25=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))+1, TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))) - TIMEVALUE(IF(ISBLANK(C25), "00:00", C25)) - TIMEVALUE(IF(ISBLANK(E25), "00:00", E25))), "hh:mm"))
 </f>
-        <v>10:00</v>
+        <v>13:00</v>
       </c>
       <c r="G25" s="81">
         <f>COUNTIF(RestiaCSV!E:E, B25)</f>
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H25" s="82" t="b">
         <v>1</v>
       </c>
       <c r="I25" s="83">
         <f t="shared" ref="I25:I31" si="3">IF(H25,G25*40, 0)</f>
-        <v>80</v>
+        <v>920</v>
       </c>
       <c r="J25" s="84"/>
       <c r="K25" s="84"/>
@@ -3295,29 +3953,21 @@
     <row r="26">
       <c r="A26" s="42">
         <f t="array" ref="A26">IF(ISBLANK(B26), 0, IF(ISNUMBER(MATCH(B26, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B26, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B26, HR!B:B, 0)) * (F26 * 24), 0)))</f>
-        <v>856.32</v>
-      </c>
-      <c r="B26" s="85" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="44" t="s">
-        <v>46</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B26" s="85"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
       <c r="E26" s="86"/>
       <c r="F26" s="46" t="str">
         <f t="shared" si="2"/>
-        <v>04:00</v>
+        <v>0:00</v>
       </c>
       <c r="G26" s="81">
         <f>COUNTIF(RestiaCSV!E:E, B26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="82" t="b">
-        <v>1</v>
-      </c>
+      <c r="H26" s="82"/>
       <c r="I26" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3327,12 +3977,12 @@
         <v>1</v>
       </c>
       <c r="K26" s="75">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(FILTER(RestiaCSV!B2:B32, RestiaCSV!B2:B32 &lt;&gt; ""canceled""))"),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(FILTER(RestiaCSV!B2:B32, RestiaCSV!B2:B32 &lt;&gt; ""canceled""))"),100.0)</f>
+        <v>100</v>
       </c>
       <c r="L26" s="75">
         <f>COUNTIF(RestiaCSV!F1:F32, "delivery")</f>
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="M26" s="89">
         <f>COUNTIF(RestiaCSV!M:M, "&gt;5")</f>
@@ -3362,14 +4012,14 @@
         <v>0</v>
       </c>
       <c r="J27" s="92" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K27" s="93"/>
       <c r="L27" s="94" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M27" s="79" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
@@ -3428,11 +4078,11 @@
       <c r="K29" s="99"/>
       <c r="L29" s="100">
         <f>L23/L26</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M29" s="75">
         <f>COUNTIFS(RestiaCSV!L:L, "&gt;5", RestiaCSV!F:F, "delivery", RestiaCSV!E:E, "Wolt Kurýr")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3460,10 +4110,10 @@
       <c r="J30" s="103"/>
       <c r="K30" s="103"/>
       <c r="L30" s="104" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M30" s="104" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" ht="21.75" customHeight="1">
@@ -3496,34 +4146,34 @@
     <row r="32">
       <c r="A32" s="35"/>
       <c r="B32" s="110" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C32" s="111" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
       <c r="F32" s="112"/>
       <c r="G32" s="113">
         <f>COUNTIFS(RestiaCSV!E:E, "wolt kurýr", RestiaCSV!A:A, "&lt;&gt;wolt")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" s="114" t="b">
         <v>1</v>
       </c>
       <c r="I32" s="115">
         <f>G32*127</f>
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="J32" s="116"/>
       <c r="K32" s="116"/>
       <c r="L32" s="100">
         <f>100%-L29</f>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M32" s="100">
         <f>M29/L26</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -3583,16 +4233,16 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B12:B21">
-      <formula1>"Rothová Anastasia,Roth Stanislav ml.,Raboch Tomáš,Kratochvíl Kryštof,Tůma Vladimír"</formula1>
+      <formula1>"Sova Martin,Ahurieva Viktoriia,Šebesta Tomáš,Coufal Jakub,Hegedüs Erik,Bubník Martin,Berdar Vasyl,Gorol Patrik,Hegedüs Gergö,Barvínková Eliška,Kubík Martin,Kopic Jakub"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B1">
       <formula1>"Bolevec,Malešice,Prosek,Zličín,Libuš,Chodov,Výroba,Předloha"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G11 G19">
-      <formula1>"Sova Martin,Pešová Hana,Židek Petr"</formula1>
+      <formula1>"Roth Stanislav ml."</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B25:B31">
-      <formula1>"Mikešová Adéla,Kaločai Rudolf,Vopatová Anna,Vopatová Šárka,Světlík František,Ženíšek Lukáš,Roth Stanislav st."</formula1>
+      <formula1>"Jurkovič Martin,Nekolný Vladimír,Hanibal Filip,Nedvěd Dominik,Lanský Zoltan,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin,Eszenyiová Patrícia,Reischl Jan,Kalina Filip,Dušek Sam,Cieslar Marek,Serin David,Břicháč Pavel,Weindling Josef"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -3620,13 +4270,13 @@
       <c r="A1" s="117"/>
       <c r="B1" s="118" t="str">
         <f>Report!B1</f>
-        <v>Bolevec</v>
+        <v>Libuš</v>
       </c>
       <c r="C1" s="119">
         <v>46028.0</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="121">
         <v>46028.0</v>
@@ -4736,13 +5386,13 @@
     <row r="5">
       <c r="A5" s="134"/>
       <c r="B5" s="135" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="5"/>
       <c r="F5" s="136" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
@@ -5577,7 +6227,7 @@
       <c r="D8" s="20"/>
       <c r="E8" s="5"/>
       <c r="F8" s="145" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
@@ -5855,7 +6505,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="150" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9" s="150" t="s">
         <v>22</v>
@@ -5865,13 +6515,13 @@
         <v>18</v>
       </c>
       <c r="G9" s="150" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H9" s="150" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="152" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J9" s="153">
         <v>-1.0</v>
@@ -6146,7 +6796,7 @@
       <c r="C10" s="156"/>
       <c r="D10" s="156"/>
       <c r="E10" s="157" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F10" s="156"/>
       <c r="G10" s="156"/>
@@ -6422,7 +7072,7 @@
       <c r="C11" s="156"/>
       <c r="D11" s="156"/>
       <c r="E11" s="157" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11" s="156"/>
       <c r="G11" s="156"/>
@@ -6698,7 +7348,7 @@
       <c r="C12" s="156"/>
       <c r="D12" s="156"/>
       <c r="E12" s="157" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12" s="156"/>
       <c r="G12" s="156"/>
@@ -6974,7 +7624,7 @@
       <c r="C13" s="156"/>
       <c r="D13" s="156"/>
       <c r="E13" s="157" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F13" s="156"/>
       <c r="G13" s="156"/>
@@ -6982,7 +7632,7 @@
       <c r="I13" s="156"/>
       <c r="K13" s="15"/>
       <c r="L13" s="126" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M13" s="127"/>
       <c r="N13" s="129"/>
@@ -7250,7 +7900,7 @@
       <c r="C14" s="156"/>
       <c r="D14" s="156"/>
       <c r="E14" s="157" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F14" s="156"/>
       <c r="G14" s="156"/>
@@ -7258,7 +7908,7 @@
       <c r="I14" s="156"/>
       <c r="K14" s="15"/>
       <c r="L14" s="160" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M14" s="133"/>
       <c r="N14" s="129"/>
@@ -7526,7 +8176,7 @@
       <c r="C15" s="156"/>
       <c r="D15" s="156"/>
       <c r="E15" s="157" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F15" s="156"/>
       <c r="G15" s="156"/>
@@ -7534,7 +8184,7 @@
       <c r="I15" s="156"/>
       <c r="K15" s="15"/>
       <c r="L15" s="160" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M15" s="127"/>
       <c r="N15" s="129"/>
@@ -7808,7 +8458,7 @@
       <c r="I16" s="156"/>
       <c r="K16" s="15"/>
       <c r="L16" s="160" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M16" s="133"/>
       <c r="N16" s="129"/>
@@ -8083,7 +8733,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="13"/>
       <c r="L17" s="162" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M17" s="133"/>
       <c r="N17" s="129"/>
@@ -8629,16 +9279,16 @@
       <c r="H19" s="156"/>
       <c r="I19" s="156"/>
       <c r="J19" s="165" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K19" s="166" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L19" s="167" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M19" s="168" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
@@ -8676,7 +9326,7 @@
         <v>2.0</v>
       </c>
       <c r="M21" s="174" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N21" s="164"/>
       <c r="O21" s="164"/>
@@ -8948,16 +9598,16 @@
       <c r="H22" s="156"/>
       <c r="I22" s="156"/>
       <c r="J22" s="175" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K22" s="176" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L22" s="177" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M22" s="178" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N22" s="164"/>
       <c r="O22" s="164"/>
@@ -9783,14 +10433,14 @@
       <c r="H25" s="156"/>
       <c r="I25" s="156"/>
       <c r="J25" s="181" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K25" s="93"/>
       <c r="L25" s="177" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M25" s="178" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N25" s="164"/>
       <c r="O25" s="164"/>
@@ -10615,10 +11265,10 @@
       <c r="I28" s="156"/>
       <c r="J28" s="186"/>
       <c r="L28" s="176" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M28" s="178" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N28" s="164"/>
       <c r="O28" s="164"/>
@@ -11509,52 +12159,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="191" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="191" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="191" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="191" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="191" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F1" s="191" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G1" s="191" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H1" s="191" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I1" s="191" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="191" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K1" s="191" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="191" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M1" s="191" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N1" s="191" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O1" s="191" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P1" s="191" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q1" s="192"/>
       <c r="R1" s="192"/>
@@ -11575,40 +12225,46 @@
     </row>
     <row r="2">
       <c r="A2" s="191" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" s="191" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="191">
-        <v>393.0</v>
+        <v>369.0</v>
       </c>
       <c r="D2" s="191">
         <v>0.0</v>
       </c>
       <c r="E2" s="192"/>
       <c r="F2" s="191" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G2" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H2" s="191" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="192"/>
-      <c r="J2" s="192"/>
+        <v>86</v>
+      </c>
+      <c r="I2" s="191" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="191" t="s">
+        <v>87</v>
+      </c>
       <c r="K2" s="192"/>
       <c r="L2" s="191">
-        <v>0.0</v>
+        <v>-8.0</v>
       </c>
       <c r="M2" s="191"/>
-      <c r="N2" s="191"/>
+      <c r="N2" s="191">
+        <v>6.73065</v>
+      </c>
       <c r="O2" s="191" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="P2" s="191" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q2" s="192"/>
       <c r="R2" s="192"/>
@@ -11629,46 +12285,52 @@
     </row>
     <row r="3">
       <c r="A3" s="191" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B3" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C3" s="191">
-        <v>414.0</v>
+        <v>443.0</v>
       </c>
       <c r="D3" s="191">
-        <v>104.0</v>
-      </c>
-      <c r="E3" s="192"/>
+        <v>14.0</v>
+      </c>
+      <c r="E3" s="191" t="s">
+        <v>49</v>
+      </c>
       <c r="F3" s="191" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G3" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H3" s="191" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="191" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J3" s="191" t="s">
-        <v>91</v>
-      </c>
-      <c r="K3" s="192"/>
+        <v>95</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>96</v>
+      </c>
       <c r="L3" s="191">
         <v>-7.0</v>
       </c>
-      <c r="M3" s="191"/>
+      <c r="M3" s="191">
+        <v>0.0020833333333333333</v>
+      </c>
       <c r="N3" s="191">
-        <v>11.540733333333334</v>
+        <v>2.4166333333333334</v>
       </c>
       <c r="O3" s="191" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P3" s="191" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Q3" s="192"/>
       <c r="R3" s="192"/>
@@ -11689,48 +12351,46 @@
     </row>
     <row r="4">
       <c r="A4" s="191" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C4" s="193">
-        <v>319.0</v>
+        <v>329.0</v>
       </c>
       <c r="D4" s="191">
         <v>0.0</v>
       </c>
-      <c r="E4" s="191" t="s">
-        <v>54</v>
-      </c>
+      <c r="E4" s="192"/>
       <c r="F4" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G4" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H4" s="191" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I4" s="191" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J4" s="191" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K4" s="192"/>
       <c r="L4" s="191">
-        <v>-3.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M4" s="191"/>
       <c r="N4" s="191">
-        <v>11.1438</v>
+        <v>10.949016666666667</v>
       </c>
       <c r="O4" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P4" s="191" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q4" s="192"/>
       <c r="R4" s="192"/>
@@ -11750,48 +12410,46 @@
     </row>
     <row r="5">
       <c r="A5" s="191" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C5" s="191">
-        <v>517.0</v>
+        <v>249.0</v>
       </c>
       <c r="D5" s="191">
         <v>0.0</v>
       </c>
-      <c r="E5" s="191" t="s">
-        <v>102</v>
-      </c>
+      <c r="E5" s="192"/>
       <c r="F5" s="191" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G5" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H5" s="191" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I5" s="191" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J5" s="191" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K5" s="192"/>
       <c r="L5" s="191">
-        <v>-3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M5" s="191"/>
       <c r="N5" s="191">
-        <v>11.265066666666666</v>
+        <v>9.794583333333334</v>
       </c>
       <c r="O5" s="191" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="P5" s="191" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q5" s="192"/>
       <c r="R5" s="192"/>
@@ -11812,34 +12470,32 @@
     </row>
     <row r="6">
       <c r="A6" s="191" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B6" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="193">
-        <v>319.0</v>
+        <v>926.0</v>
       </c>
       <c r="D6" s="191">
         <v>0.0</v>
       </c>
-      <c r="E6" s="191" t="s">
-        <v>107</v>
-      </c>
+      <c r="E6" s="192"/>
       <c r="F6" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G6" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H6" s="191" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I6" s="191" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J6" s="191" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K6" s="192"/>
       <c r="L6" s="191">
@@ -11847,13 +12503,13 @@
       </c>
       <c r="M6" s="191"/>
       <c r="N6" s="191">
-        <v>8.096616666666666</v>
+        <v>8.405083333333334</v>
       </c>
       <c r="O6" s="191" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="P6" s="191" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q6" s="192"/>
       <c r="R6" s="192"/>
@@ -11874,48 +12530,46 @@
     </row>
     <row r="7">
       <c r="A7" s="191" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B7" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C7" s="193">
-        <v>603.0</v>
+        <v>249.0</v>
       </c>
       <c r="D7" s="191">
         <v>0.0</v>
       </c>
-      <c r="E7" s="191" t="s">
-        <v>54</v>
-      </c>
+      <c r="E7" s="192"/>
       <c r="F7" s="191" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G7" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H7" s="191" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I7" s="191" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J7" s="191" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K7" s="192"/>
       <c r="L7" s="191">
-        <v>-4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M7" s="191"/>
       <c r="N7" s="191">
-        <v>10.260183333333334</v>
+        <v>8.900316666666667</v>
       </c>
       <c r="O7" s="191" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P7" s="191" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q7" s="192"/>
       <c r="R7" s="192"/>
@@ -11936,25 +12590,23 @@
     </row>
     <row r="8">
       <c r="A8" s="191" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B8" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" s="193">
-        <v>319.0</v>
+        <v>204.6</v>
       </c>
       <c r="D8" s="191">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="191" t="s">
-        <v>114</v>
-      </c>
+        <v>59.4</v>
+      </c>
+      <c r="E8" s="192"/>
       <c r="F8" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G8" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H8" s="191" t="s">
         <v>115</v>
@@ -11967,14 +12619,14 @@
       </c>
       <c r="K8" s="192"/>
       <c r="L8" s="191">
-        <v>-6.0</v>
+        <v>-2.0</v>
       </c>
       <c r="M8" s="191"/>
       <c r="N8" s="191">
-        <v>8.449216666666667</v>
+        <v>12.423533333333333</v>
       </c>
       <c r="O8" s="191" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="P8" s="191" t="s">
         <v>117</v>
@@ -11998,52 +12650,48 @@
     </row>
     <row r="9">
       <c r="A9" s="191" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="B9" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C9" s="191">
-        <v>264.0</v>
+        <v>658.0</v>
       </c>
       <c r="D9" s="191">
         <v>0.0</v>
       </c>
       <c r="E9" s="191" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F9" s="191" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H9" s="191" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I9" s="191" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J9" s="191" t="s">
         <v>121</v>
       </c>
-      <c r="K9" s="191" t="s">
+      <c r="K9" s="192"/>
+      <c r="L9" s="191">
+        <v>-6.0</v>
+      </c>
+      <c r="M9" s="191"/>
+      <c r="N9" s="191">
+        <v>8.976666666666667</v>
+      </c>
+      <c r="O9" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P9" s="191" t="s">
         <v>122</v>
-      </c>
-      <c r="L9" s="191">
-        <v>-22.0</v>
-      </c>
-      <c r="M9" s="191">
-        <v>0.725</v>
-      </c>
-      <c r="N9" s="191">
-        <v>11.1493</v>
-      </c>
-      <c r="O9" s="191" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="191" t="s">
-        <v>123</v>
       </c>
       <c r="Q9" s="192"/>
       <c r="R9" s="192"/>
@@ -12064,46 +12712,46 @@
     </row>
     <row r="10">
       <c r="A10" s="191" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B10" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C10" s="193">
-        <v>207.0</v>
+        <v>523.0</v>
       </c>
       <c r="D10" s="191">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
       <c r="E10" s="192"/>
       <c r="F10" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G10" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="191" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" s="191" t="s">
         <v>124</v>
       </c>
-      <c r="H10" s="191" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" s="191" t="s">
-        <v>126</v>
-      </c>
       <c r="J10" s="191" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K10" s="192"/>
       <c r="L10" s="191">
-        <v>-11.0</v>
+        <v>-2.0</v>
       </c>
       <c r="M10" s="191"/>
       <c r="N10" s="191">
-        <v>8.22245</v>
+        <v>12.816383333333333</v>
       </c>
       <c r="O10" s="191" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P10" s="191" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q10" s="192"/>
       <c r="R10" s="192"/>
@@ -12124,48 +12772,48 @@
     </row>
     <row r="11">
       <c r="A11" s="191" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B11" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C11" s="191">
-        <v>244.0</v>
+        <v>331.0</v>
       </c>
       <c r="D11" s="191">
         <v>0.0</v>
       </c>
       <c r="E11" s="191" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G11" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H11" s="191" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="191" t="s">
         <v>128</v>
       </c>
-      <c r="I11" s="191" t="s">
-        <v>129</v>
-      </c>
       <c r="J11" s="191" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K11" s="192"/>
       <c r="L11" s="191">
-        <v>-6.0</v>
+        <v>-7.0</v>
       </c>
       <c r="M11" s="191"/>
       <c r="N11" s="191">
-        <v>8.288816666666667</v>
+        <v>7.607916666666667</v>
       </c>
       <c r="O11" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P11" s="191" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q11" s="192"/>
       <c r="R11" s="192"/>
@@ -12186,34 +12834,32 @@
     </row>
     <row r="12">
       <c r="A12" s="191" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B12" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C12" s="193">
-        <v>368.0</v>
+        <v>321.0</v>
       </c>
       <c r="D12" s="191">
         <v>0.0</v>
       </c>
-      <c r="E12" s="191" t="s">
-        <v>54</v>
-      </c>
+      <c r="E12" s="192"/>
       <c r="F12" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G12" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H12" s="191" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="191" t="s">
         <v>131</v>
       </c>
-      <c r="I12" s="191" t="s">
-        <v>132</v>
-      </c>
       <c r="J12" s="191" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K12" s="192"/>
       <c r="L12" s="191">
@@ -12221,13 +12867,13 @@
       </c>
       <c r="M12" s="191"/>
       <c r="N12" s="191">
-        <v>11.53675</v>
+        <v>11.620916666666666</v>
       </c>
       <c r="O12" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P12" s="191" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q12" s="192"/>
       <c r="R12" s="192"/>
@@ -12248,32 +12894,32 @@
     </row>
     <row r="13">
       <c r="A13" s="191" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B13" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C13" s="191">
-        <v>269.25</v>
+        <v>717.0</v>
       </c>
       <c r="D13" s="191">
-        <v>89.75</v>
+        <v>0.0</v>
       </c>
       <c r="E13" s="192"/>
       <c r="F13" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G13" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H13" s="191" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="191" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="191" t="s">
-        <v>135</v>
-      </c>
       <c r="J13" s="191" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K13" s="192"/>
       <c r="L13" s="191">
@@ -12281,13 +12927,13 @@
       </c>
       <c r="M13" s="191"/>
       <c r="N13" s="191">
-        <v>8.65495</v>
+        <v>8.3808</v>
       </c>
       <c r="O13" s="191" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="P13" s="191" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q13" s="192"/>
       <c r="R13" s="192"/>
@@ -12307,34 +12953,34 @@
     </row>
     <row r="14">
       <c r="A14" s="191" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B14" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C14" s="191">
-        <v>388.0</v>
+        <v>553.0</v>
       </c>
       <c r="D14" s="191">
         <v>0.0</v>
       </c>
       <c r="E14" s="191" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F14" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G14" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H14" s="191" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I14" s="191" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J14" s="191" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K14" s="192"/>
       <c r="L14" s="191">
@@ -12342,13 +12988,13 @@
       </c>
       <c r="M14" s="191"/>
       <c r="N14" s="191">
-        <v>8.785883333333333</v>
+        <v>8.742366666666667</v>
       </c>
       <c r="O14" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P14" s="191" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q14" s="192"/>
       <c r="R14" s="192"/>
@@ -12369,52 +13015,46 @@
     </row>
     <row r="15">
       <c r="A15" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="193">
+        <v>366.0</v>
+      </c>
+      <c r="D15" s="191">
+        <v>92.0</v>
+      </c>
+      <c r="E15" s="192"/>
+      <c r="F15" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="191" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="191" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="191" t="s">
+        <v>140</v>
+      </c>
+      <c r="K15" s="192"/>
+      <c r="L15" s="191">
+        <v>1.0</v>
+      </c>
+      <c r="M15" s="191"/>
+      <c r="N15" s="191">
+        <v>50.347233333333335</v>
+      </c>
+      <c r="O15" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" s="191" t="s">
         <v>141</v>
-      </c>
-      <c r="B15" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="193">
-        <v>329.0</v>
-      </c>
-      <c r="D15" s="191">
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="191" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="191" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="191" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="191" t="s">
-        <v>142</v>
-      </c>
-      <c r="I15" s="191" t="s">
-        <v>143</v>
-      </c>
-      <c r="J15" s="191" t="s">
-        <v>144</v>
-      </c>
-      <c r="K15" s="191" t="s">
-        <v>145</v>
-      </c>
-      <c r="L15" s="191">
-        <v>-7.0</v>
-      </c>
-      <c r="M15" s="191">
-        <v>8.733383333333334</v>
-      </c>
-      <c r="N15" s="191">
-        <v>10.950583333333332</v>
-      </c>
-      <c r="O15" s="191" t="s">
-        <v>146</v>
-      </c>
-      <c r="P15" s="191" t="s">
-        <v>147</v>
       </c>
       <c r="Q15" s="192"/>
       <c r="R15" s="192"/>
@@ -12435,46 +13075,46 @@
     </row>
     <row r="16">
       <c r="A16" s="191" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" s="191" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="C16" s="193">
-        <v>513.0</v>
+        <v>610.0</v>
       </c>
       <c r="D16" s="191">
-        <v>125.0</v>
+        <v>0.0</v>
       </c>
       <c r="E16" s="192"/>
       <c r="F16" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G16" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H16" s="191" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I16" s="191" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J16" s="191" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="K16" s="192"/>
       <c r="L16" s="191">
-        <v>0.0</v>
+        <v>-6.0</v>
       </c>
       <c r="M16" s="191"/>
       <c r="N16" s="191">
-        <v>15.8281</v>
+        <v>8.295066666666667</v>
       </c>
       <c r="O16" s="191" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="P16" s="191" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="Q16" s="192"/>
       <c r="R16" s="192"/>
@@ -12495,46 +13135,48 @@
     </row>
     <row r="17">
       <c r="A17" s="191" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="B17" s="191" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="C17" s="193">
-        <v>182.0</v>
+        <v>273.0</v>
       </c>
       <c r="D17" s="191">
-        <v>62.0</v>
-      </c>
-      <c r="E17" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E17" s="191" t="s">
+        <v>56</v>
+      </c>
       <c r="F17" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G17" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H17" s="191" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I17" s="191" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="J17" s="191" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="K17" s="192"/>
       <c r="L17" s="191">
-        <v>-6.0</v>
+        <v>-9.0</v>
       </c>
       <c r="M17" s="191"/>
       <c r="N17" s="191">
-        <v>8.864433333333332</v>
+        <v>5.994066666666667</v>
       </c>
       <c r="O17" s="191" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="P17" s="191" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="Q17" s="192"/>
       <c r="R17" s="192"/>
@@ -12555,46 +13197,46 @@
     </row>
     <row r="18">
       <c r="A18" s="191" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="B18" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C18" s="191">
-        <v>777.0</v>
+        <v>49.0</v>
       </c>
       <c r="D18" s="191">
         <v>0.0</v>
       </c>
       <c r="E18" s="192"/>
       <c r="F18" s="191" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="G18" s="191" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="H18" s="191" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I18" s="191" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J18" s="191" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="K18" s="192"/>
       <c r="L18" s="191">
-        <v>149.0</v>
+        <v>-3.0</v>
       </c>
       <c r="M18" s="191"/>
       <c r="N18" s="191">
-        <v>154.96951666666666</v>
+        <v>1.9094</v>
       </c>
       <c r="O18" s="191" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="P18" s="191" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="Q18" s="192"/>
       <c r="R18" s="192"/>
@@ -12615,34 +13257,34 @@
     </row>
     <row r="19">
       <c r="A19" s="191" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="B19" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C19" s="193">
-        <v>319.0</v>
+        <v>376.0</v>
       </c>
       <c r="D19" s="191">
         <v>0.0</v>
       </c>
       <c r="E19" s="191" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="F19" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G19" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H19" s="191" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I19" s="191" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J19" s="191" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="K19" s="192"/>
       <c r="L19" s="191">
@@ -12650,13 +13292,13 @@
       </c>
       <c r="M19" s="191"/>
       <c r="N19" s="191">
-        <v>9.479183333333333</v>
+        <v>9.196683333333333</v>
       </c>
       <c r="O19" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P19" s="191" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="Q19" s="192"/>
       <c r="R19" s="192"/>
@@ -12677,46 +13319,52 @@
     </row>
     <row r="20">
       <c r="A20" s="191" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B20" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C20" s="191">
-        <v>408.0</v>
+        <v>306.0</v>
       </c>
       <c r="D20" s="191">
-        <v>100.0</v>
-      </c>
-      <c r="E20" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E20" s="191" t="s">
+        <v>56</v>
+      </c>
       <c r="F20" s="191" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G20" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H20" s="191" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I20" s="191" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J20" s="191" t="s">
-        <v>163</v>
-      </c>
-      <c r="K20" s="192"/>
+        <v>157</v>
+      </c>
+      <c r="K20" s="191" t="s">
+        <v>158</v>
+      </c>
       <c r="L20" s="191">
-        <v>-10.0</v>
-      </c>
-      <c r="M20" s="191"/>
+        <v>1.0</v>
+      </c>
+      <c r="M20" s="191">
+        <v>3.9635666666666665</v>
+      </c>
       <c r="N20" s="191">
-        <v>8.3353</v>
+        <v>9.35105</v>
       </c>
       <c r="O20" s="191" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P20" s="191" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="Q20" s="192"/>
       <c r="R20" s="192"/>
@@ -12737,46 +13385,46 @@
     </row>
     <row r="21">
       <c r="A21" s="191" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="B21" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C21" s="193">
-        <v>183.0</v>
+        <v>309.0</v>
       </c>
       <c r="D21" s="191">
-        <v>61.0</v>
+        <v>0.0</v>
       </c>
       <c r="E21" s="192"/>
       <c r="F21" s="191" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G21" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H21" s="191" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I21" s="191" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J21" s="191" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K21" s="192"/>
       <c r="L21" s="191">
-        <v>-7.0</v>
+        <v>0.0</v>
       </c>
       <c r="M21" s="191"/>
       <c r="N21" s="191">
-        <v>7.3571333333333335</v>
+        <v>5.7817</v>
       </c>
       <c r="O21" s="191" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="P21" s="191" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="Q21" s="192"/>
       <c r="R21" s="192"/>
@@ -12797,52 +13445,46 @@
     </row>
     <row r="22">
       <c r="A22" s="191" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B22" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C22" s="191">
-        <v>428.0</v>
+        <v>40.0</v>
       </c>
       <c r="D22" s="191">
         <v>0.0</v>
       </c>
-      <c r="E22" s="191" t="s">
-        <v>45</v>
-      </c>
+      <c r="E22" s="192"/>
       <c r="F22" s="191" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="G22" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H22" s="191" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I22" s="191" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J22" s="191" t="s">
-        <v>169</v>
-      </c>
-      <c r="K22" s="191" t="s">
-        <v>170</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="K22" s="192"/>
       <c r="L22" s="191">
-        <v>0.0</v>
-      </c>
-      <c r="M22" s="191">
-        <v>1.271</v>
-      </c>
+        <v>-2.0</v>
+      </c>
+      <c r="M22" s="191"/>
       <c r="N22" s="191">
-        <v>16.686516666666666</v>
+        <v>2.4218333333333333</v>
       </c>
       <c r="O22" s="191" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="P22" s="191" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="Q22" s="192"/>
       <c r="R22" s="192"/>
@@ -12863,46 +13505,52 @@
     </row>
     <row r="23">
       <c r="A23" s="191" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="B23" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C23" s="191">
-        <v>259.0</v>
+        <v>359.0</v>
       </c>
       <c r="D23" s="191">
         <v>0.0</v>
       </c>
-      <c r="E23" s="192"/>
+      <c r="E23" s="191" t="s">
+        <v>49</v>
+      </c>
       <c r="F23" s="191" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G23" s="191" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="H23" s="191" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I23" s="191" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J23" s="191" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="192"/>
+        <v>168</v>
+      </c>
+      <c r="K23" s="191" t="s">
+        <v>169</v>
+      </c>
       <c r="L23" s="191">
-        <v>29.0</v>
-      </c>
-      <c r="M23" s="191"/>
+        <v>-16.0</v>
+      </c>
+      <c r="M23" s="191">
+        <v>0.0013666666666666666</v>
+      </c>
       <c r="N23" s="191">
-        <v>34.25653333333333</v>
+        <v>10.137616666666666</v>
       </c>
       <c r="O23" s="191" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="P23" s="191" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Q23" s="192"/>
       <c r="R23" s="192"/>
@@ -12923,46 +13571,46 @@
     </row>
     <row r="24">
       <c r="A24" s="191" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B24" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C24" s="191">
-        <v>567.3</v>
+        <v>437.0</v>
       </c>
       <c r="D24" s="191">
-        <v>164.7</v>
+        <v>131.0</v>
       </c>
       <c r="E24" s="192"/>
       <c r="F24" s="191" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G24" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H24" s="191" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I24" s="191" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J24" s="191" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="K24" s="192"/>
       <c r="L24" s="191">
-        <v>-2.0</v>
+        <v>-3.0</v>
       </c>
       <c r="M24" s="191"/>
       <c r="N24" s="191">
-        <v>12.529516666666666</v>
+        <v>15.010483333333333</v>
       </c>
       <c r="O24" s="191" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="P24" s="191" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Q24" s="192"/>
       <c r="R24" s="192"/>
@@ -12983,46 +13631,48 @@
     </row>
     <row r="25">
       <c r="A25" s="191" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="B25" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C25" s="191">
-        <v>976.0</v>
+        <v>281.0</v>
       </c>
       <c r="D25" s="191">
         <v>0.0</v>
       </c>
-      <c r="E25" s="192"/>
+      <c r="E25" s="191" t="s">
+        <v>56</v>
+      </c>
       <c r="F25" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G25" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H25" s="191" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I25" s="191" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J25" s="191" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K25" s="192"/>
       <c r="L25" s="191">
-        <v>-2.0</v>
+        <v>-6.0</v>
       </c>
       <c r="M25" s="191"/>
       <c r="N25" s="191">
-        <v>12.330166666666667</v>
+        <v>8.103166666666667</v>
       </c>
       <c r="O25" s="191" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="P25" s="191" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="Q25" s="192"/>
       <c r="R25" s="192"/>
@@ -13043,48 +13693,46 @@
     </row>
     <row r="26">
       <c r="A26" s="191" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B26" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C26" s="191">
-        <v>319.0</v>
+        <v>558.0</v>
       </c>
       <c r="D26" s="191">
         <v>0.0</v>
       </c>
-      <c r="E26" s="191" t="s">
-        <v>54</v>
-      </c>
+      <c r="E26" s="192"/>
       <c r="F26" s="191" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G26" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H26" s="191" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I26" s="191" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J26" s="191" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K26" s="192"/>
       <c r="L26" s="191">
-        <v>-7.0</v>
+        <v>0.0</v>
       </c>
       <c r="M26" s="191"/>
       <c r="N26" s="191">
-        <v>7.950283333333333</v>
+        <v>4.174133333333334</v>
       </c>
       <c r="O26" s="191" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P26" s="191" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q26" s="192"/>
       <c r="R26" s="192"/>
@@ -13105,46 +13753,48 @@
     </row>
     <row r="27">
       <c r="A27" s="191" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B27" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C27" s="193">
-        <v>139.0</v>
+        <v>223.0</v>
       </c>
       <c r="D27" s="191">
         <v>0.0</v>
       </c>
-      <c r="E27" s="192"/>
+      <c r="E27" s="191" t="s">
+        <v>56</v>
+      </c>
       <c r="F27" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G27" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H27" s="191" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I27" s="191" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J27" s="191" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K27" s="192"/>
       <c r="L27" s="191">
-        <v>1.0</v>
+        <v>-9.0</v>
       </c>
       <c r="M27" s="191"/>
       <c r="N27" s="191">
-        <v>6.846733333333333</v>
+        <v>5.520816666666667</v>
       </c>
       <c r="O27" s="191" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="P27" s="191" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Q27" s="192"/>
       <c r="R27" s="192"/>
@@ -13165,48 +13815,48 @@
     </row>
     <row r="28">
       <c r="A28" s="191" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="B28" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C28" s="193">
-        <v>319.0</v>
+        <v>369.0</v>
       </c>
       <c r="D28" s="191">
         <v>0.0</v>
       </c>
       <c r="E28" s="191" t="s">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="F28" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G28" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H28" s="191" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I28" s="191" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J28" s="191" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K28" s="192"/>
       <c r="L28" s="191">
-        <v>0.0</v>
+        <v>-6.0</v>
       </c>
       <c r="M28" s="191"/>
       <c r="N28" s="191">
-        <v>15.4617</v>
+        <v>8.5602</v>
       </c>
       <c r="O28" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P28" s="191" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="Q28" s="192"/>
       <c r="R28" s="192"/>
@@ -13227,46 +13877,46 @@
     </row>
     <row r="29">
       <c r="A29" s="191" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B29" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C29" s="193">
-        <v>536.0</v>
+        <v>188.0</v>
       </c>
       <c r="D29" s="191">
-        <v>132.0</v>
+        <v>0.0</v>
       </c>
       <c r="E29" s="192"/>
       <c r="F29" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G29" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H29" s="191" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I29" s="191" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J29" s="191" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K29" s="192"/>
       <c r="L29" s="191">
-        <v>-6.0</v>
+        <v>-9.0</v>
       </c>
       <c r="M29" s="191"/>
       <c r="N29" s="191">
-        <v>60.28143333333333</v>
+        <v>5.947533333333333</v>
       </c>
       <c r="O29" s="191" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P29" s="191" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q29" s="192"/>
       <c r="R29" s="192"/>
@@ -13287,46 +13937,48 @@
     </row>
     <row r="30">
       <c r="A30" s="191" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B30" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C30" s="193">
-        <v>55.0</v>
+        <v>414.0</v>
       </c>
       <c r="D30" s="191">
         <v>0.0</v>
       </c>
-      <c r="E30" s="192"/>
+      <c r="E30" s="191" t="s">
+        <v>190</v>
+      </c>
       <c r="F30" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G30" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H30" s="191" t="s">
+        <v>191</v>
+      </c>
+      <c r="I30" s="191" t="s">
         <v>192</v>
       </c>
-      <c r="I30" s="191" t="s">
-        <v>193</v>
-      </c>
       <c r="J30" s="191" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K30" s="192"/>
       <c r="L30" s="191">
-        <v>-1.0</v>
+        <v>-6.0</v>
       </c>
       <c r="M30" s="191"/>
       <c r="N30" s="191">
-        <v>3.26955</v>
+        <v>8.198683333333333</v>
       </c>
       <c r="O30" s="191" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="P30" s="191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q30" s="192"/>
       <c r="R30" s="192"/>
@@ -13347,46 +13999,48 @@
     </row>
     <row r="31">
       <c r="A31" s="191" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="B31" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C31" s="191">
-        <v>247.23</v>
+        <v>329.0</v>
       </c>
       <c r="D31" s="191">
-        <v>71.77</v>
-      </c>
-      <c r="E31" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="191" t="s">
+        <v>56</v>
+      </c>
       <c r="F31" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G31" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H31" s="191" t="s">
+        <v>194</v>
+      </c>
+      <c r="I31" s="191" t="s">
         <v>195</v>
       </c>
-      <c r="I31" s="191" t="s">
-        <v>196</v>
-      </c>
       <c r="J31" s="191" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K31" s="192"/>
       <c r="L31" s="191">
-        <v>-6.0</v>
+        <v>-8.0</v>
       </c>
       <c r="M31" s="191"/>
       <c r="N31" s="191">
-        <v>8.889266666666666</v>
+        <v>6.3473</v>
       </c>
       <c r="O31" s="191" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="P31" s="191" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q31" s="192"/>
       <c r="R31" s="192"/>
@@ -13407,45 +14061,49 @@
     </row>
     <row r="32">
       <c r="A32" s="191" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B32" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C32" s="191">
-        <v>1045.0</v>
+        <v>493.0</v>
       </c>
       <c r="D32" s="191">
         <v>0.0</v>
       </c>
       <c r="E32" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="191" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="191" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="191" t="s">
-        <v>95</v>
-      </c>
-      <c r="G32" s="191" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="191" t="s">
+      <c r="J32" s="191" t="s">
         <v>199</v>
       </c>
-      <c r="I32" s="191" t="s">
+      <c r="K32" s="191" t="s">
         <v>200</v>
       </c>
-      <c r="J32" s="191" t="s">
-        <v>200</v>
-      </c>
-      <c r="K32" s="192"/>
       <c r="L32" s="191">
-        <v>0.0</v>
-      </c>
-      <c r="M32" s="191"/>
+        <v>-12.0</v>
+      </c>
+      <c r="M32" s="191">
+        <v>0.0024833333333333335</v>
+      </c>
       <c r="N32" s="191">
-        <v>16.021966666666668</v>
+        <v>11.714666666666666</v>
       </c>
       <c r="O32" s="191" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="P32" s="191" t="s">
         <v>201</v>
@@ -13469,25 +14127,23 @@
     </row>
     <row r="33">
       <c r="A33" s="191" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B33" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C33" s="191">
-        <v>244.0</v>
+        <v>409.2</v>
       </c>
       <c r="D33" s="191">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="191" t="s">
-        <v>54</v>
-      </c>
+        <v>118.8</v>
+      </c>
+      <c r="E33" s="192"/>
       <c r="F33" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G33" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H33" s="191" t="s">
         <v>202</v>
@@ -13504,10 +14160,10 @@
       </c>
       <c r="M33" s="191"/>
       <c r="N33" s="191">
-        <v>10.575166666666666</v>
+        <v>10.42475</v>
       </c>
       <c r="O33" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P33" s="191" t="s">
         <v>204</v>
@@ -13531,23 +14187,25 @@
     </row>
     <row r="34">
       <c r="A34" s="191" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="B34" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C34" s="193">
-        <v>207.2</v>
+        <v>712.0</v>
       </c>
       <c r="D34" s="191">
-        <v>51.8</v>
-      </c>
-      <c r="E34" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="191" t="s">
+        <v>49</v>
+      </c>
       <c r="F34" s="191" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G34" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H34" s="191" t="s">
         <v>205</v>
@@ -13556,21 +14214,25 @@
         <v>206</v>
       </c>
       <c r="J34" s="191" t="s">
-        <v>206</v>
-      </c>
-      <c r="K34" s="192"/>
+        <v>207</v>
+      </c>
+      <c r="K34" s="191" t="s">
+        <v>208</v>
+      </c>
       <c r="L34" s="191">
-        <v>75.0</v>
-      </c>
-      <c r="M34" s="191"/>
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="191">
+        <v>0.00355</v>
+      </c>
       <c r="N34" s="191">
-        <v>80.47385</v>
+        <v>16.78076666666667</v>
       </c>
       <c r="O34" s="191" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="P34" s="191" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q34" s="192"/>
       <c r="R34" s="192"/>
@@ -13591,46 +14253,52 @@
     </row>
     <row r="35">
       <c r="A35" s="191" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="B35" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C35" s="193">
-        <v>263.2</v>
+        <v>329.0</v>
       </c>
       <c r="D35" s="191">
-        <v>65.8</v>
-      </c>
-      <c r="E35" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="191" t="s">
+        <v>49</v>
+      </c>
       <c r="F35" s="191" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G35" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H35" s="191" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I35" s="191" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J35" s="191" t="s">
-        <v>209</v>
-      </c>
-      <c r="K35" s="192"/>
+        <v>212</v>
+      </c>
+      <c r="K35" s="191" t="s">
+        <v>213</v>
+      </c>
       <c r="L35" s="191">
-        <v>77.0</v>
-      </c>
-      <c r="M35" s="191"/>
+        <v>-15.0</v>
+      </c>
+      <c r="M35" s="191">
+        <v>0.0020166666666666666</v>
+      </c>
       <c r="N35" s="191">
-        <v>82.1581</v>
+        <v>7.633033333333334</v>
       </c>
       <c r="O35" s="191" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="P35" s="191" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q35" s="192"/>
       <c r="R35" s="192"/>
@@ -13651,48 +14319,46 @@
     </row>
     <row r="36">
       <c r="A36" s="191" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B36" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C36" s="193">
-        <v>208.0</v>
+        <v>20.0</v>
       </c>
       <c r="D36" s="191">
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="191" t="s">
-        <v>54</v>
-      </c>
+        <v>35.0</v>
+      </c>
+      <c r="E36" s="192"/>
       <c r="F36" s="191" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G36" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H36" s="191" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I36" s="191" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J36" s="191" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K36" s="192"/>
       <c r="L36" s="191">
-        <v>4.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M36" s="191"/>
       <c r="N36" s="191">
-        <v>19.82005</v>
+        <v>0.08916666666666667</v>
       </c>
       <c r="O36" s="191" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P36" s="191" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q36" s="192"/>
       <c r="R36" s="192"/>
@@ -13713,46 +14379,46 @@
     </row>
     <row r="37">
       <c r="A37" s="191" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="B37" s="191" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C37" s="191">
-        <v>259.0</v>
+        <v>468.6</v>
       </c>
       <c r="D37" s="191">
-        <v>0.0</v>
+        <v>59.4</v>
       </c>
       <c r="E37" s="192"/>
       <c r="F37" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G37" s="191" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H37" s="191" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I37" s="191" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J37" s="191" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K37" s="192"/>
       <c r="L37" s="191">
-        <v>3.0</v>
+        <v>-8.0</v>
       </c>
       <c r="M37" s="191"/>
       <c r="N37" s="191">
-        <v>8.818066666666667</v>
+        <v>6.9703333333333335</v>
       </c>
       <c r="O37" s="191" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="P37" s="191" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q37" s="192"/>
       <c r="R37" s="192"/>
@@ -13773,46 +14439,52 @@
     </row>
     <row r="38">
       <c r="A38" s="191" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B38" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C38" s="193">
-        <v>216.23</v>
+        <v>298.0</v>
       </c>
       <c r="D38" s="191">
-        <v>62.77</v>
-      </c>
-      <c r="E38" s="192"/>
+        <v>11.0</v>
+      </c>
+      <c r="E38" s="191" t="s">
+        <v>49</v>
+      </c>
       <c r="F38" s="191" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G38" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H38" s="191" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I38" s="191" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J38" s="191" t="s">
-        <v>218</v>
-      </c>
-      <c r="K38" s="192"/>
+        <v>223</v>
+      </c>
+      <c r="K38" s="191" t="s">
+        <v>224</v>
+      </c>
       <c r="L38" s="191">
-        <v>-8.0</v>
-      </c>
-      <c r="M38" s="191"/>
+        <v>-2.0</v>
+      </c>
+      <c r="M38" s="191">
+        <v>0.0019666666666666665</v>
+      </c>
       <c r="N38" s="191">
-        <v>6.224183333333333</v>
+        <v>11.25675</v>
       </c>
       <c r="O38" s="191" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="P38" s="191" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q38" s="192"/>
       <c r="R38" s="192"/>
@@ -13833,48 +14505,46 @@
     </row>
     <row r="39">
       <c r="A39" s="191" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B39" s="191" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C39" s="191">
-        <v>118.0</v>
+        <v>411.03</v>
       </c>
       <c r="D39" s="191">
-        <v>0.0</v>
-      </c>
-      <c r="E39" s="191" t="s">
-        <v>54</v>
-      </c>
+        <v>78.97</v>
+      </c>
+      <c r="E39" s="192"/>
       <c r="F39" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G39" s="191" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H39" s="191" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="I39" s="191" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J39" s="191" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="K39" s="192"/>
       <c r="L39" s="191">
-        <v>-14.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M39" s="191"/>
       <c r="N39" s="191">
-        <v>0.8196833333333333</v>
+        <v>13.500766666666667</v>
       </c>
       <c r="O39" s="191" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P39" s="191" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q39" s="192"/>
       <c r="R39" s="192"/>
@@ -13895,46 +14565,52 @@
     </row>
     <row r="40">
       <c r="A40" s="191" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B40" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C40" s="191">
-        <v>208.48</v>
+        <v>583.0</v>
       </c>
       <c r="D40" s="191">
-        <v>60.52</v>
-      </c>
-      <c r="E40" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E40" s="191" t="s">
+        <v>49</v>
+      </c>
       <c r="F40" s="191" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G40" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H40" s="191" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="I40" s="191" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="J40" s="191" t="s">
-        <v>224</v>
-      </c>
-      <c r="K40" s="192"/>
+        <v>231</v>
+      </c>
+      <c r="K40" s="191" t="s">
+        <v>232</v>
+      </c>
       <c r="L40" s="191">
         <v>-6.0</v>
       </c>
-      <c r="M40" s="191"/>
+      <c r="M40" s="191">
+        <v>0.0027333333333333333</v>
+      </c>
       <c r="N40" s="191">
-        <v>8.211733333333333</v>
+        <v>10.40635</v>
       </c>
       <c r="O40" s="191" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="P40" s="191" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="Q40" s="192"/>
       <c r="R40" s="192"/>
@@ -13955,46 +14631,48 @@
     </row>
     <row r="41">
       <c r="A41" s="191" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="B41" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C41" s="193">
-        <v>318.0</v>
+        <v>329.0</v>
       </c>
       <c r="D41" s="191">
-        <v>80.0</v>
-      </c>
-      <c r="E41" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E41" s="191" t="s">
+        <v>56</v>
+      </c>
       <c r="F41" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G41" s="191" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="H41" s="191" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="I41" s="191" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="J41" s="191" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K41" s="192"/>
       <c r="L41" s="191">
-        <v>-11.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M41" s="191"/>
       <c r="N41" s="191">
-        <v>7.545966666666667</v>
+        <v>10.294366666666667</v>
       </c>
       <c r="O41" s="191" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P41" s="191" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="Q41" s="192"/>
       <c r="R41" s="192"/>
@@ -14015,46 +14693,48 @@
     </row>
     <row r="42">
       <c r="A42" s="191" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B42" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C42" s="193">
-        <v>175.2</v>
+        <v>672.0</v>
       </c>
       <c r="D42" s="191">
-        <v>43.8</v>
-      </c>
-      <c r="E42" s="192"/>
+        <v>0.0</v>
+      </c>
+      <c r="E42" s="191" t="s">
+        <v>56</v>
+      </c>
       <c r="F42" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G42" s="191" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="H42" s="191" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="I42" s="191" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="J42" s="191" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K42" s="192"/>
       <c r="L42" s="191">
-        <v>-4.0</v>
+        <v>-5.0</v>
       </c>
       <c r="M42" s="191"/>
       <c r="N42" s="191">
-        <v>0.17953333333333332</v>
+        <v>9.84005</v>
       </c>
       <c r="O42" s="191" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="P42" s="191" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="Q42" s="192"/>
       <c r="R42" s="192"/>
@@ -14075,46 +14755,46 @@
     </row>
     <row r="43">
       <c r="A43" s="191" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B43" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C43" s="191">
-        <v>189.1</v>
+        <v>434.0</v>
       </c>
       <c r="D43" s="191">
-        <v>54.9</v>
+        <v>0.0</v>
       </c>
       <c r="E43" s="192"/>
       <c r="F43" s="191" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G43" s="191" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H43" s="191" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="I43" s="191" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J43" s="191" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="K43" s="192"/>
       <c r="L43" s="191">
-        <v>-6.0</v>
+        <v>-9.0</v>
       </c>
       <c r="M43" s="191"/>
       <c r="N43" s="191">
-        <v>8.886033333333334</v>
+        <v>5.87465</v>
       </c>
       <c r="O43" s="191" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="P43" s="191" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="Q43" s="192"/>
       <c r="R43" s="192"/>
@@ -14135,46 +14815,46 @@
     </row>
     <row r="44">
       <c r="A44" s="191" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="B44" s="191" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C44" s="193">
-        <v>198.0</v>
+        <v>453.0</v>
       </c>
       <c r="D44" s="191">
         <v>0.0</v>
       </c>
       <c r="E44" s="192"/>
       <c r="F44" s="191" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G44" s="191" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="H44" s="191" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I44" s="191" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="J44" s="191" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="K44" s="192"/>
       <c r="L44" s="191">
-        <v>26.0</v>
+        <v>-5.0</v>
       </c>
       <c r="M44" s="191"/>
       <c r="N44" s="191">
-        <v>31.72405</v>
+        <v>9.7597</v>
       </c>
       <c r="O44" s="191" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="P44" s="191" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="Q44" s="192"/>
       <c r="R44" s="192"/>
@@ -14194,22 +14874,48 @@
       <c r="AF44" s="192"/>
     </row>
     <row r="45">
-      <c r="A45" s="192"/>
-      <c r="B45" s="192"/>
-      <c r="C45" s="192"/>
-      <c r="D45" s="192"/>
+      <c r="A45" s="191" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="191">
+        <v>40.0</v>
+      </c>
+      <c r="D45" s="191">
+        <v>70.0</v>
+      </c>
       <c r="E45" s="192"/>
-      <c r="F45" s="192"/>
-      <c r="G45" s="192"/>
-      <c r="H45" s="192"/>
-      <c r="I45" s="192"/>
-      <c r="J45" s="192"/>
+      <c r="F45" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H45" s="191" t="s">
+        <v>246</v>
+      </c>
+      <c r="I45" s="191" t="s">
+        <v>247</v>
+      </c>
+      <c r="J45" s="191" t="s">
+        <v>247</v>
+      </c>
       <c r="K45" s="192"/>
-      <c r="L45" s="192"/>
-      <c r="M45" s="192"/>
-      <c r="N45" s="192"/>
-      <c r="O45" s="192"/>
-      <c r="P45" s="192"/>
+      <c r="L45" s="191">
+        <v>-4.0</v>
+      </c>
+      <c r="M45" s="191"/>
+      <c r="N45" s="191">
+        <v>0.16266666666666665</v>
+      </c>
+      <c r="O45" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="P45" s="191" t="s">
+        <v>248</v>
+      </c>
       <c r="Q45" s="192"/>
       <c r="R45" s="192"/>
       <c r="S45" s="192"/>
@@ -14228,22 +14934,54 @@
       <c r="AF45" s="192"/>
     </row>
     <row r="46">
-      <c r="A46" s="192"/>
-      <c r="B46" s="192"/>
-      <c r="C46" s="194"/>
-      <c r="D46" s="192"/>
-      <c r="E46" s="192"/>
-      <c r="F46" s="192"/>
-      <c r="G46" s="192"/>
-      <c r="H46" s="192"/>
-      <c r="I46" s="192"/>
-      <c r="J46" s="192"/>
-      <c r="K46" s="192"/>
-      <c r="L46" s="192"/>
-      <c r="M46" s="192"/>
-      <c r="N46" s="192"/>
-      <c r="O46" s="192"/>
-      <c r="P46" s="192"/>
+      <c r="A46" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="193">
+        <v>249.0</v>
+      </c>
+      <c r="D46" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E46" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G46" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H46" s="191" t="s">
+        <v>249</v>
+      </c>
+      <c r="I46" s="191" t="s">
+        <v>250</v>
+      </c>
+      <c r="J46" s="191" t="s">
+        <v>251</v>
+      </c>
+      <c r="K46" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="L46" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="M46" s="191">
+        <v>0.00295</v>
+      </c>
+      <c r="N46" s="191">
+        <v>7.621366666666667</v>
+      </c>
+      <c r="O46" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P46" s="191" t="s">
+        <v>253</v>
+      </c>
       <c r="Q46" s="192"/>
       <c r="R46" s="192"/>
       <c r="S46" s="192"/>
@@ -14262,22 +15000,50 @@
       <c r="AF46" s="192"/>
     </row>
     <row r="47">
-      <c r="A47" s="192"/>
-      <c r="B47" s="192"/>
-      <c r="C47" s="194"/>
-      <c r="D47" s="192"/>
-      <c r="E47" s="192"/>
-      <c r="F47" s="192"/>
-      <c r="G47" s="192"/>
-      <c r="H47" s="192"/>
-      <c r="I47" s="192"/>
-      <c r="J47" s="192"/>
+      <c r="A47" s="191" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="193">
+        <v>602.0</v>
+      </c>
+      <c r="D47" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E47" s="191" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G47" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H47" s="191" t="s">
+        <v>255</v>
+      </c>
+      <c r="I47" s="191" t="s">
+        <v>256</v>
+      </c>
+      <c r="J47" s="191" t="s">
+        <v>256</v>
+      </c>
       <c r="K47" s="192"/>
-      <c r="L47" s="192"/>
-      <c r="M47" s="192"/>
-      <c r="N47" s="192"/>
-      <c r="O47" s="192"/>
-      <c r="P47" s="192"/>
+      <c r="L47" s="191">
+        <v>-7.0</v>
+      </c>
+      <c r="M47" s="191"/>
+      <c r="N47" s="191">
+        <v>7.72695</v>
+      </c>
+      <c r="O47" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P47" s="191" t="s">
+        <v>257</v>
+      </c>
       <c r="Q47" s="192"/>
       <c r="R47" s="192"/>
       <c r="S47" s="192"/>
@@ -14296,22 +15062,48 @@
       <c r="AF47" s="192"/>
     </row>
     <row r="48">
-      <c r="A48" s="192"/>
-      <c r="B48" s="192"/>
-      <c r="C48" s="194"/>
-      <c r="D48" s="192"/>
+      <c r="A48" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="193">
+        <v>756.0</v>
+      </c>
+      <c r="D48" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E48" s="192"/>
-      <c r="F48" s="192"/>
-      <c r="G48" s="192"/>
-      <c r="H48" s="192"/>
-      <c r="I48" s="192"/>
-      <c r="J48" s="192"/>
+      <c r="F48" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H48" s="191" t="s">
+        <v>258</v>
+      </c>
+      <c r="I48" s="191" t="s">
+        <v>259</v>
+      </c>
+      <c r="J48" s="191" t="s">
+        <v>259</v>
+      </c>
       <c r="K48" s="192"/>
-      <c r="L48" s="192"/>
-      <c r="M48" s="192"/>
-      <c r="N48" s="192"/>
-      <c r="O48" s="192"/>
-      <c r="P48" s="192"/>
+      <c r="L48" s="191">
+        <v>-3.0</v>
+      </c>
+      <c r="M48" s="191"/>
+      <c r="N48" s="191">
+        <v>11.435416666666667</v>
+      </c>
+      <c r="O48" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P48" s="191" t="s">
+        <v>260</v>
+      </c>
       <c r="Q48" s="192"/>
       <c r="R48" s="192"/>
       <c r="S48" s="192"/>
@@ -14330,22 +15122,48 @@
       <c r="AF48" s="192"/>
     </row>
     <row r="49">
-      <c r="A49" s="192"/>
-      <c r="B49" s="192"/>
-      <c r="C49" s="192"/>
-      <c r="D49" s="192"/>
+      <c r="A49" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="191">
+        <v>89.0</v>
+      </c>
+      <c r="D49" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E49" s="192"/>
-      <c r="F49" s="192"/>
-      <c r="G49" s="192"/>
-      <c r="H49" s="192"/>
-      <c r="I49" s="192"/>
-      <c r="J49" s="192"/>
+      <c r="F49" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H49" s="191" t="s">
+        <v>261</v>
+      </c>
+      <c r="I49" s="191" t="s">
+        <v>262</v>
+      </c>
+      <c r="J49" s="191" t="s">
+        <v>262</v>
+      </c>
       <c r="K49" s="192"/>
-      <c r="L49" s="192"/>
-      <c r="M49" s="192"/>
-      <c r="N49" s="192"/>
-      <c r="O49" s="192"/>
-      <c r="P49" s="192"/>
+      <c r="L49" s="191">
+        <v>-6.0</v>
+      </c>
+      <c r="M49" s="191"/>
+      <c r="N49" s="191">
+        <v>13.3881</v>
+      </c>
+      <c r="O49" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P49" s="191" t="s">
+        <v>263</v>
+      </c>
       <c r="Q49" s="192"/>
       <c r="R49" s="192"/>
       <c r="S49" s="192"/>
@@ -14364,22 +15182,54 @@
       <c r="AF49" s="192"/>
     </row>
     <row r="50">
-      <c r="A50" s="192"/>
-      <c r="B50" s="192"/>
-      <c r="C50" s="192"/>
-      <c r="D50" s="192"/>
-      <c r="E50" s="192"/>
-      <c r="F50" s="192"/>
-      <c r="G50" s="192"/>
-      <c r="H50" s="192"/>
-      <c r="I50" s="192"/>
-      <c r="J50" s="192"/>
-      <c r="K50" s="192"/>
-      <c r="L50" s="192"/>
-      <c r="M50" s="192"/>
-      <c r="N50" s="192"/>
-      <c r="O50" s="192"/>
-      <c r="P50" s="192"/>
+      <c r="A50" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="191">
+        <v>309.0</v>
+      </c>
+      <c r="D50" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E50" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F50" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H50" s="191" t="s">
+        <v>264</v>
+      </c>
+      <c r="I50" s="191" t="s">
+        <v>265</v>
+      </c>
+      <c r="J50" s="191" t="s">
+        <v>266</v>
+      </c>
+      <c r="K50" s="191" t="s">
+        <v>267</v>
+      </c>
+      <c r="L50" s="191">
+        <v>-19.0</v>
+      </c>
+      <c r="M50" s="191">
+        <v>0.0020666666666666667</v>
+      </c>
+      <c r="N50" s="191">
+        <v>7.231683333333334</v>
+      </c>
+      <c r="O50" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P50" s="191" t="s">
+        <v>268</v>
+      </c>
       <c r="Q50" s="192"/>
       <c r="R50" s="192"/>
       <c r="S50" s="192"/>
@@ -14398,22 +15248,48 @@
       <c r="AF50" s="192"/>
     </row>
     <row r="51">
-      <c r="A51" s="192"/>
-      <c r="B51" s="194"/>
-      <c r="C51" s="192"/>
-      <c r="D51" s="192"/>
+      <c r="A51" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" s="191">
+        <v>558.0</v>
+      </c>
+      <c r="D51" s="191">
+        <v>125.0</v>
+      </c>
       <c r="E51" s="192"/>
-      <c r="F51" s="192"/>
-      <c r="G51" s="192"/>
-      <c r="H51" s="192"/>
-      <c r="I51" s="192"/>
-      <c r="J51" s="192"/>
+      <c r="F51" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G51" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" s="191" t="s">
+        <v>269</v>
+      </c>
+      <c r="I51" s="191" t="s">
+        <v>270</v>
+      </c>
+      <c r="J51" s="191" t="s">
+        <v>270</v>
+      </c>
       <c r="K51" s="192"/>
-      <c r="L51" s="192"/>
-      <c r="M51" s="192"/>
-      <c r="N51" s="192"/>
-      <c r="O51" s="192"/>
-      <c r="P51" s="192"/>
+      <c r="L51" s="191">
+        <v>-9.0</v>
+      </c>
+      <c r="M51" s="191"/>
+      <c r="N51" s="191">
+        <v>9.678266666666667</v>
+      </c>
+      <c r="O51" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P51" s="191" t="s">
+        <v>271</v>
+      </c>
       <c r="Q51" s="192"/>
       <c r="R51" s="192"/>
       <c r="S51" s="192"/>
@@ -14432,22 +15308,50 @@
       <c r="AF51" s="192"/>
     </row>
     <row r="52">
-      <c r="A52" s="192"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="194"/>
-      <c r="D52" s="192"/>
-      <c r="E52" s="192"/>
-      <c r="F52" s="192"/>
-      <c r="G52" s="192"/>
-      <c r="H52" s="192"/>
-      <c r="I52" s="192"/>
-      <c r="J52" s="192"/>
+      <c r="A52" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" s="193">
+        <v>553.0</v>
+      </c>
+      <c r="D52" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E52" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G52" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H52" s="191" t="s">
+        <v>272</v>
+      </c>
+      <c r="I52" s="191" t="s">
+        <v>273</v>
+      </c>
+      <c r="J52" s="191" t="s">
+        <v>273</v>
+      </c>
       <c r="K52" s="192"/>
-      <c r="L52" s="192"/>
-      <c r="M52" s="192"/>
-      <c r="N52" s="192"/>
-      <c r="O52" s="192"/>
-      <c r="P52" s="192"/>
+      <c r="L52" s="191">
+        <v>-3.0</v>
+      </c>
+      <c r="M52" s="191"/>
+      <c r="N52" s="191">
+        <v>11.173216666666667</v>
+      </c>
+      <c r="O52" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P52" s="191" t="s">
+        <v>274</v>
+      </c>
       <c r="Q52" s="192"/>
       <c r="R52" s="192"/>
       <c r="S52" s="192"/>
@@ -14466,22 +15370,48 @@
       <c r="AF52" s="192"/>
     </row>
     <row r="53">
-      <c r="A53" s="192"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="194"/>
-      <c r="D53" s="192"/>
+      <c r="A53" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" s="193">
+        <v>394.0</v>
+      </c>
+      <c r="D53" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E53" s="192"/>
-      <c r="F53" s="192"/>
-      <c r="G53" s="192"/>
-      <c r="H53" s="192"/>
-      <c r="I53" s="192"/>
-      <c r="J53" s="192"/>
+      <c r="F53" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H53" s="191" t="s">
+        <v>275</v>
+      </c>
+      <c r="I53" s="191" t="s">
+        <v>276</v>
+      </c>
+      <c r="J53" s="191" t="s">
+        <v>276</v>
+      </c>
       <c r="K53" s="192"/>
-      <c r="L53" s="192"/>
-      <c r="M53" s="192"/>
-      <c r="N53" s="192"/>
-      <c r="O53" s="192"/>
-      <c r="P53" s="192"/>
+      <c r="L53" s="191">
+        <v>3.0</v>
+      </c>
+      <c r="M53" s="191"/>
+      <c r="N53" s="191">
+        <v>18.19175</v>
+      </c>
+      <c r="O53" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P53" s="191" t="s">
+        <v>277</v>
+      </c>
       <c r="Q53" s="192"/>
       <c r="R53" s="192"/>
       <c r="S53" s="192"/>
@@ -14500,22 +15430,54 @@
       <c r="AF53" s="192"/>
     </row>
     <row r="54">
-      <c r="A54" s="192"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="192"/>
-      <c r="D54" s="192"/>
-      <c r="E54" s="192"/>
-      <c r="F54" s="192"/>
-      <c r="G54" s="192"/>
-      <c r="H54" s="192"/>
-      <c r="I54" s="192"/>
-      <c r="J54" s="192"/>
-      <c r="K54" s="192"/>
-      <c r="L54" s="192"/>
-      <c r="M54" s="192"/>
-      <c r="N54" s="192"/>
-      <c r="O54" s="192"/>
-      <c r="P54" s="192"/>
+      <c r="A54" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="191">
+        <v>259.0</v>
+      </c>
+      <c r="D54" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E54" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H54" s="191" t="s">
+        <v>278</v>
+      </c>
+      <c r="I54" s="191" t="s">
+        <v>279</v>
+      </c>
+      <c r="J54" s="191" t="s">
+        <v>280</v>
+      </c>
+      <c r="K54" s="191" t="s">
+        <v>281</v>
+      </c>
+      <c r="L54" s="191">
+        <v>-14.0</v>
+      </c>
+      <c r="M54" s="191">
+        <v>0.0020666666666666667</v>
+      </c>
+      <c r="N54" s="191">
+        <v>8.24735</v>
+      </c>
+      <c r="O54" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P54" s="191" t="s">
+        <v>282</v>
+      </c>
       <c r="Q54" s="192"/>
       <c r="R54" s="192"/>
       <c r="S54" s="192"/>
@@ -14534,22 +15496,48 @@
       <c r="AF54" s="192"/>
     </row>
     <row r="55">
-      <c r="A55" s="192"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="194"/>
-      <c r="D55" s="192"/>
+      <c r="A55" s="191" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C55" s="193">
+        <v>39.0</v>
+      </c>
+      <c r="D55" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E55" s="192"/>
-      <c r="F55" s="192"/>
-      <c r="G55" s="192"/>
-      <c r="H55" s="192"/>
-      <c r="I55" s="192"/>
-      <c r="J55" s="192"/>
+      <c r="F55" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G55" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H55" s="191" t="s">
+        <v>283</v>
+      </c>
+      <c r="I55" s="191" t="s">
+        <v>284</v>
+      </c>
+      <c r="J55" s="191" t="s">
+        <v>284</v>
+      </c>
       <c r="K55" s="192"/>
-      <c r="L55" s="192"/>
-      <c r="M55" s="192"/>
-      <c r="N55" s="192"/>
-      <c r="O55" s="192"/>
-      <c r="P55" s="192"/>
+      <c r="L55" s="191">
+        <v>-3.0</v>
+      </c>
+      <c r="M55" s="191"/>
+      <c r="N55" s="191">
+        <v>1.4128333333333334</v>
+      </c>
+      <c r="O55" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="P55" s="191" t="s">
+        <v>285</v>
+      </c>
       <c r="Q55" s="192"/>
       <c r="R55" s="192"/>
       <c r="S55" s="192"/>
@@ -14568,22 +15556,48 @@
       <c r="AF55" s="192"/>
     </row>
     <row r="56">
-      <c r="A56" s="192"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="194"/>
-      <c r="D56" s="192"/>
+      <c r="A56" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="193">
+        <v>788.0</v>
+      </c>
+      <c r="D56" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E56" s="192"/>
-      <c r="F56" s="192"/>
-      <c r="G56" s="192"/>
-      <c r="H56" s="192"/>
-      <c r="I56" s="192"/>
-      <c r="J56" s="192"/>
+      <c r="F56" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G56" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H56" s="191" t="s">
+        <v>286</v>
+      </c>
+      <c r="I56" s="191" t="s">
+        <v>287</v>
+      </c>
+      <c r="J56" s="191" t="s">
+        <v>287</v>
+      </c>
       <c r="K56" s="192"/>
-      <c r="L56" s="192"/>
-      <c r="M56" s="192"/>
-      <c r="N56" s="192"/>
-      <c r="O56" s="192"/>
-      <c r="P56" s="192"/>
+      <c r="L56" s="191">
+        <v>-1.0</v>
+      </c>
+      <c r="M56" s="191"/>
+      <c r="N56" s="191">
+        <v>13.272466666666666</v>
+      </c>
+      <c r="O56" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P56" s="191" t="s">
+        <v>288</v>
+      </c>
       <c r="Q56" s="192"/>
       <c r="R56" s="192"/>
       <c r="S56" s="192"/>
@@ -14602,22 +15616,48 @@
       <c r="AF56" s="192"/>
     </row>
     <row r="57">
-      <c r="A57" s="192"/>
-      <c r="B57" s="192"/>
-      <c r="C57" s="194"/>
-      <c r="D57" s="192"/>
+      <c r="A57" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C57" s="193">
+        <v>472.75</v>
+      </c>
+      <c r="D57" s="191">
+        <v>137.25</v>
+      </c>
       <c r="E57" s="192"/>
-      <c r="F57" s="192"/>
-      <c r="G57" s="192"/>
-      <c r="H57" s="192"/>
-      <c r="I57" s="192"/>
-      <c r="J57" s="192"/>
+      <c r="F57" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H57" s="191" t="s">
+        <v>289</v>
+      </c>
+      <c r="I57" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="J57" s="191" t="s">
+        <v>290</v>
+      </c>
       <c r="K57" s="192"/>
-      <c r="L57" s="192"/>
-      <c r="M57" s="192"/>
-      <c r="N57" s="192"/>
-      <c r="O57" s="192"/>
-      <c r="P57" s="192"/>
+      <c r="L57" s="191">
+        <v>-4.0</v>
+      </c>
+      <c r="M57" s="191"/>
+      <c r="N57" s="191">
+        <v>10.754633333333333</v>
+      </c>
+      <c r="O57" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P57" s="191" t="s">
+        <v>291</v>
+      </c>
       <c r="Q57" s="192"/>
       <c r="R57" s="192"/>
       <c r="S57" s="192"/>
@@ -14636,22 +15676,48 @@
       <c r="AF57" s="192"/>
     </row>
     <row r="58">
-      <c r="A58" s="192"/>
-      <c r="B58" s="192"/>
-      <c r="C58" s="192"/>
-      <c r="D58" s="192"/>
+      <c r="A58" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="191">
+        <v>204.6</v>
+      </c>
+      <c r="D58" s="191">
+        <v>59.4</v>
+      </c>
       <c r="E58" s="192"/>
-      <c r="F58" s="192"/>
-      <c r="G58" s="192"/>
-      <c r="H58" s="192"/>
-      <c r="I58" s="192"/>
-      <c r="J58" s="192"/>
+      <c r="F58" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G58" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H58" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="I58" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="J58" s="191" t="s">
+        <v>293</v>
+      </c>
       <c r="K58" s="192"/>
-      <c r="L58" s="192"/>
-      <c r="M58" s="192"/>
-      <c r="N58" s="192"/>
-      <c r="O58" s="192"/>
-      <c r="P58" s="192"/>
+      <c r="L58" s="191">
+        <v>-8.0</v>
+      </c>
+      <c r="M58" s="191"/>
+      <c r="N58" s="191">
+        <v>6.565783333333333</v>
+      </c>
+      <c r="O58" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P58" s="191" t="s">
+        <v>117</v>
+      </c>
       <c r="Q58" s="192"/>
       <c r="R58" s="192"/>
       <c r="S58" s="192"/>
@@ -14670,22 +15736,48 @@
       <c r="AF58" s="192"/>
     </row>
     <row r="59">
-      <c r="A59" s="192"/>
-      <c r="B59" s="192"/>
-      <c r="C59" s="194"/>
-      <c r="D59" s="192"/>
+      <c r="A59" s="191" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="193">
+        <v>368.0</v>
+      </c>
+      <c r="D59" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
+      <c r="F59" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G59" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H59" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="I59" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="J59" s="191" t="s">
+        <v>295</v>
+      </c>
       <c r="K59" s="192"/>
-      <c r="L59" s="192"/>
-      <c r="M59" s="192"/>
-      <c r="N59" s="192"/>
-      <c r="O59" s="192"/>
-      <c r="P59" s="192"/>
+      <c r="L59" s="191">
+        <v>3.0</v>
+      </c>
+      <c r="M59" s="191"/>
+      <c r="N59" s="191">
+        <v>8.662683333333334</v>
+      </c>
+      <c r="O59" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="P59" s="191" t="s">
+        <v>296</v>
+      </c>
       <c r="Q59" s="192"/>
       <c r="R59" s="192"/>
       <c r="S59" s="192"/>
@@ -14704,22 +15796,50 @@
       <c r="AF59" s="192"/>
     </row>
     <row r="60">
-      <c r="A60" s="192"/>
-      <c r="B60" s="192"/>
-      <c r="C60" s="192"/>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
+      <c r="A60" s="191" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60" s="191">
+        <v>329.0</v>
+      </c>
+      <c r="D60" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E60" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="F60" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G60" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H60" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="I60" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="J60" s="191" t="s">
+        <v>299</v>
+      </c>
       <c r="K60" s="192"/>
-      <c r="L60" s="192"/>
-      <c r="M60" s="192"/>
-      <c r="N60" s="192"/>
-      <c r="O60" s="192"/>
-      <c r="P60" s="192"/>
+      <c r="L60" s="191">
+        <v>-6.0</v>
+      </c>
+      <c r="M60" s="191"/>
+      <c r="N60" s="191">
+        <v>8.975766666666667</v>
+      </c>
+      <c r="O60" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P60" s="191" t="s">
+        <v>300</v>
+      </c>
       <c r="Q60" s="192"/>
       <c r="R60" s="192"/>
       <c r="S60" s="192"/>
@@ -14738,22 +15858,48 @@
       <c r="AF60" s="192"/>
     </row>
     <row r="61">
-      <c r="A61" s="192"/>
-      <c r="B61" s="192"/>
-      <c r="C61" s="194"/>
-      <c r="D61" s="192"/>
+      <c r="A61" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="193">
+        <v>522.58</v>
+      </c>
+      <c r="D61" s="191">
+        <v>124.42</v>
+      </c>
       <c r="E61" s="192"/>
-      <c r="F61" s="192"/>
-      <c r="G61" s="192"/>
-      <c r="H61" s="192"/>
-      <c r="I61" s="192"/>
-      <c r="J61" s="192"/>
+      <c r="F61" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G61" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H61" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="I61" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="J61" s="191" t="s">
+        <v>302</v>
+      </c>
       <c r="K61" s="192"/>
-      <c r="L61" s="192"/>
-      <c r="M61" s="192"/>
-      <c r="N61" s="192"/>
-      <c r="O61" s="192"/>
-      <c r="P61" s="192"/>
+      <c r="L61" s="191">
+        <v>-4.0</v>
+      </c>
+      <c r="M61" s="191"/>
+      <c r="N61" s="191">
+        <v>10.597183333333334</v>
+      </c>
+      <c r="O61" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P61" s="191" t="s">
+        <v>303</v>
+      </c>
       <c r="Q61" s="192"/>
       <c r="R61" s="192"/>
       <c r="S61" s="192"/>
@@ -14772,22 +15918,54 @@
       <c r="AF61" s="192"/>
     </row>
     <row r="62">
-      <c r="A62" s="192"/>
-      <c r="B62" s="192"/>
-      <c r="C62" s="192"/>
-      <c r="D62" s="192"/>
-      <c r="E62" s="192"/>
-      <c r="F62" s="192"/>
-      <c r="G62" s="192"/>
-      <c r="H62" s="192"/>
-      <c r="I62" s="192"/>
-      <c r="J62" s="192"/>
-      <c r="K62" s="192"/>
-      <c r="L62" s="192"/>
-      <c r="M62" s="192"/>
-      <c r="N62" s="192"/>
-      <c r="O62" s="192"/>
-      <c r="P62" s="192"/>
+      <c r="A62" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C62" s="191">
+        <v>-42.0</v>
+      </c>
+      <c r="D62" s="191">
+        <v>500.0</v>
+      </c>
+      <c r="E62" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F62" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G62" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H62" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="I62" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="J62" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="K62" s="191" t="s">
+        <v>307</v>
+      </c>
+      <c r="L62" s="191">
+        <v>-5.0</v>
+      </c>
+      <c r="M62" s="191">
+        <v>0.0018833333333333334</v>
+      </c>
+      <c r="N62" s="191">
+        <v>15.42275</v>
+      </c>
+      <c r="O62" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P62" s="191" t="s">
+        <v>308</v>
+      </c>
       <c r="Q62" s="192"/>
       <c r="R62" s="192"/>
       <c r="S62" s="192"/>
@@ -14806,22 +15984,48 @@
       <c r="AF62" s="192"/>
     </row>
     <row r="63">
-      <c r="A63" s="192"/>
-      <c r="B63" s="192"/>
-      <c r="C63" s="192"/>
-      <c r="D63" s="192"/>
+      <c r="A63" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="191">
+        <v>793.0</v>
+      </c>
+      <c r="D63" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E63" s="192"/>
-      <c r="F63" s="192"/>
-      <c r="G63" s="192"/>
-      <c r="H63" s="192"/>
-      <c r="I63" s="192"/>
-      <c r="J63" s="192"/>
+      <c r="F63" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G63" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H63" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="I63" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="J63" s="191" t="s">
+        <v>310</v>
+      </c>
       <c r="K63" s="192"/>
-      <c r="L63" s="192"/>
-      <c r="M63" s="192"/>
-      <c r="N63" s="192"/>
-      <c r="O63" s="192"/>
-      <c r="P63" s="192"/>
+      <c r="L63" s="191">
+        <v>-1.0</v>
+      </c>
+      <c r="M63" s="191"/>
+      <c r="N63" s="191">
+        <v>13.774366666666667</v>
+      </c>
+      <c r="O63" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P63" s="191" t="s">
+        <v>311</v>
+      </c>
       <c r="Q63" s="192"/>
       <c r="R63" s="192"/>
       <c r="S63" s="192"/>
@@ -14840,22 +16044,54 @@
       <c r="AF63" s="192"/>
     </row>
     <row r="64">
-      <c r="A64" s="192"/>
-      <c r="B64" s="192"/>
-      <c r="C64" s="192"/>
-      <c r="D64" s="192"/>
-      <c r="E64" s="192"/>
-      <c r="F64" s="192"/>
-      <c r="G64" s="192"/>
-      <c r="H64" s="192"/>
-      <c r="I64" s="192"/>
-      <c r="J64" s="192"/>
-      <c r="K64" s="192"/>
-      <c r="L64" s="192"/>
-      <c r="M64" s="192"/>
-      <c r="N64" s="192"/>
-      <c r="O64" s="192"/>
-      <c r="P64" s="192"/>
+      <c r="A64" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="191">
+        <v>453.0</v>
+      </c>
+      <c r="D64" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E64" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G64" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="I64" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="J64" s="191" t="s">
+        <v>314</v>
+      </c>
+      <c r="K64" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="L64" s="191">
+        <v>-1.0</v>
+      </c>
+      <c r="M64" s="191">
+        <v>0.002416666666666667</v>
+      </c>
+      <c r="N64" s="191">
+        <v>23.0693</v>
+      </c>
+      <c r="O64" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P64" s="191" t="s">
+        <v>316</v>
+      </c>
       <c r="Q64" s="192"/>
       <c r="R64" s="192"/>
       <c r="S64" s="192"/>
@@ -14874,22 +16110,50 @@
       <c r="AF64" s="192"/>
     </row>
     <row r="65">
-      <c r="A65" s="192"/>
-      <c r="B65" s="192"/>
-      <c r="C65" s="194"/>
-      <c r="D65" s="192"/>
-      <c r="E65" s="192"/>
-      <c r="F65" s="192"/>
-      <c r="G65" s="192"/>
-      <c r="H65" s="192"/>
-      <c r="I65" s="192"/>
-      <c r="J65" s="192"/>
+      <c r="A65" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C65" s="193">
+        <v>329.0</v>
+      </c>
+      <c r="D65" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E65" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F65" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G65" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H65" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="I65" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="J65" s="191" t="s">
+        <v>318</v>
+      </c>
       <c r="K65" s="192"/>
-      <c r="L65" s="192"/>
-      <c r="M65" s="192"/>
-      <c r="N65" s="192"/>
-      <c r="O65" s="192"/>
-      <c r="P65" s="192"/>
+      <c r="L65" s="191">
+        <v>-4.0</v>
+      </c>
+      <c r="M65" s="191"/>
+      <c r="N65" s="191">
+        <v>10.6354</v>
+      </c>
+      <c r="O65" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P65" s="191" t="s">
+        <v>319</v>
+      </c>
       <c r="Q65" s="192"/>
       <c r="R65" s="192"/>
       <c r="S65" s="192"/>
@@ -14908,22 +16172,48 @@
       <c r="AF65" s="192"/>
     </row>
     <row r="66">
-      <c r="A66" s="192"/>
-      <c r="B66" s="192"/>
-      <c r="C66" s="192"/>
-      <c r="D66" s="192"/>
+      <c r="A66" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C66" s="191">
+        <v>1070.0</v>
+      </c>
+      <c r="D66" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E66" s="192"/>
-      <c r="F66" s="192"/>
-      <c r="G66" s="192"/>
-      <c r="H66" s="192"/>
-      <c r="I66" s="192"/>
-      <c r="J66" s="192"/>
+      <c r="F66" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G66" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H66" s="191" t="s">
+        <v>320</v>
+      </c>
+      <c r="I66" s="191" t="s">
+        <v>321</v>
+      </c>
+      <c r="J66" s="191" t="s">
+        <v>321</v>
+      </c>
       <c r="K66" s="192"/>
-      <c r="L66" s="192"/>
-      <c r="M66" s="192"/>
-      <c r="N66" s="192"/>
-      <c r="O66" s="192"/>
-      <c r="P66" s="192"/>
+      <c r="L66" s="191">
+        <v>-1.0</v>
+      </c>
+      <c r="M66" s="191"/>
+      <c r="N66" s="191">
+        <v>13.780183333333333</v>
+      </c>
+      <c r="O66" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P66" s="191" t="s">
+        <v>322</v>
+      </c>
       <c r="Q66" s="192"/>
       <c r="R66" s="192"/>
       <c r="S66" s="192"/>
@@ -14942,22 +16232,54 @@
       <c r="AF66" s="192"/>
     </row>
     <row r="67">
-      <c r="A67" s="192"/>
-      <c r="B67" s="192"/>
-      <c r="C67" s="192"/>
-      <c r="D67" s="192"/>
-      <c r="E67" s="192"/>
-      <c r="F67" s="192"/>
-      <c r="G67" s="192"/>
-      <c r="H67" s="192"/>
-      <c r="I67" s="192"/>
-      <c r="J67" s="192"/>
-      <c r="K67" s="192"/>
-      <c r="L67" s="192"/>
-      <c r="M67" s="192"/>
-      <c r="N67" s="192"/>
-      <c r="O67" s="192"/>
-      <c r="P67" s="192"/>
+      <c r="A67" s="191" t="s">
+        <v>102</v>
+      </c>
+      <c r="B67" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C67" s="191">
+        <v>1235.9</v>
+      </c>
+      <c r="D67" s="191">
+        <v>218.1</v>
+      </c>
+      <c r="E67" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G67" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H67" s="191" t="s">
+        <v>323</v>
+      </c>
+      <c r="I67" s="191" t="s">
+        <v>324</v>
+      </c>
+      <c r="J67" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="K67" s="191" t="s">
+        <v>326</v>
+      </c>
+      <c r="L67" s="191">
+        <v>-44.0</v>
+      </c>
+      <c r="M67" s="191">
+        <v>0.0023333333333333335</v>
+      </c>
+      <c r="N67" s="191">
+        <v>42.2378</v>
+      </c>
+      <c r="O67" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="P67" s="191" t="s">
+        <v>327</v>
+      </c>
       <c r="Q67" s="192"/>
       <c r="R67" s="192"/>
       <c r="S67" s="192"/>
@@ -14976,22 +16298,54 @@
       <c r="AF67" s="192"/>
     </row>
     <row r="68">
-      <c r="A68" s="192"/>
-      <c r="B68" s="192"/>
-      <c r="C68" s="192"/>
-      <c r="D68" s="192"/>
-      <c r="E68" s="192"/>
-      <c r="F68" s="192"/>
-      <c r="G68" s="192"/>
-      <c r="H68" s="192"/>
-      <c r="I68" s="192"/>
-      <c r="J68" s="192"/>
-      <c r="K68" s="192"/>
-      <c r="L68" s="192"/>
-      <c r="M68" s="192"/>
-      <c r="N68" s="192"/>
-      <c r="O68" s="192"/>
-      <c r="P68" s="192"/>
+      <c r="A68" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" s="191">
+        <v>240.0</v>
+      </c>
+      <c r="D68" s="191">
+        <v>9.0</v>
+      </c>
+      <c r="E68" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F68" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G68" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H68" s="191" t="s">
+        <v>328</v>
+      </c>
+      <c r="I68" s="191" t="s">
+        <v>329</v>
+      </c>
+      <c r="J68" s="191" t="s">
+        <v>330</v>
+      </c>
+      <c r="K68" s="191" t="s">
+        <v>331</v>
+      </c>
+      <c r="L68" s="191">
+        <v>-8.0</v>
+      </c>
+      <c r="M68" s="191">
+        <v>21.92995</v>
+      </c>
+      <c r="N68" s="191">
+        <v>109.9884</v>
+      </c>
+      <c r="O68" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P68" s="191" t="s">
+        <v>282</v>
+      </c>
       <c r="Q68" s="192"/>
       <c r="R68" s="192"/>
       <c r="S68" s="192"/>
@@ -15010,22 +16364,50 @@
       <c r="AF68" s="192"/>
     </row>
     <row r="69">
-      <c r="A69" s="192"/>
-      <c r="B69" s="192"/>
-      <c r="C69" s="192"/>
-      <c r="D69" s="192"/>
-      <c r="E69" s="192"/>
-      <c r="F69" s="192"/>
-      <c r="G69" s="192"/>
-      <c r="H69" s="192"/>
-      <c r="I69" s="192"/>
-      <c r="J69" s="192"/>
+      <c r="A69" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" s="191">
+        <v>528.0</v>
+      </c>
+      <c r="D69" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E69" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G69" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H69" s="191" t="s">
+        <v>332</v>
+      </c>
+      <c r="I69" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="J69" s="191" t="s">
+        <v>333</v>
+      </c>
       <c r="K69" s="192"/>
-      <c r="L69" s="192"/>
-      <c r="M69" s="192"/>
-      <c r="N69" s="192"/>
-      <c r="O69" s="192"/>
-      <c r="P69" s="192"/>
+      <c r="L69" s="191">
+        <v>-1.0</v>
+      </c>
+      <c r="M69" s="191"/>
+      <c r="N69" s="191">
+        <v>13.20405</v>
+      </c>
+      <c r="O69" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P69" s="191" t="s">
+        <v>334</v>
+      </c>
       <c r="Q69" s="192"/>
       <c r="R69" s="192"/>
       <c r="S69" s="192"/>
@@ -15044,22 +16426,50 @@
       <c r="AF69" s="192"/>
     </row>
     <row r="70">
-      <c r="A70" s="192"/>
-      <c r="B70" s="192"/>
-      <c r="C70" s="194"/>
-      <c r="D70" s="192"/>
-      <c r="E70" s="192"/>
-      <c r="F70" s="192"/>
-      <c r="G70" s="192"/>
-      <c r="H70" s="192"/>
-      <c r="I70" s="192"/>
-      <c r="J70" s="192"/>
+      <c r="A70" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C70" s="193">
+        <v>388.0</v>
+      </c>
+      <c r="D70" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E70" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G70" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H70" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="I70" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="J70" s="191" t="s">
+        <v>336</v>
+      </c>
       <c r="K70" s="192"/>
-      <c r="L70" s="192"/>
-      <c r="M70" s="192"/>
-      <c r="N70" s="192"/>
-      <c r="O70" s="192"/>
-      <c r="P70" s="192"/>
+      <c r="L70" s="191">
+        <v>-1.0</v>
+      </c>
+      <c r="M70" s="191"/>
+      <c r="N70" s="191">
+        <v>13.15385</v>
+      </c>
+      <c r="O70" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P70" s="191" t="s">
+        <v>337</v>
+      </c>
       <c r="Q70" s="192"/>
       <c r="R70" s="192"/>
       <c r="S70" s="192"/>
@@ -15078,22 +16488,50 @@
       <c r="AF70" s="192"/>
     </row>
     <row r="71">
-      <c r="A71" s="192"/>
-      <c r="B71" s="192"/>
-      <c r="C71" s="192"/>
-      <c r="D71" s="192"/>
-      <c r="E71" s="192"/>
-      <c r="F71" s="192"/>
-      <c r="G71" s="192"/>
-      <c r="H71" s="192"/>
-      <c r="I71" s="192"/>
-      <c r="J71" s="192"/>
+      <c r="A71" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="191">
+        <v>399.0</v>
+      </c>
+      <c r="D71" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E71" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F71" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G71" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H71" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="I71" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="J71" s="191" t="s">
+        <v>339</v>
+      </c>
       <c r="K71" s="192"/>
-      <c r="L71" s="192"/>
-      <c r="M71" s="192"/>
-      <c r="N71" s="192"/>
-      <c r="O71" s="192"/>
-      <c r="P71" s="192"/>
+      <c r="L71" s="191">
+        <v>-2.0</v>
+      </c>
+      <c r="M71" s="191"/>
+      <c r="N71" s="191">
+        <v>12.304166666666667</v>
+      </c>
+      <c r="O71" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P71" s="191" t="s">
+        <v>340</v>
+      </c>
       <c r="Q71" s="192"/>
       <c r="R71" s="192"/>
       <c r="S71" s="192"/>
@@ -15112,22 +16550,54 @@
       <c r="AF71" s="192"/>
     </row>
     <row r="72">
-      <c r="A72" s="192"/>
-      <c r="B72" s="192"/>
-      <c r="C72" s="192"/>
-      <c r="D72" s="192"/>
-      <c r="E72" s="192"/>
-      <c r="F72" s="192"/>
-      <c r="G72" s="192"/>
-      <c r="H72" s="192"/>
-      <c r="I72" s="192"/>
-      <c r="J72" s="192"/>
-      <c r="K72" s="192"/>
-      <c r="L72" s="192"/>
-      <c r="M72" s="192"/>
-      <c r="N72" s="192"/>
-      <c r="O72" s="192"/>
-      <c r="P72" s="192"/>
+      <c r="A72" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B72" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C72" s="191">
+        <v>319.0</v>
+      </c>
+      <c r="D72" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E72" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F72" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G72" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H72" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I72" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="J72" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="K72" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="L72" s="191">
+        <v>5.0</v>
+      </c>
+      <c r="M72" s="191">
+        <v>0.017633333333333334</v>
+      </c>
+      <c r="N72" s="191">
+        <v>22.511733333333332</v>
+      </c>
+      <c r="O72" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P72" s="191" t="s">
+        <v>345</v>
+      </c>
       <c r="Q72" s="192"/>
       <c r="R72" s="192"/>
       <c r="S72" s="192"/>
@@ -15146,22 +16616,50 @@
       <c r="AF72" s="192"/>
     </row>
     <row r="73">
-      <c r="A73" s="192"/>
-      <c r="B73" s="192"/>
-      <c r="C73" s="192"/>
-      <c r="D73" s="192"/>
-      <c r="E73" s="192"/>
-      <c r="F73" s="192"/>
-      <c r="G73" s="192"/>
-      <c r="H73" s="192"/>
-      <c r="I73" s="192"/>
-      <c r="J73" s="192"/>
+      <c r="A73" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C73" s="191">
+        <v>264.0</v>
+      </c>
+      <c r="D73" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E73" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F73" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H73" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="I73" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="J73" s="191" t="s">
+        <v>347</v>
+      </c>
       <c r="K73" s="192"/>
-      <c r="L73" s="192"/>
-      <c r="M73" s="192"/>
-      <c r="N73" s="192"/>
-      <c r="O73" s="192"/>
-      <c r="P73" s="192"/>
+      <c r="L73" s="191">
+        <v>-2.0</v>
+      </c>
+      <c r="M73" s="191"/>
+      <c r="N73" s="191">
+        <v>12.897433333333334</v>
+      </c>
+      <c r="O73" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P73" s="191" t="s">
+        <v>348</v>
+      </c>
       <c r="Q73" s="192"/>
       <c r="R73" s="192"/>
       <c r="S73" s="192"/>
@@ -15180,22 +16678,50 @@
       <c r="AF73" s="192"/>
     </row>
     <row r="74">
-      <c r="A74" s="192"/>
-      <c r="B74" s="194"/>
-      <c r="C74" s="194"/>
-      <c r="D74" s="192"/>
-      <c r="E74" s="192"/>
-      <c r="F74" s="192"/>
-      <c r="G74" s="192"/>
-      <c r="H74" s="192"/>
-      <c r="I74" s="192"/>
-      <c r="J74" s="192"/>
+      <c r="A74" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="C74" s="193">
+        <v>354.0</v>
+      </c>
+      <c r="D74" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E74" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F74" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H74" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="I74" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="J74" s="191" t="s">
+        <v>350</v>
+      </c>
       <c r="K74" s="192"/>
-      <c r="L74" s="192"/>
-      <c r="M74" s="192"/>
-      <c r="N74" s="192"/>
-      <c r="O74" s="192"/>
-      <c r="P74" s="192"/>
+      <c r="L74" s="191">
+        <v>-6.0</v>
+      </c>
+      <c r="M74" s="191"/>
+      <c r="N74" s="191">
+        <v>8.288783333333333</v>
+      </c>
+      <c r="O74" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P74" s="191" t="s">
+        <v>351</v>
+      </c>
       <c r="Q74" s="192"/>
       <c r="R74" s="192"/>
       <c r="S74" s="192"/>
@@ -15214,22 +16740,54 @@
       <c r="AF74" s="192"/>
     </row>
     <row r="75">
-      <c r="A75" s="192"/>
-      <c r="B75" s="192"/>
-      <c r="C75" s="192"/>
-      <c r="D75" s="192"/>
-      <c r="E75" s="192"/>
-      <c r="F75" s="192"/>
-      <c r="G75" s="192"/>
-      <c r="H75" s="192"/>
-      <c r="I75" s="192"/>
-      <c r="J75" s="192"/>
-      <c r="K75" s="192"/>
-      <c r="L75" s="192"/>
-      <c r="M75" s="192"/>
-      <c r="N75" s="192"/>
-      <c r="O75" s="192"/>
-      <c r="P75" s="192"/>
+      <c r="A75" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C75" s="191">
+        <v>563.0</v>
+      </c>
+      <c r="D75" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E75" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F75" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G75" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H75" s="191" t="s">
+        <v>352</v>
+      </c>
+      <c r="I75" s="191" t="s">
+        <v>353</v>
+      </c>
+      <c r="J75" s="191" t="s">
+        <v>354</v>
+      </c>
+      <c r="K75" s="191" t="s">
+        <v>355</v>
+      </c>
+      <c r="L75" s="191">
+        <v>-8.0</v>
+      </c>
+      <c r="M75" s="191">
+        <v>0.0018166666666666667</v>
+      </c>
+      <c r="N75" s="191">
+        <v>19.2112</v>
+      </c>
+      <c r="O75" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P75" s="191" t="s">
+        <v>356</v>
+      </c>
       <c r="Q75" s="192"/>
       <c r="R75" s="192"/>
       <c r="S75" s="192"/>
@@ -15248,22 +16806,54 @@
       <c r="AF75" s="192"/>
     </row>
     <row r="76">
-      <c r="A76" s="192"/>
-      <c r="B76" s="192"/>
-      <c r="C76" s="192"/>
-      <c r="D76" s="192"/>
-      <c r="E76" s="192"/>
-      <c r="F76" s="192"/>
-      <c r="G76" s="192"/>
-      <c r="H76" s="192"/>
-      <c r="I76" s="192"/>
-      <c r="J76" s="192"/>
-      <c r="K76" s="192"/>
-      <c r="L76" s="192"/>
-      <c r="M76" s="192"/>
-      <c r="N76" s="192"/>
-      <c r="O76" s="192"/>
-      <c r="P76" s="192"/>
+      <c r="A76" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B76" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C76" s="191">
+        <v>309.0</v>
+      </c>
+      <c r="D76" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E76" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F76" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G76" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H76" s="191" t="s">
+        <v>357</v>
+      </c>
+      <c r="I76" s="191" t="s">
+        <v>358</v>
+      </c>
+      <c r="J76" s="191" t="s">
+        <v>359</v>
+      </c>
+      <c r="K76" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="L76" s="191">
+        <v>2.0</v>
+      </c>
+      <c r="M76" s="191">
+        <v>0.002266666666666667</v>
+      </c>
+      <c r="N76" s="191">
+        <v>17.532283333333332</v>
+      </c>
+      <c r="O76" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P76" s="191" t="s">
+        <v>345</v>
+      </c>
       <c r="Q76" s="192"/>
       <c r="R76" s="192"/>
       <c r="S76" s="192"/>
@@ -15282,22 +16872,50 @@
       <c r="AF76" s="192"/>
     </row>
     <row r="77">
-      <c r="A77" s="192"/>
-      <c r="B77" s="192"/>
-      <c r="C77" s="194"/>
-      <c r="D77" s="192"/>
-      <c r="E77" s="192"/>
-      <c r="F77" s="192"/>
-      <c r="G77" s="192"/>
-      <c r="H77" s="192"/>
-      <c r="I77" s="192"/>
-      <c r="J77" s="192"/>
+      <c r="A77" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B77" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C77" s="193">
+        <v>329.0</v>
+      </c>
+      <c r="D77" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E77" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F77" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H77" s="191" t="s">
+        <v>361</v>
+      </c>
+      <c r="I77" s="191" t="s">
+        <v>362</v>
+      </c>
+      <c r="J77" s="191" t="s">
+        <v>362</v>
+      </c>
       <c r="K77" s="192"/>
-      <c r="L77" s="192"/>
-      <c r="M77" s="192"/>
-      <c r="N77" s="192"/>
-      <c r="O77" s="192"/>
-      <c r="P77" s="192"/>
+      <c r="L77" s="191">
+        <v>-5.0</v>
+      </c>
+      <c r="M77" s="191"/>
+      <c r="N77" s="191">
+        <v>9.98895</v>
+      </c>
+      <c r="O77" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P77" s="191" t="s">
+        <v>363</v>
+      </c>
       <c r="Q77" s="192"/>
       <c r="R77" s="192"/>
       <c r="S77" s="192"/>
@@ -15316,22 +16934,48 @@
       <c r="AF77" s="192"/>
     </row>
     <row r="78">
-      <c r="A78" s="192"/>
-      <c r="B78" s="192"/>
-      <c r="C78" s="192"/>
-      <c r="D78" s="192"/>
+      <c r="A78" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C78" s="191">
+        <v>289.0</v>
+      </c>
+      <c r="D78" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E78" s="192"/>
-      <c r="F78" s="192"/>
-      <c r="G78" s="192"/>
-      <c r="H78" s="192"/>
-      <c r="I78" s="192"/>
-      <c r="J78" s="192"/>
+      <c r="F78" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G78" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H78" s="191" t="s">
+        <v>364</v>
+      </c>
+      <c r="I78" s="191" t="s">
+        <v>365</v>
+      </c>
+      <c r="J78" s="191" t="s">
+        <v>365</v>
+      </c>
       <c r="K78" s="192"/>
-      <c r="L78" s="192"/>
-      <c r="M78" s="192"/>
-      <c r="N78" s="192"/>
-      <c r="O78" s="192"/>
-      <c r="P78" s="192"/>
+      <c r="L78" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="M78" s="191"/>
+      <c r="N78" s="191">
+        <v>15.574983333333334</v>
+      </c>
+      <c r="O78" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P78" s="191" t="s">
+        <v>366</v>
+      </c>
       <c r="Q78" s="192"/>
       <c r="R78" s="192"/>
       <c r="S78" s="192"/>
@@ -15350,22 +16994,48 @@
       <c r="AF78" s="192"/>
     </row>
     <row r="79">
-      <c r="A79" s="192"/>
-      <c r="B79" s="192"/>
-      <c r="C79" s="192"/>
-      <c r="D79" s="192"/>
+      <c r="A79" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79" s="191">
+        <v>394.0</v>
+      </c>
+      <c r="D79" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E79" s="192"/>
-      <c r="F79" s="192"/>
-      <c r="G79" s="192"/>
-      <c r="H79" s="192"/>
-      <c r="I79" s="192"/>
-      <c r="J79" s="192"/>
+      <c r="F79" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G79" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H79" s="191" t="s">
+        <v>367</v>
+      </c>
+      <c r="I79" s="191" t="s">
+        <v>368</v>
+      </c>
+      <c r="J79" s="191" t="s">
+        <v>368</v>
+      </c>
       <c r="K79" s="192"/>
-      <c r="L79" s="192"/>
-      <c r="M79" s="192"/>
-      <c r="N79" s="192"/>
-      <c r="O79" s="192"/>
-      <c r="P79" s="192"/>
+      <c r="L79" s="191">
+        <v>3.0</v>
+      </c>
+      <c r="M79" s="191"/>
+      <c r="N79" s="191">
+        <v>18.5053</v>
+      </c>
+      <c r="O79" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P79" s="191" t="s">
+        <v>369</v>
+      </c>
       <c r="Q79" s="192"/>
       <c r="R79" s="192"/>
       <c r="S79" s="192"/>
@@ -15384,22 +17054,48 @@
       <c r="AF79" s="192"/>
     </row>
     <row r="80">
-      <c r="A80" s="192"/>
-      <c r="B80" s="192"/>
-      <c r="C80" s="194"/>
-      <c r="D80" s="192"/>
+      <c r="A80" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" s="193">
+        <v>423.0</v>
+      </c>
+      <c r="D80" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E80" s="192"/>
-      <c r="F80" s="192"/>
-      <c r="G80" s="192"/>
-      <c r="H80" s="192"/>
-      <c r="I80" s="192"/>
-      <c r="J80" s="192"/>
+      <c r="F80" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H80" s="191" t="s">
+        <v>370</v>
+      </c>
+      <c r="I80" s="191" t="s">
+        <v>371</v>
+      </c>
+      <c r="J80" s="191" t="s">
+        <v>371</v>
+      </c>
       <c r="K80" s="192"/>
-      <c r="L80" s="192"/>
-      <c r="M80" s="192"/>
-      <c r="N80" s="192"/>
-      <c r="O80" s="192"/>
-      <c r="P80" s="192"/>
+      <c r="L80" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="M80" s="191"/>
+      <c r="N80" s="191">
+        <v>15.452</v>
+      </c>
+      <c r="O80" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P80" s="191" t="s">
+        <v>372</v>
+      </c>
       <c r="Q80" s="192"/>
       <c r="R80" s="192"/>
       <c r="S80" s="192"/>
@@ -15418,22 +17114,54 @@
       <c r="AF80" s="192"/>
     </row>
     <row r="81">
-      <c r="A81" s="192"/>
-      <c r="B81" s="192"/>
-      <c r="C81" s="192"/>
-      <c r="D81" s="192"/>
-      <c r="E81" s="192"/>
-      <c r="F81" s="192"/>
-      <c r="G81" s="192"/>
-      <c r="H81" s="192"/>
-      <c r="I81" s="192"/>
-      <c r="J81" s="192"/>
-      <c r="K81" s="192"/>
-      <c r="L81" s="192"/>
-      <c r="M81" s="192"/>
-      <c r="N81" s="192"/>
-      <c r="O81" s="192"/>
-      <c r="P81" s="192"/>
+      <c r="A81" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C81" s="191">
+        <v>359.0</v>
+      </c>
+      <c r="D81" s="191">
+        <v>15.0</v>
+      </c>
+      <c r="E81" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F81" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G81" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H81" s="191" t="s">
+        <v>373</v>
+      </c>
+      <c r="I81" s="191" t="s">
+        <v>374</v>
+      </c>
+      <c r="J81" s="191" t="s">
+        <v>375</v>
+      </c>
+      <c r="K81" s="191" t="s">
+        <v>376</v>
+      </c>
+      <c r="L81" s="191">
+        <v>8.0</v>
+      </c>
+      <c r="M81" s="191">
+        <v>1.0522666666666667</v>
+      </c>
+      <c r="N81" s="191">
+        <v>22.673183333333334</v>
+      </c>
+      <c r="O81" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P81" s="191" t="s">
+        <v>377</v>
+      </c>
       <c r="Q81" s="192"/>
       <c r="R81" s="192"/>
       <c r="S81" s="192"/>
@@ -15452,22 +17180,50 @@
       <c r="AF81" s="192"/>
     </row>
     <row r="82">
-      <c r="A82" s="192"/>
-      <c r="B82" s="192"/>
-      <c r="C82" s="194"/>
-      <c r="D82" s="192"/>
-      <c r="E82" s="192"/>
-      <c r="F82" s="192"/>
-      <c r="G82" s="192"/>
-      <c r="H82" s="192"/>
-      <c r="I82" s="192"/>
-      <c r="J82" s="192"/>
+      <c r="A82" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" s="193">
+        <v>243.0</v>
+      </c>
+      <c r="D82" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E82" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F82" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G82" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H82" s="191" t="s">
+        <v>378</v>
+      </c>
+      <c r="I82" s="191" t="s">
+        <v>379</v>
+      </c>
+      <c r="J82" s="191" t="s">
+        <v>379</v>
+      </c>
       <c r="K82" s="192"/>
-      <c r="L82" s="192"/>
-      <c r="M82" s="192"/>
-      <c r="N82" s="192"/>
-      <c r="O82" s="192"/>
-      <c r="P82" s="192"/>
+      <c r="L82" s="191">
+        <v>-5.0</v>
+      </c>
+      <c r="M82" s="191"/>
+      <c r="N82" s="191">
+        <v>9.625933333333334</v>
+      </c>
+      <c r="O82" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P82" s="191" t="s">
+        <v>380</v>
+      </c>
       <c r="Q82" s="192"/>
       <c r="R82" s="192"/>
       <c r="S82" s="192"/>
@@ -15486,22 +17242,50 @@
       <c r="AF82" s="192"/>
     </row>
     <row r="83">
-      <c r="A83" s="192"/>
-      <c r="B83" s="192"/>
-      <c r="C83" s="192"/>
-      <c r="D83" s="192"/>
-      <c r="E83" s="192"/>
-      <c r="F83" s="192"/>
-      <c r="G83" s="192"/>
-      <c r="H83" s="192"/>
-      <c r="I83" s="192"/>
-      <c r="J83" s="192"/>
+      <c r="A83" s="191" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" s="191">
+        <v>264.0</v>
+      </c>
+      <c r="D83" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E83" s="191" t="s">
+        <v>381</v>
+      </c>
+      <c r="F83" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G83" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H83" s="191" t="s">
+        <v>382</v>
+      </c>
+      <c r="I83" s="191" t="s">
+        <v>383</v>
+      </c>
+      <c r="J83" s="191" t="s">
+        <v>383</v>
+      </c>
       <c r="K83" s="192"/>
-      <c r="L83" s="192"/>
-      <c r="M83" s="192"/>
-      <c r="N83" s="192"/>
-      <c r="O83" s="192"/>
-      <c r="P83" s="192"/>
+      <c r="L83" s="191">
+        <v>-8.0</v>
+      </c>
+      <c r="M83" s="191"/>
+      <c r="N83" s="191">
+        <v>6.7185</v>
+      </c>
+      <c r="O83" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P83" s="191" t="s">
+        <v>384</v>
+      </c>
       <c r="Q83" s="192"/>
       <c r="R83" s="192"/>
       <c r="S83" s="192"/>
@@ -15520,22 +17304,54 @@
       <c r="AF83" s="192"/>
     </row>
     <row r="84">
-      <c r="A84" s="192"/>
-      <c r="B84" s="192"/>
-      <c r="C84" s="194"/>
-      <c r="D84" s="192"/>
-      <c r="E84" s="192"/>
-      <c r="F84" s="192"/>
-      <c r="G84" s="192"/>
-      <c r="H84" s="192"/>
-      <c r="I84" s="192"/>
-      <c r="J84" s="192"/>
-      <c r="K84" s="192"/>
-      <c r="L84" s="192"/>
-      <c r="M84" s="192"/>
-      <c r="N84" s="192"/>
-      <c r="O84" s="192"/>
-      <c r="P84" s="192"/>
+      <c r="A84" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C84" s="193">
+        <v>259.0</v>
+      </c>
+      <c r="D84" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E84" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F84" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G84" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H84" s="191" t="s">
+        <v>385</v>
+      </c>
+      <c r="I84" s="191" t="s">
+        <v>386</v>
+      </c>
+      <c r="J84" s="191" t="s">
+        <v>387</v>
+      </c>
+      <c r="K84" s="191" t="s">
+        <v>388</v>
+      </c>
+      <c r="L84" s="191">
+        <v>-14.0</v>
+      </c>
+      <c r="M84" s="191">
+        <v>0.0019833333333333335</v>
+      </c>
+      <c r="N84" s="191">
+        <v>3.0616166666666667</v>
+      </c>
+      <c r="O84" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P84" s="191" t="s">
+        <v>389</v>
+      </c>
       <c r="Q84" s="192"/>
       <c r="R84" s="192"/>
       <c r="S84" s="192"/>
@@ -15554,22 +17370,54 @@
       <c r="AF84" s="192"/>
     </row>
     <row r="85">
-      <c r="A85" s="192"/>
-      <c r="B85" s="192"/>
-      <c r="C85" s="194"/>
-      <c r="D85" s="192"/>
-      <c r="E85" s="192"/>
-      <c r="F85" s="192"/>
-      <c r="G85" s="192"/>
-      <c r="H85" s="192"/>
-      <c r="I85" s="192"/>
-      <c r="J85" s="192"/>
-      <c r="K85" s="192"/>
-      <c r="L85" s="192"/>
-      <c r="M85" s="192"/>
-      <c r="N85" s="192"/>
-      <c r="O85" s="192"/>
-      <c r="P85" s="192"/>
+      <c r="A85" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" s="193">
+        <v>356.0</v>
+      </c>
+      <c r="D85" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E85" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F85" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G85" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H85" s="191" t="s">
+        <v>390</v>
+      </c>
+      <c r="I85" s="191" t="s">
+        <v>391</v>
+      </c>
+      <c r="J85" s="191" t="s">
+        <v>392</v>
+      </c>
+      <c r="K85" s="191" t="s">
+        <v>393</v>
+      </c>
+      <c r="L85" s="191">
+        <v>9.0</v>
+      </c>
+      <c r="M85" s="191">
+        <v>0.0019666666666666665</v>
+      </c>
+      <c r="N85" s="191">
+        <v>5.960333333333334</v>
+      </c>
+      <c r="O85" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P85" s="191" t="s">
+        <v>394</v>
+      </c>
       <c r="Q85" s="192"/>
       <c r="R85" s="192"/>
       <c r="S85" s="192"/>
@@ -15588,22 +17436,50 @@
       <c r="AF85" s="192"/>
     </row>
     <row r="86">
-      <c r="A86" s="192"/>
-      <c r="B86" s="192"/>
-      <c r="C86" s="192"/>
-      <c r="D86" s="192"/>
-      <c r="E86" s="192"/>
-      <c r="F86" s="192"/>
-      <c r="G86" s="192"/>
-      <c r="H86" s="192"/>
-      <c r="I86" s="192"/>
-      <c r="J86" s="192"/>
+      <c r="A86" s="191" t="s">
+        <v>118</v>
+      </c>
+      <c r="B86" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C86" s="191">
+        <v>658.0</v>
+      </c>
+      <c r="D86" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E86" s="191" t="s">
+        <v>395</v>
+      </c>
+      <c r="F86" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G86" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H86" s="191" t="s">
+        <v>396</v>
+      </c>
+      <c r="I86" s="191" t="s">
+        <v>397</v>
+      </c>
+      <c r="J86" s="191" t="s">
+        <v>397</v>
+      </c>
       <c r="K86" s="192"/>
-      <c r="L86" s="192"/>
-      <c r="M86" s="192"/>
-      <c r="N86" s="192"/>
-      <c r="O86" s="192"/>
-      <c r="P86" s="192"/>
+      <c r="L86" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="M86" s="191"/>
+      <c r="N86" s="191">
+        <v>14.524366666666667</v>
+      </c>
+      <c r="O86" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P86" s="191" t="s">
+        <v>398</v>
+      </c>
       <c r="Q86" s="192"/>
       <c r="R86" s="192"/>
       <c r="S86" s="192"/>
@@ -15622,22 +17498,48 @@
       <c r="AF86" s="192"/>
     </row>
     <row r="87">
-      <c r="A87" s="192"/>
-      <c r="B87" s="192"/>
-      <c r="C87" s="192"/>
-      <c r="D87" s="192"/>
+      <c r="A87" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B87" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" s="191">
+        <v>388.0</v>
+      </c>
+      <c r="D87" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E87" s="192"/>
-      <c r="F87" s="192"/>
-      <c r="G87" s="192"/>
-      <c r="H87" s="192"/>
-      <c r="I87" s="192"/>
-      <c r="J87" s="192"/>
+      <c r="F87" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G87" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H87" s="191" t="s">
+        <v>399</v>
+      </c>
+      <c r="I87" s="191" t="s">
+        <v>400</v>
+      </c>
+      <c r="J87" s="191" t="s">
+        <v>400</v>
+      </c>
       <c r="K87" s="192"/>
-      <c r="L87" s="192"/>
-      <c r="M87" s="192"/>
-      <c r="N87" s="192"/>
-      <c r="O87" s="192"/>
-      <c r="P87" s="192"/>
+      <c r="L87" s="191">
+        <v>-7.0</v>
+      </c>
+      <c r="M87" s="191"/>
+      <c r="N87" s="191">
+        <v>7.280666666666667</v>
+      </c>
+      <c r="O87" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P87" s="191" t="s">
+        <v>401</v>
+      </c>
       <c r="Q87" s="192"/>
       <c r="R87" s="192"/>
       <c r="S87" s="192"/>
@@ -15656,22 +17558,50 @@
       <c r="AF87" s="192"/>
     </row>
     <row r="88">
-      <c r="A88" s="192"/>
-      <c r="B88" s="192"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="192"/>
-      <c r="E88" s="192"/>
-      <c r="F88" s="192"/>
-      <c r="G88" s="192"/>
-      <c r="H88" s="192"/>
-      <c r="I88" s="192"/>
-      <c r="J88" s="192"/>
+      <c r="A88" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C88" s="191">
+        <v>233.0</v>
+      </c>
+      <c r="D88" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E88" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F88" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G88" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H88" s="191" t="s">
+        <v>402</v>
+      </c>
+      <c r="I88" s="191" t="s">
+        <v>403</v>
+      </c>
+      <c r="J88" s="191" t="s">
+        <v>403</v>
+      </c>
       <c r="K88" s="192"/>
-      <c r="L88" s="192"/>
-      <c r="M88" s="192"/>
-      <c r="N88" s="192"/>
-      <c r="O88" s="192"/>
-      <c r="P88" s="192"/>
+      <c r="L88" s="191">
+        <v>-3.0</v>
+      </c>
+      <c r="M88" s="191"/>
+      <c r="N88" s="191">
+        <v>11.968216666666667</v>
+      </c>
+      <c r="O88" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P88" s="191" t="s">
+        <v>404</v>
+      </c>
       <c r="Q88" s="192"/>
       <c r="R88" s="192"/>
       <c r="S88" s="192"/>
@@ -15690,22 +17620,54 @@
       <c r="AF88" s="192"/>
     </row>
     <row r="89">
-      <c r="A89" s="192"/>
-      <c r="B89" s="192"/>
-      <c r="C89" s="194"/>
-      <c r="D89" s="192"/>
-      <c r="E89" s="192"/>
-      <c r="F89" s="192"/>
-      <c r="G89" s="192"/>
-      <c r="H89" s="192"/>
-      <c r="I89" s="192"/>
-      <c r="J89" s="192"/>
-      <c r="K89" s="192"/>
-      <c r="L89" s="192"/>
-      <c r="M89" s="192"/>
-      <c r="N89" s="192"/>
-      <c r="O89" s="192"/>
-      <c r="P89" s="192"/>
+      <c r="A89" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C89" s="193">
+        <v>638.0</v>
+      </c>
+      <c r="D89" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E89" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F89" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G89" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H89" s="191" t="s">
+        <v>405</v>
+      </c>
+      <c r="I89" s="191" t="s">
+        <v>406</v>
+      </c>
+      <c r="J89" s="191" t="s">
+        <v>407</v>
+      </c>
+      <c r="K89" s="191" t="s">
+        <v>408</v>
+      </c>
+      <c r="L89" s="191">
+        <v>4.0</v>
+      </c>
+      <c r="M89" s="191">
+        <v>0.0018333333333333333</v>
+      </c>
+      <c r="N89" s="191">
+        <v>9.756783333333333</v>
+      </c>
+      <c r="O89" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P89" s="191" t="s">
+        <v>409</v>
+      </c>
       <c r="Q89" s="192"/>
       <c r="R89" s="192"/>
       <c r="S89" s="192"/>
@@ -15724,22 +17686,54 @@
       <c r="AF89" s="192"/>
     </row>
     <row r="90">
-      <c r="A90" s="192"/>
-      <c r="B90" s="192"/>
-      <c r="C90" s="194"/>
-      <c r="D90" s="192"/>
-      <c r="E90" s="192"/>
-      <c r="F90" s="192"/>
-      <c r="G90" s="192"/>
-      <c r="H90" s="192"/>
-      <c r="I90" s="192"/>
-      <c r="J90" s="192"/>
-      <c r="K90" s="192"/>
-      <c r="L90" s="192"/>
-      <c r="M90" s="192"/>
-      <c r="N90" s="192"/>
-      <c r="O90" s="192"/>
-      <c r="P90" s="192"/>
+      <c r="A90" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C90" s="193">
+        <v>376.0</v>
+      </c>
+      <c r="D90" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E90" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F90" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G90" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H90" s="191" t="s">
+        <v>410</v>
+      </c>
+      <c r="I90" s="191" t="s">
+        <v>411</v>
+      </c>
+      <c r="J90" s="191" t="s">
+        <v>412</v>
+      </c>
+      <c r="K90" s="191" t="s">
+        <v>413</v>
+      </c>
+      <c r="L90" s="191">
+        <v>12.0</v>
+      </c>
+      <c r="M90" s="191">
+        <v>0.002</v>
+      </c>
+      <c r="N90" s="191">
+        <v>6.208383333333333</v>
+      </c>
+      <c r="O90" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P90" s="191" t="s">
+        <v>414</v>
+      </c>
       <c r="Q90" s="192"/>
       <c r="R90" s="192"/>
       <c r="S90" s="192"/>
@@ -15758,22 +17752,48 @@
       <c r="AF90" s="192"/>
     </row>
     <row r="91">
-      <c r="A91" s="192"/>
-      <c r="B91" s="192"/>
-      <c r="C91" s="192"/>
-      <c r="D91" s="192"/>
+      <c r="A91" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B91" s="191" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" s="191">
+        <v>618.0</v>
+      </c>
+      <c r="D91" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E91" s="192"/>
-      <c r="F91" s="192"/>
-      <c r="G91" s="192"/>
-      <c r="H91" s="192"/>
-      <c r="I91" s="192"/>
-      <c r="J91" s="192"/>
+      <c r="F91" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G91" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H91" s="191" t="s">
+        <v>415</v>
+      </c>
+      <c r="I91" s="191" t="s">
+        <v>416</v>
+      </c>
+      <c r="J91" s="191" t="s">
+        <v>416</v>
+      </c>
       <c r="K91" s="192"/>
-      <c r="L91" s="192"/>
-      <c r="M91" s="192"/>
-      <c r="N91" s="192"/>
-      <c r="O91" s="192"/>
-      <c r="P91" s="192"/>
+      <c r="L91" s="191">
+        <v>3.0</v>
+      </c>
+      <c r="M91" s="191"/>
+      <c r="N91" s="191">
+        <v>18.437066666666666</v>
+      </c>
+      <c r="O91" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P91" s="191" t="s">
+        <v>417</v>
+      </c>
       <c r="Q91" s="192"/>
       <c r="R91" s="192"/>
       <c r="S91" s="192"/>
@@ -15792,22 +17812,54 @@
       <c r="AF91" s="192"/>
     </row>
     <row r="92">
-      <c r="A92" s="192"/>
-      <c r="B92" s="192"/>
-      <c r="C92" s="192"/>
-      <c r="D92" s="192"/>
-      <c r="E92" s="192"/>
-      <c r="F92" s="192"/>
-      <c r="G92" s="192"/>
-      <c r="H92" s="192"/>
-      <c r="I92" s="192"/>
-      <c r="J92" s="192"/>
-      <c r="K92" s="192"/>
-      <c r="L92" s="192"/>
-      <c r="M92" s="192"/>
-      <c r="N92" s="192"/>
-      <c r="O92" s="192"/>
-      <c r="P92" s="192"/>
+      <c r="A92" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" s="191">
+        <v>1536.0</v>
+      </c>
+      <c r="D92" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E92" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F92" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G92" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H92" s="191" t="s">
+        <v>418</v>
+      </c>
+      <c r="I92" s="191" t="s">
+        <v>419</v>
+      </c>
+      <c r="J92" s="191" t="s">
+        <v>420</v>
+      </c>
+      <c r="K92" s="191" t="s">
+        <v>421</v>
+      </c>
+      <c r="L92" s="191">
+        <v>-3.0</v>
+      </c>
+      <c r="M92" s="191">
+        <v>0.005083333333333333</v>
+      </c>
+      <c r="N92" s="191">
+        <v>19.391816666666667</v>
+      </c>
+      <c r="O92" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P92" s="191" t="s">
+        <v>422</v>
+      </c>
       <c r="Q92" s="192"/>
       <c r="R92" s="192"/>
       <c r="S92" s="192"/>
@@ -15826,22 +17878,50 @@
       <c r="AF92" s="192"/>
     </row>
     <row r="93">
-      <c r="A93" s="192"/>
-      <c r="B93" s="192"/>
-      <c r="C93" s="194"/>
-      <c r="D93" s="192"/>
-      <c r="E93" s="192"/>
-      <c r="F93" s="192"/>
-      <c r="G93" s="192"/>
-      <c r="H93" s="192"/>
-      <c r="I93" s="192"/>
-      <c r="J93" s="192"/>
+      <c r="A93" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B93" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" s="193">
+        <v>352.0</v>
+      </c>
+      <c r="D93" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E93" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F93" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G93" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H93" s="191" t="s">
+        <v>423</v>
+      </c>
+      <c r="I93" s="191" t="s">
+        <v>424</v>
+      </c>
+      <c r="J93" s="191" t="s">
+        <v>424</v>
+      </c>
       <c r="K93" s="192"/>
-      <c r="L93" s="192"/>
-      <c r="M93" s="192"/>
-      <c r="N93" s="192"/>
-      <c r="O93" s="192"/>
-      <c r="P93" s="192"/>
+      <c r="L93" s="191">
+        <v>6.0</v>
+      </c>
+      <c r="M93" s="191"/>
+      <c r="N93" s="191">
+        <v>21.324133333333332</v>
+      </c>
+      <c r="O93" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P93" s="191" t="s">
+        <v>425</v>
+      </c>
       <c r="Q93" s="192"/>
       <c r="R93" s="192"/>
       <c r="S93" s="192"/>
@@ -15860,22 +17940,48 @@
       <c r="AF93" s="192"/>
     </row>
     <row r="94">
-      <c r="A94" s="192"/>
-      <c r="B94" s="192"/>
-      <c r="C94" s="192"/>
-      <c r="D94" s="192"/>
+      <c r="A94" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B94" s="191" t="s">
+        <v>83</v>
+      </c>
+      <c r="C94" s="191">
+        <v>605.0</v>
+      </c>
+      <c r="D94" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E94" s="192"/>
-      <c r="F94" s="192"/>
-      <c r="G94" s="192"/>
-      <c r="H94" s="192"/>
-      <c r="I94" s="192"/>
-      <c r="J94" s="192"/>
+      <c r="F94" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G94" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H94" s="191" t="s">
+        <v>426</v>
+      </c>
+      <c r="I94" s="191" t="s">
+        <v>427</v>
+      </c>
+      <c r="J94" s="191" t="s">
+        <v>427</v>
+      </c>
       <c r="K94" s="192"/>
-      <c r="L94" s="192"/>
-      <c r="M94" s="192"/>
-      <c r="N94" s="192"/>
-      <c r="O94" s="192"/>
-      <c r="P94" s="192"/>
+      <c r="L94" s="191">
+        <v>6.0</v>
+      </c>
+      <c r="M94" s="191"/>
+      <c r="N94" s="191">
+        <v>21.492066666666666</v>
+      </c>
+      <c r="O94" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P94" s="191" t="s">
+        <v>428</v>
+      </c>
       <c r="Q94" s="192"/>
       <c r="R94" s="192"/>
       <c r="S94" s="192"/>
@@ -15894,22 +18000,50 @@
       <c r="AF94" s="192"/>
     </row>
     <row r="95">
-      <c r="A95" s="192"/>
-      <c r="B95" s="192"/>
-      <c r="C95" s="192"/>
-      <c r="D95" s="192"/>
-      <c r="E95" s="192"/>
-      <c r="F95" s="192"/>
-      <c r="G95" s="192"/>
-      <c r="H95" s="192"/>
-      <c r="I95" s="192"/>
-      <c r="J95" s="192"/>
+      <c r="A95" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B95" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" s="191">
+        <v>558.0</v>
+      </c>
+      <c r="D95" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E95" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F95" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G95" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H95" s="191" t="s">
+        <v>429</v>
+      </c>
+      <c r="I95" s="191" t="s">
+        <v>430</v>
+      </c>
+      <c r="J95" s="191" t="s">
+        <v>430</v>
+      </c>
       <c r="K95" s="192"/>
-      <c r="L95" s="192"/>
-      <c r="M95" s="192"/>
-      <c r="N95" s="192"/>
-      <c r="O95" s="192"/>
-      <c r="P95" s="192"/>
+      <c r="L95" s="191">
+        <v>2.0</v>
+      </c>
+      <c r="M95" s="191"/>
+      <c r="N95" s="191">
+        <v>17.507066666666667</v>
+      </c>
+      <c r="O95" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P95" s="191" t="s">
+        <v>431</v>
+      </c>
       <c r="Q95" s="192"/>
       <c r="R95" s="192"/>
       <c r="S95" s="192"/>
@@ -15928,22 +18062,48 @@
       <c r="AF95" s="192"/>
     </row>
     <row r="96">
-      <c r="A96" s="192"/>
-      <c r="B96" s="192"/>
-      <c r="C96" s="192"/>
-      <c r="D96" s="192"/>
+      <c r="A96" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B96" s="191" t="s">
+        <v>83</v>
+      </c>
+      <c r="C96" s="191">
+        <v>5679.0</v>
+      </c>
+      <c r="D96" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E96" s="192"/>
-      <c r="F96" s="192"/>
-      <c r="G96" s="192"/>
-      <c r="H96" s="192"/>
-      <c r="I96" s="192"/>
-      <c r="J96" s="192"/>
+      <c r="F96" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G96" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H96" s="191" t="s">
+        <v>432</v>
+      </c>
+      <c r="I96" s="191" t="s">
+        <v>433</v>
+      </c>
+      <c r="J96" s="191" t="s">
+        <v>433</v>
+      </c>
       <c r="K96" s="192"/>
-      <c r="L96" s="192"/>
-      <c r="M96" s="192"/>
-      <c r="N96" s="192"/>
-      <c r="O96" s="192"/>
-      <c r="P96" s="192"/>
+      <c r="L96" s="191">
+        <v>13.0</v>
+      </c>
+      <c r="M96" s="191"/>
+      <c r="N96" s="191">
+        <v>30.469733333333334</v>
+      </c>
+      <c r="O96" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P96" s="191" t="s">
+        <v>434</v>
+      </c>
       <c r="Q96" s="192"/>
       <c r="R96" s="192"/>
       <c r="S96" s="192"/>
@@ -15962,22 +18122,48 @@
       <c r="AF96" s="192"/>
     </row>
     <row r="97">
-      <c r="A97" s="192"/>
-      <c r="B97" s="192"/>
-      <c r="C97" s="194"/>
-      <c r="D97" s="192"/>
+      <c r="A97" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B97" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C97" s="193">
+        <v>247.0</v>
+      </c>
+      <c r="D97" s="191">
+        <v>62.0</v>
+      </c>
       <c r="E97" s="192"/>
-      <c r="F97" s="192"/>
-      <c r="G97" s="192"/>
-      <c r="H97" s="192"/>
-      <c r="I97" s="192"/>
-      <c r="J97" s="192"/>
+      <c r="F97" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G97" s="191" t="s">
+        <v>435</v>
+      </c>
+      <c r="H97" s="191" t="s">
+        <v>436</v>
+      </c>
+      <c r="I97" s="191" t="s">
+        <v>437</v>
+      </c>
+      <c r="J97" s="191" t="s">
+        <v>437</v>
+      </c>
       <c r="K97" s="192"/>
-      <c r="L97" s="192"/>
-      <c r="M97" s="192"/>
-      <c r="N97" s="192"/>
-      <c r="O97" s="192"/>
-      <c r="P97" s="192"/>
+      <c r="L97" s="191">
+        <v>-12.0</v>
+      </c>
+      <c r="M97" s="191"/>
+      <c r="N97" s="191">
+        <v>6.979066666666666</v>
+      </c>
+      <c r="O97" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P97" s="191" t="s">
+        <v>438</v>
+      </c>
       <c r="Q97" s="192"/>
       <c r="R97" s="192"/>
       <c r="S97" s="192"/>
@@ -15996,22 +18182,48 @@
       <c r="AF97" s="192"/>
     </row>
     <row r="98">
-      <c r="A98" s="192"/>
-      <c r="B98" s="192"/>
-      <c r="C98" s="192"/>
-      <c r="D98" s="192"/>
+      <c r="A98" s="191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B98" s="191" t="s">
+        <v>83</v>
+      </c>
+      <c r="C98" s="191">
+        <v>523.0</v>
+      </c>
+      <c r="D98" s="191">
+        <v>0.0</v>
+      </c>
       <c r="E98" s="192"/>
-      <c r="F98" s="192"/>
-      <c r="G98" s="192"/>
-      <c r="H98" s="192"/>
-      <c r="I98" s="192"/>
-      <c r="J98" s="192"/>
+      <c r="F98" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G98" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H98" s="191" t="s">
+        <v>439</v>
+      </c>
+      <c r="I98" s="191" t="s">
+        <v>440</v>
+      </c>
+      <c r="J98" s="191" t="s">
+        <v>440</v>
+      </c>
       <c r="K98" s="192"/>
-      <c r="L98" s="192"/>
-      <c r="M98" s="192"/>
-      <c r="N98" s="192"/>
-      <c r="O98" s="192"/>
-      <c r="P98" s="192"/>
+      <c r="L98" s="191">
+        <v>-2.0</v>
+      </c>
+      <c r="M98" s="191"/>
+      <c r="N98" s="191">
+        <v>12.4963</v>
+      </c>
+      <c r="O98" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P98" s="191" t="s">
+        <v>441</v>
+      </c>
       <c r="Q98" s="192"/>
       <c r="R98" s="192"/>
       <c r="S98" s="192"/>
@@ -16030,22 +18242,50 @@
       <c r="AF98" s="192"/>
     </row>
     <row r="99">
-      <c r="A99" s="192"/>
-      <c r="B99" s="192"/>
-      <c r="C99" s="194"/>
-      <c r="D99" s="192"/>
-      <c r="E99" s="192"/>
-      <c r="F99" s="192"/>
-      <c r="G99" s="192"/>
-      <c r="H99" s="192"/>
-      <c r="I99" s="192"/>
-      <c r="J99" s="192"/>
+      <c r="A99" s="191" t="s">
+        <v>126</v>
+      </c>
+      <c r="B99" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" s="193">
+        <v>702.0</v>
+      </c>
+      <c r="D99" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E99" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="F99" s="191" t="s">
+        <v>84</v>
+      </c>
+      <c r="G99" s="191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H99" s="191" t="s">
+        <v>442</v>
+      </c>
+      <c r="I99" s="191" t="s">
+        <v>443</v>
+      </c>
+      <c r="J99" s="191" t="s">
+        <v>443</v>
+      </c>
       <c r="K99" s="192"/>
-      <c r="L99" s="192"/>
-      <c r="M99" s="192"/>
-      <c r="N99" s="192"/>
-      <c r="O99" s="192"/>
-      <c r="P99" s="192"/>
+      <c r="L99" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="M99" s="191"/>
+      <c r="N99" s="191">
+        <v>15.754733333333334</v>
+      </c>
+      <c r="O99" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="P99" s="191" t="s">
+        <v>444</v>
+      </c>
       <c r="Q99" s="192"/>
       <c r="R99" s="192"/>
       <c r="S99" s="192"/>
@@ -16064,22 +18304,54 @@
       <c r="AF99" s="192"/>
     </row>
     <row r="100">
-      <c r="A100" s="192"/>
-      <c r="B100" s="192"/>
-      <c r="C100" s="194"/>
-      <c r="D100" s="192"/>
-      <c r="E100" s="192"/>
-      <c r="F100" s="192"/>
-      <c r="G100" s="192"/>
-      <c r="H100" s="192"/>
-      <c r="I100" s="192"/>
-      <c r="J100" s="192"/>
-      <c r="K100" s="192"/>
-      <c r="L100" s="192"/>
-      <c r="M100" s="192"/>
-      <c r="N100" s="192"/>
-      <c r="O100" s="192"/>
-      <c r="P100" s="192"/>
+      <c r="A100" s="191" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C100" s="193">
+        <v>618.0</v>
+      </c>
+      <c r="D100" s="191">
+        <v>0.0</v>
+      </c>
+      <c r="E100" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="G100" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H100" s="191" t="s">
+        <v>445</v>
+      </c>
+      <c r="I100" s="191" t="s">
+        <v>446</v>
+      </c>
+      <c r="J100" s="191" t="s">
+        <v>447</v>
+      </c>
+      <c r="K100" s="191" t="s">
+        <v>448</v>
+      </c>
+      <c r="L100" s="191">
+        <v>-9.0</v>
+      </c>
+      <c r="M100" s="191">
+        <v>0.002533333333333333</v>
+      </c>
+      <c r="N100" s="191">
+        <v>12.910733333333333</v>
+      </c>
+      <c r="O100" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="P100" s="191" t="s">
+        <v>449</v>
+      </c>
       <c r="Q100" s="192"/>
       <c r="R100" s="192"/>
       <c r="S100" s="192"/>
@@ -16098,22 +18370,48 @@
       <c r="AF100" s="192"/>
     </row>
     <row r="101">
-      <c r="A101" s="192"/>
-      <c r="B101" s="192"/>
-      <c r="C101" s="194"/>
-      <c r="D101" s="192"/>
+      <c r="A101" s="191" t="s">
+        <v>90</v>
+      </c>
+      <c r="B101" s="191" t="s">
+        <v>91</v>
+      </c>
+      <c r="C101" s="193">
+        <v>598.0</v>
+      </c>
+      <c r="D101" s="191">
+        <v>149.0</v>
+      </c>
       <c r="E101" s="192"/>
-      <c r="F101" s="192"/>
-      <c r="G101" s="192"/>
-      <c r="H101" s="192"/>
-      <c r="I101" s="192"/>
-      <c r="J101" s="192"/>
+      <c r="F101" s="191" t="s">
+        <v>103</v>
+      </c>
+      <c r="G101" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="H101" s="191" t="s">
+        <v>450</v>
+      </c>
+      <c r="I101" s="191" t="s">
+        <v>451</v>
+      </c>
+      <c r="J101" s="191" t="s">
+        <v>451</v>
+      </c>
       <c r="K101" s="192"/>
-      <c r="L101" s="192"/>
-      <c r="M101" s="192"/>
-      <c r="N101" s="192"/>
-      <c r="O101" s="192"/>
-      <c r="P101" s="192"/>
+      <c r="L101" s="191">
+        <v>-3.0</v>
+      </c>
+      <c r="M101" s="191"/>
+      <c r="N101" s="191">
+        <v>29.536583333333333</v>
+      </c>
+      <c r="O101" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="P101" s="191" t="s">
+        <v>452</v>
+      </c>
       <c r="Q101" s="192"/>
       <c r="R101" s="192"/>
       <c r="S101" s="192"/>
@@ -25412,73 +27710,73 @@
         <v>1</v>
       </c>
       <c r="B1" s="191" t="s">
-        <v>238</v>
+        <v>453</v>
       </c>
       <c r="C1" s="191" t="s">
-        <v>239</v>
+        <v>454</v>
       </c>
       <c r="D1" s="191" t="s">
-        <v>240</v>
+        <v>455</v>
       </c>
       <c r="E1" s="191" t="s">
-        <v>241</v>
+        <v>456</v>
       </c>
       <c r="F1" s="191" t="s">
-        <v>242</v>
+        <v>457</v>
       </c>
       <c r="G1" s="191" t="s">
-        <v>243</v>
+        <v>458</v>
       </c>
       <c r="H1" s="191" t="s">
-        <v>244</v>
+        <v>459</v>
       </c>
       <c r="I1" s="191" t="s">
-        <v>245</v>
+        <v>460</v>
       </c>
       <c r="J1" s="191" t="s">
-        <v>246</v>
+        <v>461</v>
       </c>
       <c r="K1" s="191" t="s">
-        <v>247</v>
+        <v>462</v>
       </c>
       <c r="L1" s="191" t="s">
-        <v>248</v>
+        <v>463</v>
       </c>
       <c r="M1" s="191" t="s">
-        <v>249</v>
+        <v>464</v>
       </c>
       <c r="N1" s="191" t="s">
-        <v>250</v>
+        <v>465</v>
       </c>
       <c r="O1" s="191" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P1" s="191" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q1" s="191" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="191" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S1" s="191" t="s">
-        <v>251</v>
+        <v>466</v>
       </c>
       <c r="T1" s="191" t="s">
-        <v>252</v>
+        <v>467</v>
       </c>
       <c r="U1" s="191" t="s">
-        <v>253</v>
+        <v>468</v>
       </c>
       <c r="V1" s="191" t="s">
-        <v>254</v>
+        <v>469</v>
       </c>
       <c r="W1" s="191" t="s">
-        <v>255</v>
+        <v>470</v>
       </c>
       <c r="X1" s="191" t="s">
-        <v>256</v>
+        <v>471</v>
       </c>
       <c r="Y1" s="191" t="s">
         <v>13</v>
@@ -25493,64 +27791,64 @@
         <v>3</v>
       </c>
       <c r="AC1" s="191" t="s">
-        <v>257</v>
+        <v>472</v>
       </c>
       <c r="AD1" s="191" t="s">
         <v>2</v>
       </c>
       <c r="AE1" s="191" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF1" s="191" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AG1" s="191" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AH1" s="191" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI1" s="191" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AJ1" s="191" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AK1" s="191" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL1" s="191" t="s">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="AM1" s="191" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AN1" s="191" t="s">
-        <v>259</v>
+        <v>474</v>
       </c>
       <c r="AO1" s="191" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP1" s="191" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AQ1" s="191" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AR1" s="191" t="s">
-        <v>260</v>
+        <v>475</v>
       </c>
       <c r="AS1" s="191" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AT1" s="191" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AU1" s="191" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AV1" s="191" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
@@ -25558,19 +27856,19 @@
         <v>45524.0</v>
       </c>
       <c r="B2" s="191" t="s">
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="C2" s="191" t="s">
-        <v>262</v>
+        <v>477</v>
       </c>
       <c r="D2" s="196" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="196" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2" s="196" t="s">
-        <v>263</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3">
@@ -25578,19 +27876,19 @@
         <v>45524.0</v>
       </c>
       <c r="B3" s="191" t="s">
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="C3" s="191" t="s">
-        <v>264</v>
+        <v>479</v>
       </c>
       <c r="D3" s="196" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" s="196" t="s">
-        <v>25</v>
+        <v>480</v>
       </c>
       <c r="G3" s="196" t="s">
-        <v>265</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4">
@@ -25598,19 +27896,19 @@
         <v>45524.0</v>
       </c>
       <c r="B4" s="191" t="s">
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="H4" s="191" t="s">
-        <v>266</v>
+        <v>482</v>
       </c>
       <c r="I4" s="196" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J4" s="196" t="s">
-        <v>267</v>
+        <v>483</v>
       </c>
       <c r="L4" s="196" t="s">
-        <v>268</v>
+        <v>484</v>
       </c>
       <c r="M4" s="197">
         <v>9.0</v>
@@ -25621,19 +27919,19 @@
         <v>45524.0</v>
       </c>
       <c r="B5" s="191" t="s">
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="H5" s="191" t="s">
-        <v>269</v>
+        <v>485</v>
       </c>
       <c r="I5" s="196" t="s">
-        <v>267</v>
+        <v>483</v>
       </c>
       <c r="J5" s="196" t="s">
-        <v>270</v>
+        <v>28</v>
       </c>
       <c r="L5" s="196" t="s">
-        <v>271</v>
+        <v>486</v>
       </c>
       <c r="M5" s="197">
         <v>13.0</v>
@@ -25650,19 +27948,19 @@
         <v>45524.0</v>
       </c>
       <c r="B6" s="191" t="s">
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="H6" s="191" t="s">
-        <v>272</v>
+        <v>487</v>
       </c>
       <c r="I6" s="196" t="s">
-        <v>273</v>
+        <v>25</v>
       </c>
       <c r="J6" s="196" t="s">
-        <v>25</v>
+        <v>480</v>
       </c>
       <c r="L6" s="196" t="s">
-        <v>274</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7">
@@ -25670,16 +27968,16 @@
         <v>45524.0</v>
       </c>
       <c r="B7" s="191" t="s">
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="P7" s="197">
         <v>7.0</v>
       </c>
       <c r="Q7" s="191" t="s">
-        <v>262</v>
+        <v>477</v>
       </c>
       <c r="R7" s="191" t="s">
-        <v>264</v>
+        <v>479</v>
       </c>
       <c r="S7" s="197">
         <v>8461.0</v>
@@ -25733,7 +28031,7 @@
         <v>7.0</v>
       </c>
       <c r="AM7" s="191" t="s">
-        <v>275</v>
+        <v>489</v>
       </c>
       <c r="AN7" s="197">
         <v>1.0</v>
@@ -25903,10 +28201,10 @@
     </row>
     <row r="4">
       <c r="A4" s="202" t="s">
-        <v>276</v>
+        <v>490</v>
       </c>
       <c r="B4" s="202" t="s">
-        <v>277</v>
+        <v>491</v>
       </c>
       <c r="C4" s="198" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -26032,7 +28330,7 @@
       </c>
       <c r="B6" s="203" t="str">
         <f>IF(OR(E6=Report!$B$1, F6=Report!$B$1, G6=Report!$B$1, H6=Report!$B$1), D6, "")</f>
-        <v/>
+        <v>Sova Martin</v>
       </c>
       <c r="C6" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -26158,7 +28456,7 @@
       </c>
       <c r="B8" s="203" t="str">
         <f>IF(OR(E8=Report!$B$1, F8=Report!$B$1, G8=Report!$B$1, H8=Report!$B$1), D8, "")</f>
-        <v/>
+        <v>Ahurieva Viktoriia</v>
       </c>
       <c r="C8" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -26290,7 +28588,7 @@
       </c>
       <c r="B10" s="203" t="str">
         <f>IF(OR(E10=Report!$B$1, F10=Report!$B$1, G10=Report!$B$1, H10=Report!$B$1), D10, "")</f>
-        <v/>
+        <v>Šebesta Tomáš</v>
       </c>
       <c r="C10" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -26539,7 +28837,7 @@
       </c>
       <c r="B14" s="203" t="str">
         <f>IF(OR(E14=Report!$B$1, F14=Report!$B$1, G14=Report!$B$1, H14=Report!$B$1), D14, "")</f>
-        <v/>
+        <v>Coufal Jakub</v>
       </c>
       <c r="C14" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -26851,7 +29149,7 @@
       </c>
       <c r="B19" s="203" t="str">
         <f>IF(OR(E19=Report!$B$1, F19=Report!$B$1, G19=Report!$B$1, H19=Report!$B$1), D19, "")</f>
-        <v>Rothová Anastasia</v>
+        <v/>
       </c>
       <c r="C19" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -26967,11 +29265,11 @@
     <row r="21">
       <c r="A21" s="198" t="str">
         <f>IF(AND(B21&lt;&gt;"", C21=TRUE, E21=Report!$B$1), B21, "")</f>
-        <v/>
+        <v>Hegedüs Erik</v>
       </c>
       <c r="B21" s="203" t="str">
         <f>IF(OR(E21=Report!$B$1, F21=Report!$B$1, G21=Report!$B$1, H21=Report!$B$1), D21, "")</f>
-        <v/>
+        <v>Hegedüs Erik</v>
       </c>
       <c r="C21" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -27036,11 +29334,11 @@
     <row r="22">
       <c r="A22" s="198" t="str">
         <f>IF(AND(B22&lt;&gt;"", C22=TRUE, E22=Report!$B$1), B22, "")</f>
-        <v>Roth Stanislav ml.</v>
+        <v/>
       </c>
       <c r="B22" s="203" t="str">
         <f>IF(OR(E22=Report!$B$1, F22=Report!$B$1, G22=Report!$B$1, H22=Report!$B$1), D22, "")</f>
-        <v>Roth Stanislav ml.</v>
+        <v/>
       </c>
       <c r="C22" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -27160,7 +29458,7 @@
       </c>
       <c r="B24" s="203" t="str">
         <f>IF(OR(E24=Report!$B$1, F24=Report!$B$1, G24=Report!$B$1, H24=Report!$B$1), D24, "")</f>
-        <v/>
+        <v>Bubník Martin</v>
       </c>
       <c r="C24" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27337,7 +29635,7 @@
       </c>
       <c r="B27" s="203" t="str">
         <f>IF(OR(E27=Report!$B$1, F27=Report!$B$1, G27=Report!$B$1, H27=Report!$B$1), D27, "")</f>
-        <v/>
+        <v>Berdar Vasyl</v>
       </c>
       <c r="C27" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27466,7 +29764,7 @@
       </c>
       <c r="B29" s="203" t="str">
         <f>IF(OR(E29=Report!$B$1, F29=Report!$B$1, G29=Report!$B$1, H29=Report!$B$1), D29, "")</f>
-        <v>Raboch Tomáš</v>
+        <v/>
       </c>
       <c r="C29" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27586,7 +29884,7 @@
       </c>
       <c r="B31" s="203" t="str">
         <f>IF(OR(E31=Report!$B$1, F31=Report!$B$1, G31=Report!$B$1, H31=Report!$B$1), D31, "")</f>
-        <v/>
+        <v>Gorol Patrik</v>
       </c>
       <c r="C31" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27652,7 +29950,7 @@
       </c>
       <c r="B32" s="203" t="str">
         <f>IF(OR(E32=Report!$B$1, F32=Report!$B$1, G32=Report!$B$1, H32=Report!$B$1), D32, "")</f>
-        <v>Kratochvíl Kryštof</v>
+        <v/>
       </c>
       <c r="C32" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27712,7 +30010,7 @@
       </c>
       <c r="B33" s="203" t="str">
         <f>IF(OR(E33=Report!$B$1, F33=Report!$B$1, G33=Report!$B$1, H33=Report!$B$1), D33, "")</f>
-        <v/>
+        <v>Hegedüs Gergö</v>
       </c>
       <c r="C33" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27772,7 +30070,7 @@
       </c>
       <c r="B34" s="203" t="str">
         <f>IF(OR(E34=Report!$B$1, F34=Report!$B$1, G34=Report!$B$1, H34=Report!$B$1), D34, "")</f>
-        <v/>
+        <v>Barvínková Eliška</v>
       </c>
       <c r="C34" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27895,7 +30193,7 @@
       </c>
       <c r="B36" s="203" t="str">
         <f>IF(OR(E36=Report!$B$1, F36=Report!$B$1, G36=Report!$B$1, H36=Report!$B$1), D36, "")</f>
-        <v>Tůma Vladimír</v>
+        <v/>
       </c>
       <c r="C36" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -27955,7 +30253,7 @@
       </c>
       <c r="B37" s="203" t="str">
         <f>IF(OR(E37=Report!$B$1, F37=Report!$B$1, G37=Report!$B$1, H37=Report!$B$1), D37, "")</f>
-        <v/>
+        <v>Kubík Martin</v>
       </c>
       <c r="C37" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -28078,7 +30376,7 @@
       </c>
       <c r="B39" s="203" t="str">
         <f>IF(OR(E39=Report!$B$1, F39=Report!$B$1, G39=Report!$B$1, H39=Report!$B$1), D39, "")</f>
-        <v/>
+        <v>Kopic Jakub</v>
       </c>
       <c r="C39" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -29827,7 +32125,7 @@
       <c r="A75" s="198"/>
       <c r="B75" s="203" t="str">
         <f>IF(OR(E75=Report!$B$1, F75=Report!$B$1, G75=Report!$B$1, H75=Report!$B$1), D75, "")</f>
-        <v/>
+        <v>Jurkovič Martin</v>
       </c>
       <c r="C75" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30061,7 +32359,7 @@
       <c r="A79" s="198"/>
       <c r="B79" s="203" t="str">
         <f>IF(OR(E79=Report!$B$1, F79=Report!$B$1, G79=Report!$B$1, H79=Report!$B$1), D79, "")</f>
-        <v/>
+        <v>Nekolný Vladimír</v>
       </c>
       <c r="C79" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30124,7 +32422,7 @@
       <c r="A80" s="198"/>
       <c r="B80" s="203" t="str">
         <f>IF(OR(E80=Report!$B$1, F80=Report!$B$1, G80=Report!$B$1, H80=Report!$B$1), D80, "")</f>
-        <v/>
+        <v>Hanibal Filip</v>
       </c>
       <c r="C80" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30304,7 +32602,7 @@
       <c r="A83" s="198"/>
       <c r="B83" s="203" t="str">
         <f>IF(OR(E83=Report!$B$1, F83=Report!$B$1, G83=Report!$B$1, H83=Report!$B$1), D83, "")</f>
-        <v/>
+        <v>Nedvěd Dominik</v>
       </c>
       <c r="C83" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30318,7 +32616,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F83" s="198"/>
+      <c r="F83" s="198" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G83" s="198"/>
       <c r="H83" s="198"/>
       <c r="I83" s="198"/>
@@ -30361,7 +32662,7 @@
       <c r="A84" s="198"/>
       <c r="B84" s="203" t="str">
         <f>IF(OR(E84=Report!$B$1, F84=Report!$B$1, G84=Report!$B$1, H84=Report!$B$1), D84, "")</f>
-        <v/>
+        <v>Lanský Zoltan</v>
       </c>
       <c r="C84" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30652,7 +32953,7 @@
       <c r="A89" s="198"/>
       <c r="B89" s="203" t="str">
         <f>IF(OR(E89=Report!$B$1, F89=Report!$B$1, G89=Report!$B$1, H89=Report!$B$1), D89, "")</f>
-        <v/>
+        <v>Lažek Jaroslav</v>
       </c>
       <c r="C89" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30880,7 +33181,7 @@
       <c r="A93" s="198"/>
       <c r="B93" s="203" t="str">
         <f>IF(OR(E93=Report!$B$1, F93=Report!$B$1, G93=Report!$B$1, H93=Report!$B$1), D93, "")</f>
-        <v/>
+        <v>Chlubna Tomáš</v>
       </c>
       <c r="C93" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31057,7 +33358,7 @@
       <c r="A96" s="198"/>
       <c r="B96" s="203" t="str">
         <f>IF(OR(E96=Report!$B$1, F96=Report!$B$1, G96=Report!$B$1, H96=Report!$B$1), D96, "")</f>
-        <v/>
+        <v>Hřebík Martin</v>
       </c>
       <c r="C96" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31123,7 +33424,7 @@
       <c r="A97" s="198"/>
       <c r="B97" s="203" t="str">
         <f>IF(OR(E97=Report!$B$1, F97=Report!$B$1, G97=Report!$B$1, H97=Report!$B$1), D97, "")</f>
-        <v/>
+        <v>Eszenyiová Patrícia</v>
       </c>
       <c r="C97" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31180,7 +33481,7 @@
       <c r="A98" s="198"/>
       <c r="B98" s="203" t="str">
         <f>IF(OR(E98=Report!$B$1, F98=Report!$B$1, G98=Report!$B$1, H98=Report!$B$1), D98, "")</f>
-        <v/>
+        <v>Reischl Jan</v>
       </c>
       <c r="C98" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31246,7 +33547,7 @@
       <c r="A99" s="198"/>
       <c r="B99" s="203" t="str">
         <f>IF(OR(E99=Report!$B$1, F99=Report!$B$1, G99=Report!$B$1, H99=Report!$B$1), D99, "")</f>
-        <v>Mikešová Adéla</v>
+        <v/>
       </c>
       <c r="C99" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31576,7 +33877,7 @@
       <c r="A105" s="198"/>
       <c r="B105" s="203" t="str">
         <f>IF(OR(E105=Report!$B$1, F105=Report!$B$1, G105=Report!$B$1, H105=Report!$B$1), D105, "")</f>
-        <v/>
+        <v>Kalina Filip</v>
       </c>
       <c r="C105" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31687,7 +33988,7 @@
       <c r="A107" s="198"/>
       <c r="B107" s="203" t="str">
         <f>IF(OR(E107=Report!$B$1, F107=Report!$B$1, G107=Report!$B$1, H107=Report!$B$1), D107, "")</f>
-        <v>Kaločai Rudolf</v>
+        <v/>
       </c>
       <c r="C107" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31744,7 +34045,7 @@
       <c r="A108" s="198"/>
       <c r="B108" s="203" t="str">
         <f>IF(OR(E108=Report!$B$1, F108=Report!$B$1, G108=Report!$B$1, H108=Report!$B$1), D108, "")</f>
-        <v/>
+        <v>Dušek Sam</v>
       </c>
       <c r="C108" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31861,7 +34162,7 @@
       <c r="A110" s="198"/>
       <c r="B110" s="203" t="str">
         <f>IF(OR(E110=Report!$B$1, F110=Report!$B$1, G110=Report!$B$1, H110=Report!$B$1), D110, "")</f>
-        <v/>
+        <v>Cieslar Marek</v>
       </c>
       <c r="C110" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -31975,7 +34276,7 @@
       <c r="A112" s="198"/>
       <c r="B112" s="203" t="str">
         <f>IF(OR(E112=Report!$B$1, F112=Report!$B$1, G112=Report!$B$1, H112=Report!$B$1), D112, "")</f>
-        <v>Vopatová Anna</v>
+        <v/>
       </c>
       <c r="C112" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32032,7 +34333,7 @@
       <c r="A113" s="198"/>
       <c r="B113" s="203" t="str">
         <f>IF(OR(E113=Report!$B$1, F113=Report!$B$1, G113=Report!$B$1, H113=Report!$B$1), D113, "")</f>
-        <v>Vopatová Šárka</v>
+        <v/>
       </c>
       <c r="C113" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32146,7 +34447,7 @@
       <c r="A115" s="198"/>
       <c r="B115" s="203" t="str">
         <f>IF(OR(E115=Report!$B$1, F115=Report!$B$1, G115=Report!$B$1, H115=Report!$B$1), D115, "")</f>
-        <v/>
+        <v>Serin David</v>
       </c>
       <c r="C115" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32371,7 +34672,7 @@
       <c r="A119" s="198"/>
       <c r="B119" s="203" t="str">
         <f>IF(OR(E119=Report!$B$1, F119=Report!$B$1, G119=Report!$B$1, H119=Report!$B$1), D119, "")</f>
-        <v>Světlík František</v>
+        <v/>
       </c>
       <c r="C119" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32428,7 +34729,7 @@
       <c r="A120" s="198"/>
       <c r="B120" s="203" t="str">
         <f>IF(OR(E120=Report!$B$1, F120=Report!$B$1, G120=Report!$B$1, H120=Report!$B$1), D120, "")</f>
-        <v>Ženíšek Lukáš</v>
+        <v/>
       </c>
       <c r="C120" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32539,7 +34840,7 @@
       <c r="A122" s="198"/>
       <c r="B122" s="203" t="str">
         <f>IF(OR(E122=Report!$B$1, F122=Report!$B$1, G122=Report!$B$1, H122=Report!$B$1), D122, "")</f>
-        <v>Roth Stanislav st.</v>
+        <v/>
       </c>
       <c r="C122" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32755,7 +35056,7 @@
       <c r="A126" s="198"/>
       <c r="B126" s="203" t="str">
         <f>IF(OR(E126=Report!$B$1, F126=Report!$B$1, G126=Report!$B$1, H126=Report!$B$1), D126, "")</f>
-        <v/>
+        <v>Břicháč Pavel</v>
       </c>
       <c r="C126" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32869,7 +35170,7 @@
       <c r="A128" s="198"/>
       <c r="B128" s="203" t="str">
         <f>IF(OR(E128=Report!$B$1, F128=Report!$B$1, G128=Report!$B$1, H128=Report!$B$1), D128, "")</f>
-        <v/>
+        <v>Weindling Josef</v>
       </c>
       <c r="C128" s="198" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>

--- a/google_data/Opravný Report.xlsx
+++ b/google_data/Opravný Report.xlsx
@@ -3427,8 +3427,8 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),0.37901842169458555)</f>
-        <v>0.3790184217</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),0.37802113773511886)</f>
+        <v>0.3780211377</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="16">
@@ -3617,7 +3617,7 @@
       <c r="I11" s="15"/>
       <c r="J11" s="40">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="41" t="s">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="M17" s="57">
         <f>SUM(I25:I31)</f>
-        <v>360</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1">
@@ -3974,8 +3974,8 @@
         <v>1</v>
       </c>
       <c r="I25" s="82">
-        <f t="shared" ref="I25:I31" si="3">IF(H25,G25*45, 0)</f>
-        <v>360</v>
+        <f>IF(H25,G25*40, 0)</f>
+        <v>320</v>
       </c>
       <c r="J25" s="83"/>
       <c r="K25" s="83"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="H26" s="81"/>
       <c r="I26" s="82">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="I26:I31" si="3">IF(H26,G26*45, 0)</f>
         <v>0</v>
       </c>
       <c r="J26" s="86">
